--- a/AAII_Financials/Quarterly/IBKR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IBKR_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>IBKR</t>
   </si>
@@ -656,408 +656,420 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2104000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2055000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1851000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1766000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1522000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1100000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>768000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>695000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>658000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>515000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>787000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>978000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>654000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>593000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>587000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>645000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>640000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>697000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>652000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>623000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>637000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>578000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>565000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>581000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>500000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>456000</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>409000</v>
       </c>
       <c r="AD8" s="3">
         <v>409000</v>
       </c>
       <c r="AE8" s="3">
+        <v>409000</v>
+      </c>
+      <c r="AF8" s="3">
         <v>215000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>366000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1065000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1008000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>944000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>805000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>636000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>396000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>189000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>121000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>108000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>112000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>87000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>153000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>121000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>119000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>124000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>113000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>131000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>177000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>173000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>162000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>142000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>119000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>108000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>94000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>78000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>61000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>51000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>35000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>22000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1039000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1047000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>907000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>961000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>886000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>704000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>579000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>574000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>550000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>403000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>700000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>825000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>533000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>474000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>463000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>532000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>509000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>520000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>479000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>461000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>495000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>459000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>457000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>487000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>422000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>395000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>358000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>374000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>193000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>345000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1090,8 +1102,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1182,8 +1195,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1274,8 +1290,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1330,17 +1349,17 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
+      <c r="W14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
@@ -1348,11 +1367,11 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3">
         <v>-93000</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
@@ -1366,8 +1385,11 @@
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1458,8 +1480,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1489,192 +1514,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1288000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1215000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1199000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1005000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>833000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>577000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>376000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>301000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>285000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>281000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>246000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>339000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>262000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>259000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>365000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>337000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>319000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>362000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>361000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>381000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>325000</v>
-      </c>
-      <c r="X17" s="3">
-        <v>282000</v>
       </c>
       <c r="Y17" s="3">
         <v>282000</v>
       </c>
       <c r="Z17" s="3">
+        <v>282000</v>
+      </c>
+      <c r="AA17" s="3">
         <v>281000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>136000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>219000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>234000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>196000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>187000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>816000</v>
+      </c>
+      <c r="E18" s="3">
         <v>840000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>652000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>761000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>689000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>523000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>392000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>394000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>373000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>234000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>541000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>639000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>392000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>334000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>222000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>308000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>321000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>335000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>291000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>242000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>312000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>296000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>283000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>300000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>364000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>237000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>175000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>213000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>28000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1707,8 +1739,9 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1758,141 +1791,147 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-9000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-54000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-66000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>97000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-20000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>40000</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>31000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>29000</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>832000</v>
+      </c>
+      <c r="E21" s="3">
         <v>857000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>668000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>777000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>704000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>537000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>406000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>409000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>386000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>246000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>553000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>652000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>403000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>345000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>232000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>318000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>322000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>288000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>232000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>346000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>317000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>282000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>276000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>347000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>371000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>274000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>210000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>219000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>35000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>189000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1983,192 +2022,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>816000</v>
+      </c>
+      <c r="E23" s="3">
         <v>840000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>652000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>761000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>689000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>523000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>392000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>394000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>373000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>234000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>541000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>639000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>392000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>334000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>222000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>308000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>312000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>281000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>225000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>339000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>309000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>276000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>271000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>340000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>364000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>268000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>204000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>213000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>28000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>77000</v>
+      </c>
+      <c r="E24" s="3">
         <v>68000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>51000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>61000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>56000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>40000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>32000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>28000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>35000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>28000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>35000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>53000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>12000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>32000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>15000</v>
-      </c>
-      <c r="R24" s="3">
-        <v>18000</v>
       </c>
       <c r="S24" s="3">
         <v>18000</v>
       </c>
       <c r="T24" s="3">
+        <v>18000</v>
+      </c>
+      <c r="U24" s="3">
         <v>20000</v>
-      </c>
-      <c r="U24" s="3">
-        <v>15000</v>
       </c>
       <c r="V24" s="3">
         <v>15000</v>
       </c>
       <c r="W24" s="3">
+        <v>15000</v>
+      </c>
+      <c r="X24" s="3">
         <v>19000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>18000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>13000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>21000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>23000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>21000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>17000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>18000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>7000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2259,192 +2307,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>739000</v>
+      </c>
+      <c r="E26" s="3">
         <v>772000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>601000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>700000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>633000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>483000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>360000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>366000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>338000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>206000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>506000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>586000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>380000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>302000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>207000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>290000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>294000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>261000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>210000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>324000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>290000</v>
-      </c>
-      <c r="X26" s="3">
-        <v>258000</v>
       </c>
       <c r="Y26" s="3">
         <v>258000</v>
       </c>
       <c r="Z26" s="3">
+        <v>258000</v>
+      </c>
+      <c r="AA26" s="3">
         <v>319000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>341000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>247000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>187000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>195000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>21000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>168000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E27" s="3">
         <v>167000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>125000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>148000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>136000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>99000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>72000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>73000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>67000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>42000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>92000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>107000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>71000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>46000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>32000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>46000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>44000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>36000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>32000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>49000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>43000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>39000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>41000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>46000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>175000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>31000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>23000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>24000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>4000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2535,8 +2592,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2591,17 +2651,17 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3" t="s">
+      <c r="W29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2609,11 +2669,11 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-177000</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2627,8 +2687,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2719,8 +2782,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2811,8 +2877,11 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2862,141 +2931,147 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>9000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>54000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>66000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-97000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>20000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>12000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-40000</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-31000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-29000</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E33" s="3">
         <v>167000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>125000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>148000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>136000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>99000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>72000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>73000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>67000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>42000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>92000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>107000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>71000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>46000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>32000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>46000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>44000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>36000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>32000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>49000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>43000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>39000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>41000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>46000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>31000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>23000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>24000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>4000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3087,197 +3162,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E35" s="3">
         <v>167000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>125000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>148000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>136000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>99000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>72000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>73000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>67000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>42000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>92000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>107000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>71000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>46000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>32000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>46000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>44000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>36000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>32000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>49000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>43000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>39000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>41000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>46000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>31000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>23000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>24000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>4000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3310,8 +3394,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3344,100 +3429,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3753000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3824000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3681000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3214000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3436000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3184000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2881000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2667000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2395000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2838000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3218000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2627000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4292000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3292000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3115000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3101000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2882000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3035000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3162000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2546000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2597000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3062000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2500000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1901000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1732000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2056000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2115000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1656000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1925000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1550000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3528,100 +3617,106 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>46490000</v>
+      </c>
+      <c r="E43" s="3">
         <v>45768000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>43757000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>41541000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>42570000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>43969000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>44641000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>50612000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>58833000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>54654000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>54045000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>46129000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>40691000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>32987000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>27154000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>21740000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>32147000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>26969000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>26770000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>26746000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>27864000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>31876000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>30221000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>30565000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>30760000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>26444000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>24056000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>22387000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>20506000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>19053000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3712,68 +3807,71 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>64226000</v>
+      </c>
+      <c r="E45" s="3">
         <v>57720000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>59227000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>61341000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>56948000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>56733000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>54245000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>48931000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>38009000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>37525000</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3">
         <v>21204000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>15903000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>12789000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>12684000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>14272000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>9400000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>8794000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>8819000</v>
       </c>
-      <c r="V45" s="3">
-        <v>0</v>
-      </c>
       <c r="W45" s="3">
         <v>0</v>
       </c>
@@ -3804,8 +3902,11 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3896,162 +3997,168 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>12827000</v>
+      </c>
+      <c r="E47" s="3">
         <v>12282000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>12925000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>12388000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>11263000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9861000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>10694000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>11290000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8965000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>10578000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>30621000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8040000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6378000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5848000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7092000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>6082000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>8943000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7284000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>6522000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7103000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>6692000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>6470000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>6209000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>6060000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>8146000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>7364000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>6834000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>7058000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>7777000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>8756000</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E48" s="3">
         <v>117000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>119000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>120000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>119000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>109000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>105000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>109000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>101000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>100000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>96000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>98000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>101000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>107000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>110000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>114000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>118000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>122000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>127000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>131000</v>
-      </c>
-      <c r="W48" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>8</v>
@@ -4062,8 +4169,8 @@
       <c r="Z48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA48" s="3">
-        <v>0</v>
+      <c r="AA48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB48" s="3">
         <v>0</v>
@@ -4080,8 +4187,11 @@
       <c r="AF48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4172,8 +4282,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4264,8 +4377,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4356,8 +4472,11 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4389,67 +4508,70 @@
         <v>0</v>
       </c>
       <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
         <v>15635000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>25069000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>27821000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>29316000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>33450000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>30187000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>17824000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>21246000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>20273000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>26575000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>23098000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>20355000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>21054000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>20268000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>20232000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>23566000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>24187000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>24710000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>24017000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>25250000</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4540,100 +4662,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>128423000</v>
+      </c>
+      <c r="E54" s="3">
         <v>120636000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>120593000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>119469000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>115143000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>114683000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>113386000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>114423000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>109113000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>106282000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>104331000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>103764000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>95679000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>84698000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>83965000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>75849000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>71676000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>67804000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>66034000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>63526000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>60547000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>62062000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>60303000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>59093000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>61162000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>59843000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>57597000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>56257000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>54673000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>55064000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4666,8 +4794,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4700,284 +4829,294 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>102345000</v>
+      </c>
+      <c r="E57" s="3">
         <v>96255000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>97090000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>95939000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>94091000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>93618000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>91691000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>91923000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>86782000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>85345000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>82082000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>81928000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>76441000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>69480000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>69360000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>63348000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>56791000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>55041000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>53763000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>51403000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>48615000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>50347000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>48660000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>47928000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>48165000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>48167000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>46777000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>44865000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>42335000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>43090000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11364000</v>
+      </c>
+      <c r="E58" s="3">
         <v>10493000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10278000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10729000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>8958000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>9525000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10713000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>11690000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11796000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>10563000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>12005000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>12079000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>9956000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6366000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5995000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4058000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>6335000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3970000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4116000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4265000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4054000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>28000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>193000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>19000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1331000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>38000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>9000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>38000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>74000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>454000</v>
+      </c>
+      <c r="E59" s="3">
         <v>426000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>411000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>378000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>333000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>229000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>162000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>138000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>131000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>130000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>125000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>129000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>126000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>119000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>122000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>135000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>153000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>163000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>178000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>177000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>41000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>35000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>29000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>27000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>22000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>17000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>14000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>11000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>6000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5068,8 +5207,11 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5160,8 +5302,11 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5252,8 +5397,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5344,8 +5492,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5436,8 +5587,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5528,100 +5682,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>124839000</v>
+      </c>
+      <c r="E66" s="3">
         <v>117246000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>117435000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>116468000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>112295000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>112006000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>110862000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>111967000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>106718000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>103951000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>102181000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>101728000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>93728000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>83089000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>82427000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>74363000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>70224000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>66399000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>64654000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>62201000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>59265000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>60819000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>59120000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>57961000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>60072000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>58747000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>56548000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>55260000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>53699000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>54083000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5654,8 +5814,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5746,8 +5907,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5838,8 +6002,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5930,8 +6097,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6022,100 +6192,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1852000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1703000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1546000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1432000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1294000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1168000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1079000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1017000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>953000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>896000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>864000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>781000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>683000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>621000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>583000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>558000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>520000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>484000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>456000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>431000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>390000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>354000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>323000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>290000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>251000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>260000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>236000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>220000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>203000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6206,8 +6382,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6298,8 +6477,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6390,100 +6572,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3584000</v>
+      </c>
+      <c r="E76" s="3">
         <v>3390000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3158000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3001000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2848000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2677000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2524000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2456000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2395000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2331000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2150000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2036000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1951000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1609000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1538000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1486000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1452000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1405000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1380000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1325000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1282000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1243000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1183000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1132000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1090000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1096000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1049000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>997000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>974000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>981000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6574,197 +6762,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E81" s="3">
         <v>167000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>125000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>148000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>136000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>99000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>72000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>73000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>67000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>42000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>92000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>107000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>71000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>46000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>32000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>46000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>44000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>36000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>32000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>49000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>43000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>39000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>41000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>46000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>31000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>23000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>24000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>4000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6797,52 +6994,53 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E83" s="3">
         <v>17000</v>
-      </c>
-      <c r="E83" s="3">
-        <v>16000</v>
       </c>
       <c r="F83" s="3">
         <v>16000</v>
       </c>
       <c r="G83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="H83" s="3">
         <v>15000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>14000</v>
       </c>
       <c r="I83" s="3">
         <v>14000</v>
       </c>
       <c r="J83" s="3">
+        <v>14000</v>
+      </c>
+      <c r="K83" s="3">
         <v>15000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>13000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>12000</v>
       </c>
       <c r="M83" s="3">
         <v>12000</v>
       </c>
       <c r="N83" s="3">
+        <v>12000</v>
+      </c>
+      <c r="O83" s="3">
         <v>13000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>11000</v>
       </c>
       <c r="P83" s="3">
         <v>11000</v>
       </c>
       <c r="Q83" s="3">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="R83" s="3">
         <v>10000</v>
@@ -6851,7 +7049,7 @@
         <v>10000</v>
       </c>
       <c r="T83" s="3">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="U83" s="3">
         <v>7000</v>
@@ -6860,22 +7058,22 @@
         <v>7000</v>
       </c>
       <c r="W83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="X83" s="3">
         <v>8000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>6000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>5000</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>7000</v>
       </c>
       <c r="AA83" s="3">
         <v>7000</v>
       </c>
       <c r="AB83" s="3">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="AC83" s="3">
         <v>6000</v>
@@ -6884,13 +7082,16 @@
         <v>6000</v>
       </c>
       <c r="AE83" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AF83" s="3">
         <v>7000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6981,8 +7182,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7073,8 +7277,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7165,8 +7372,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7257,8 +7467,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7349,100 +7562,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2369000</v>
+      </c>
+      <c r="E89" s="3">
         <v>979000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2119000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-923000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-30000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2414000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-541000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2125000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-375000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1213000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1324000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3734000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4596000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-174000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1557000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5203000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>488000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>133000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1442000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>603000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-408000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>632000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>931000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1201000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-2153000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>709000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>807000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>779000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>430000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>102000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7475,100 +7694,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-15000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-17000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-19000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-18000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-19000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-26000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-17000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-21000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-19000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-10000</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-12000</v>
       </c>
       <c r="S91" s="3">
         <v>-12000</v>
       </c>
       <c r="T91" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="U91" s="3">
         <v>-17000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-19000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-26000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-13000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7659,8 +7882,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7751,100 +7977,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-18000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-15000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>6000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-19000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-22000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-129000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-21000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-17000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-21000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-22000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-12000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-11000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-12000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-15000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-20000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-42000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-14000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-28000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-12000</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>-4000</v>
       </c>
       <c r="AC94" s="3">
         <v>-4000</v>
       </c>
       <c r="AD94" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-17000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7877,19 +8109,20 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-10000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-11000</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-10000</v>
       </c>
       <c r="G96" s="3">
         <v>-10000</v>
@@ -7898,19 +8131,19 @@
         <v>-10000</v>
       </c>
       <c r="I96" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="J96" s="3">
         <v>-11000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-9000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-10000</v>
       </c>
       <c r="L96" s="3">
         <v>-10000</v>
       </c>
       <c r="M96" s="3">
-        <v>-9000</v>
+        <v>-10000</v>
       </c>
       <c r="N96" s="3">
         <v>-9000</v>
@@ -7919,13 +8152,13 @@
         <v>-9000</v>
       </c>
       <c r="P96" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-7000</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-8000</v>
       </c>
       <c r="S96" s="3">
         <v>-8000</v>
@@ -7934,19 +8167,19 @@
         <v>-8000</v>
       </c>
       <c r="U96" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="V96" s="3">
         <v>-7000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-8000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-7000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-8000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-7000</v>
       </c>
       <c r="Z96" s="3">
         <v>-7000</v>
@@ -7964,13 +8197,16 @@
         <v>-7000</v>
       </c>
       <c r="AE96" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8061,8 +8297,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8153,8 +8392,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8245,280 +8487,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-108000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-127000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-252000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-137000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-122000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-70000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-173000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-105000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-174000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-506000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>158000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-555000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>416000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-27000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-63000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-61000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-242000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-46000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-70000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-58000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-222000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-55000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-64000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-80000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-133000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-84000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-77000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>9000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>148000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-76000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>31000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>19000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>158000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-123000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-105000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-41000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-40000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>21000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-76000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>95000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>45000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>22000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-38000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>38000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-28000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>16000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-5000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-78000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>8000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>5000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>38000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>23000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-47000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2384000</v>
+      </c>
+      <c r="E102" s="3">
         <v>758000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1883000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1035000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-13000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2199000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-831000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1965000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-680000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>646000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1486000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3636000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4114000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>282000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1574000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5091000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>453000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-152000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1392000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>489000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-485000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>399000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>770000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1137000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2246000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>577000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>757000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>719000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>375000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>107000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IBKR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IBKR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
   <si>
     <t>IBKR</t>
   </si>
@@ -656,420 +656,432 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2216000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2104000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2055000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1851000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1766000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1522000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1100000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>768000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>695000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>658000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>515000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>787000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>978000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>654000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>593000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>587000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>645000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>640000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>697000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>652000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>623000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>637000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>578000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>565000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>581000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>500000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>456000</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>409000</v>
       </c>
       <c r="AE8" s="3">
         <v>409000</v>
       </c>
       <c r="AF8" s="3">
+        <v>409000</v>
+      </c>
+      <c r="AG8" s="3">
         <v>215000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>366000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1114000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1065000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1008000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>944000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>805000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>636000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>396000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>189000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>121000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>108000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>112000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>87000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>153000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>121000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>119000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>124000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>113000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>131000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>177000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>173000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>162000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>142000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>119000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>108000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>94000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>78000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>61000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>51000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>35000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>22000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1102000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1039000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1047000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>907000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>961000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>886000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>704000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>579000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>574000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>550000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>403000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>700000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>825000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>533000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>474000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>463000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>532000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>509000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>520000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>479000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>461000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>495000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>459000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>457000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>487000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>422000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>395000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>358000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>374000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>193000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>345000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1103,8 +1115,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1198,8 +1211,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1293,8 +1309,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1352,17 +1371,17 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
+      <c r="X14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
@@ -1370,11 +1389,11 @@
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3">
         <v>-93000</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
@@ -1388,8 +1407,11 @@
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1483,8 +1505,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1515,198 +1540,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1350000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1288000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1215000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1199000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1005000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>833000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>577000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>376000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>301000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>285000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>281000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>246000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>339000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>262000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>259000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>365000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>337000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>319000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>362000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>361000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>381000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>325000</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>282000</v>
       </c>
       <c r="Z17" s="3">
         <v>282000</v>
       </c>
       <c r="AA17" s="3">
+        <v>282000</v>
+      </c>
+      <c r="AB17" s="3">
         <v>281000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>136000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>219000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>234000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>196000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>187000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>866000</v>
+      </c>
+      <c r="E18" s="3">
         <v>816000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>840000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>652000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>761000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>689000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>523000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>392000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>394000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>373000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>234000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>541000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>639000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>392000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>334000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>222000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>308000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>321000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>335000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>291000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>242000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>312000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>296000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>283000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>300000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>364000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>237000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>175000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>213000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>28000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1740,8 +1772,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1794,144 +1827,150 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-9000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-54000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-66000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>97000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-20000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-12000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>40000</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>31000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>29000</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
         <v>0</v>
       </c>
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>883000</v>
+      </c>
+      <c r="E21" s="3">
         <v>832000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>857000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>668000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>777000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>704000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>537000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>406000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>409000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>386000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>246000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>553000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>652000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>403000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>345000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>232000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>318000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>322000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>288000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>232000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>346000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>317000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>282000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>276000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>347000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>371000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>274000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>210000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>219000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>35000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>189000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2025,198 +2064,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>866000</v>
+      </c>
+      <c r="E23" s="3">
         <v>816000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>840000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>652000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>761000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>689000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>523000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>392000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>394000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>373000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>234000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>541000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>639000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>392000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>334000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>222000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>308000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>312000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>281000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>225000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>339000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>309000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>276000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>271000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>340000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>364000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>268000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>204000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>213000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>28000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E24" s="3">
         <v>77000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>68000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>51000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>61000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>56000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>40000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>32000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>28000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>35000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>28000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>35000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>53000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>12000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>32000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>15000</v>
-      </c>
-      <c r="S24" s="3">
-        <v>18000</v>
       </c>
       <c r="T24" s="3">
         <v>18000</v>
       </c>
       <c r="U24" s="3">
+        <v>18000</v>
+      </c>
+      <c r="V24" s="3">
         <v>20000</v>
-      </c>
-      <c r="V24" s="3">
-        <v>15000</v>
       </c>
       <c r="W24" s="3">
         <v>15000</v>
       </c>
       <c r="X24" s="3">
+        <v>15000</v>
+      </c>
+      <c r="Y24" s="3">
         <v>19000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>18000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>13000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>21000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>23000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>21000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>17000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>18000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>7000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2310,198 +2358,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>795000</v>
+      </c>
+      <c r="E26" s="3">
         <v>739000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>772000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>601000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>700000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>633000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>483000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>360000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>366000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>338000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>206000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>506000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>586000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>380000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>302000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>207000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>290000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>294000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>261000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>210000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>324000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>290000</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>258000</v>
       </c>
       <c r="Z26" s="3">
         <v>258000</v>
       </c>
       <c r="AA26" s="3">
+        <v>258000</v>
+      </c>
+      <c r="AB26" s="3">
         <v>319000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>341000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>247000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>187000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>195000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>21000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>168000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>175000</v>
+      </c>
+      <c r="E27" s="3">
         <v>160000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>167000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>125000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>148000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>136000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>99000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>72000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>73000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>67000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>42000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>92000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>107000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>71000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>46000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>32000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>46000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>44000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>36000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>32000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>49000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>43000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>39000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>41000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>46000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>175000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>31000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>23000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>24000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>4000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2595,8 +2652,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2654,17 +2714,17 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3" t="s">
+      <c r="X29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2672,11 +2732,11 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-177000</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2690,8 +2750,11 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2785,8 +2848,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2880,8 +2946,11 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2934,144 +3003,150 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>9000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>54000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>66000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-97000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>20000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>12000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-40000</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-31000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-29000</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
         <v>0</v>
       </c>
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>175000</v>
+      </c>
+      <c r="E33" s="3">
         <v>160000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>167000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>125000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>148000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>136000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>99000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>72000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>73000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>67000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>42000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>92000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>107000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>71000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>46000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>32000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>46000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>44000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>36000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>32000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>49000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>43000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>39000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>41000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>46000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>31000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>23000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>24000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>4000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3165,203 +3240,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>175000</v>
+      </c>
+      <c r="E35" s="3">
         <v>160000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>167000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>125000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>148000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>136000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>99000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>72000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>73000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>67000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>42000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>92000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>107000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>71000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>46000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>32000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>46000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>44000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>36000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>32000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>49000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>43000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>39000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>41000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>46000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>31000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>23000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>24000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>4000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3395,8 +3479,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3430,103 +3515,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4063000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3753000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3824000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3681000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3214000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3436000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3184000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2881000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2667000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2395000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2838000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3218000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2627000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4292000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3292000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3115000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3101000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2882000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3035000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3162000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2546000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2597000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3062000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2500000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1901000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1732000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2056000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2115000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1656000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1925000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1550000</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3620,103 +3709,109 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>53516000</v>
+      </c>
+      <c r="E43" s="3">
         <v>46490000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>45768000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>43757000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>41541000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>42570000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>43969000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>44641000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>50612000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>58833000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>54654000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>54045000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>46129000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>40691000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>32987000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>27154000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>21740000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>32147000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>26969000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>26770000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>26746000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>27864000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>31876000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>30221000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>30565000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>30760000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>26444000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>24056000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>22387000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>20506000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>19053000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3810,71 +3905,74 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>59253000</v>
+      </c>
+      <c r="E45" s="3">
         <v>64226000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>57720000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>59227000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>61341000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>56948000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>56733000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>54245000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>48931000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>38009000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>37525000</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
       <c r="O45" s="3">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3">
         <v>21204000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>15903000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>12789000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>12684000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>14272000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>9400000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>8794000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>8819000</v>
       </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
       <c r="X45" s="3">
         <v>0</v>
       </c>
@@ -3905,8 +4003,11 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4000,168 +4101,174 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>14148000</v>
+      </c>
+      <c r="E47" s="3">
         <v>12827000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>12282000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>12925000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>12388000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>11263000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>9861000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>10694000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>11290000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8965000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>10578000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>30621000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8040000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6378000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>5848000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7092000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>6082000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8943000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7284000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>6522000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7103000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>6692000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>6470000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>6209000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>6060000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>8146000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>7364000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>6834000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>7058000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>7777000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>8756000</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E48" s="3">
         <v>120000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>117000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>119000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>120000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>119000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>109000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>105000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>109000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>101000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>100000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>96000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>98000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>101000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>107000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>110000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>114000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>118000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>122000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>127000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>131000</v>
-      </c>
-      <c r="X48" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y48" s="3" t="s">
         <v>8</v>
@@ -4172,8 +4279,8 @@
       <c r="AA48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB48" s="3">
-        <v>0</v>
+      <c r="AB48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC48" s="3">
         <v>0</v>
@@ -4190,8 +4297,11 @@
       <c r="AG48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4285,8 +4395,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4380,8 +4493,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4475,8 +4591,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4511,67 +4630,70 @@
         <v>0</v>
       </c>
       <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
         <v>15635000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>25069000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>27821000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>29316000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>33450000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>30187000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>17824000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>21246000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>20273000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>26575000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>23098000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>20355000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>21054000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>20268000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>20232000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>23566000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>24187000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>24710000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>24017000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>25250000</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4665,103 +4787,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>132238000</v>
+      </c>
+      <c r="E54" s="3">
         <v>128423000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>120636000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>120593000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>119469000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>115143000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>114683000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>113386000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>114423000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>109113000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>106282000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>104331000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>103764000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>95679000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>84698000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>83965000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>75849000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>71676000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>67804000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>66034000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>63526000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>60547000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>62062000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>60303000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>59093000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>61162000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>59843000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>57597000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>56257000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>54673000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>55064000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4795,8 +4923,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4830,293 +4959,303 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>102663000</v>
+      </c>
+      <c r="E57" s="3">
         <v>102345000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>96255000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>97090000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>95939000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>94091000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>93618000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>91691000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>91923000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>86782000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>85345000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>82082000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>81928000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>76441000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>69480000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>69360000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>63348000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>56791000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>55041000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>53763000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>51403000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>48615000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>50347000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>48660000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>47928000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>48165000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>48167000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>46777000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>44865000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>42335000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>43090000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>14230000</v>
+      </c>
+      <c r="E58" s="3">
         <v>11364000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10493000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10278000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10729000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>8958000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>9525000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10713000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11690000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11796000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>10563000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>12005000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>12079000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>9956000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6366000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5995000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4058000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>6335000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3970000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4116000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4265000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4054000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>28000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>193000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>19000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1331000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>38000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>9000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>38000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>74000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>450000</v>
+      </c>
+      <c r="E59" s="3">
         <v>454000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>426000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>411000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>378000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>333000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>229000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>162000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>138000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>131000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>130000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>125000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>129000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>126000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>119000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>122000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>135000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>153000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>163000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>178000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>177000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>41000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>35000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>29000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>27000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>22000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>17000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>14000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>11000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>6000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5210,8 +5349,11 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5305,8 +5447,11 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5400,8 +5545,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5495,8 +5643,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5590,8 +5741,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5685,103 +5839,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>128506000</v>
+      </c>
+      <c r="E66" s="3">
         <v>124839000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>117246000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>117435000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>116468000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>112295000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>112006000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>110862000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>111967000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>106718000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>103951000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>102181000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>101728000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>93728000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>83089000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>82427000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>74363000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>70224000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>66399000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>64654000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>62201000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>59265000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>60819000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>59120000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>57961000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>60072000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>58747000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>56548000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>55260000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>53699000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>54083000</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5815,8 +5975,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5910,8 +6071,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6005,8 +6169,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6100,8 +6267,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6195,103 +6365,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2016000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1852000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1703000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1546000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1432000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1294000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1168000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1079000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1017000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>953000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>896000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>864000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>781000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>683000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>621000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>583000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>558000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>520000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>484000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>456000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>431000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>390000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>354000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>323000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>290000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>251000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>260000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>236000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>220000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>203000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6385,8 +6561,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6480,8 +6659,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6575,103 +6757,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3732000</v>
+      </c>
+      <c r="E76" s="3">
         <v>3584000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3390000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3158000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3001000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2848000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2677000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2524000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2456000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2395000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2331000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2150000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2036000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1951000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1609000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1538000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1486000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1452000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1405000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1380000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1325000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1282000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1243000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1183000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1132000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1090000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1096000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1049000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>997000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>974000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>981000</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6765,203 +6953,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>175000</v>
+      </c>
+      <c r="E81" s="3">
         <v>160000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>167000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>125000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>148000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>136000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>99000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>72000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>73000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>67000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>42000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>92000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>107000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>71000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>46000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>32000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>46000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>44000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>36000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>32000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>49000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>43000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>39000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>41000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>46000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>31000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>23000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>24000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>4000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6995,55 +7192,56 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E83" s="3">
         <v>16000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>17000</v>
-      </c>
-      <c r="F83" s="3">
-        <v>16000</v>
       </c>
       <c r="G83" s="3">
         <v>16000</v>
       </c>
       <c r="H83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="I83" s="3">
         <v>15000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>14000</v>
       </c>
       <c r="J83" s="3">
         <v>14000</v>
       </c>
       <c r="K83" s="3">
+        <v>14000</v>
+      </c>
+      <c r="L83" s="3">
         <v>15000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>13000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>12000</v>
       </c>
       <c r="N83" s="3">
         <v>12000</v>
       </c>
       <c r="O83" s="3">
+        <v>12000</v>
+      </c>
+      <c r="P83" s="3">
         <v>13000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>11000</v>
       </c>
       <c r="Q83" s="3">
         <v>11000</v>
       </c>
       <c r="R83" s="3">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="S83" s="3">
         <v>10000</v>
@@ -7052,7 +7250,7 @@
         <v>10000</v>
       </c>
       <c r="U83" s="3">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="V83" s="3">
         <v>7000</v>
@@ -7061,22 +7259,22 @@
         <v>7000</v>
       </c>
       <c r="X83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="Y83" s="3">
         <v>8000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>6000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>5000</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>7000</v>
       </c>
       <c r="AB83" s="3">
         <v>7000</v>
       </c>
       <c r="AC83" s="3">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="AD83" s="3">
         <v>6000</v>
@@ -7085,13 +7283,16 @@
         <v>6000</v>
       </c>
       <c r="AF83" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AG83" s="3">
         <v>7000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7185,8 +7386,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7280,8 +7484,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7375,8 +7582,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7470,8 +7680,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7565,103 +7778,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1683000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2369000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>979000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2119000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-923000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-30000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2414000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-541000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2125000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-375000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1213000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1324000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3734000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4596000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-174000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1557000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>5203000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>488000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>133000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1442000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>603000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-408000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>632000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>931000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1201000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-2153000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>709000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>807000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>779000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>430000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>102000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7695,103 +7914,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-9000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-15000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-17000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-19000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-18000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-13000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-19000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-26000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-17000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-21000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-19000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-9000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-10000</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-12000</v>
       </c>
       <c r="T91" s="3">
         <v>-12000</v>
       </c>
       <c r="U91" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="V91" s="3">
         <v>-17000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-19000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-26000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-13000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7885,8 +8108,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7980,103 +8206,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-25000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-18000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-15000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>6000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-19000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-22000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-12000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-129000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-21000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-17000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-21000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-12000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-11000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-12000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-15000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-20000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-42000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-14000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-28000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-12000</v>
-      </c>
-      <c r="AC94" s="3">
-        <v>-4000</v>
       </c>
       <c r="AD94" s="3">
         <v>-4000</v>
       </c>
       <c r="AE94" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-17000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8110,8 +8342,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8119,13 +8352,13 @@
         <v>-11000</v>
       </c>
       <c r="E96" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="F96" s="3">
         <v>-10000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-11000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-10000</v>
       </c>
       <c r="H96" s="3">
         <v>-10000</v>
@@ -8134,19 +8367,19 @@
         <v>-10000</v>
       </c>
       <c r="J96" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-11000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-9000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-10000</v>
       </c>
       <c r="M96" s="3">
         <v>-10000</v>
       </c>
       <c r="N96" s="3">
-        <v>-9000</v>
+        <v>-10000</v>
       </c>
       <c r="O96" s="3">
         <v>-9000</v>
@@ -8155,13 +8388,13 @@
         <v>-9000</v>
       </c>
       <c r="Q96" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="R96" s="3">
         <v>-8000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-7000</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-8000</v>
       </c>
       <c r="T96" s="3">
         <v>-8000</v>
@@ -8170,19 +8403,19 @@
         <v>-8000</v>
       </c>
       <c r="V96" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-7000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-8000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-8000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-7000</v>
       </c>
       <c r="AA96" s="3">
         <v>-7000</v>
@@ -8200,13 +8433,16 @@
         <v>-7000</v>
       </c>
       <c r="AF96" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8300,8 +8536,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8395,8 +8634,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8490,289 +8732,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-137000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-108000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-127000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-252000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-137000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-122000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-70000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-173000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-105000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-174000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-506000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>158000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-555000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>416000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-27000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-63000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-61000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-242000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-46000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-70000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-58000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-222000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-55000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-64000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-80000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-133000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-84000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-77000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>9000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-102000</v>
+      </c>
+      <c r="E101" s="3">
         <v>148000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-76000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>31000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>19000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>158000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-123000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-105000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-41000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-40000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>21000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-76000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>95000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>45000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>22000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-38000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>38000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-28000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>16000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-78000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>8000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>5000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>38000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>23000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-47000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1431000</v>
+      </c>
+      <c r="E102" s="3">
         <v>2384000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>758000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1883000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1035000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-13000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2199000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-831000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1965000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-680000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>646000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1486000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3636000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4114000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>282000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1574000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>5091000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>453000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-152000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1392000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>489000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-485000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>399000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>770000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1137000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2246000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>577000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>757000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>719000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>375000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>107000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IBKR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IBKR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>IBKR</t>
   </si>
@@ -656,432 +656,444 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2266000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2216000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2104000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2055000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1851000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1766000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1522000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1100000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>768000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>695000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>658000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>515000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>787000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>978000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>654000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>593000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>587000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>645000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>640000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>697000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>652000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>623000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>637000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>578000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>565000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>581000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>500000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>456000</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>409000</v>
       </c>
       <c r="AF8" s="3">
         <v>409000</v>
       </c>
       <c r="AG8" s="3">
+        <v>409000</v>
+      </c>
+      <c r="AH8" s="3">
         <v>215000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>366000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1151000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1114000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1065000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1008000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>944000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>805000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>636000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>396000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>189000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>121000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>108000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>112000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>87000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>153000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>121000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>119000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>124000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>113000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>131000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>177000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>173000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>162000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>142000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>119000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>108000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>94000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>78000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>61000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>51000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>35000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>22000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1115000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1102000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1039000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1047000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>907000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>961000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>886000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>704000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>579000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>574000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>550000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>403000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>700000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>825000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>533000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>474000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>463000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>532000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>509000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>520000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>479000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>461000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>495000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>459000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>457000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>487000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>422000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>395000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>358000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>374000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>193000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>345000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1116,8 +1128,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1214,8 +1227,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1312,8 +1328,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1374,17 +1393,17 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
+      <c r="Y14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
@@ -1392,11 +1411,11 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3">
         <v>-93000</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
@@ -1410,8 +1429,11 @@
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1508,8 +1530,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1541,204 +1566,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1386000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1350000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1288000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1215000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1199000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1005000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>833000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>577000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>376000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>301000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>285000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>281000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>246000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>339000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>262000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>259000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>365000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>337000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>319000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>362000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>361000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>381000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>325000</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>282000</v>
       </c>
       <c r="AA17" s="3">
         <v>282000</v>
       </c>
       <c r="AB17" s="3">
+        <v>282000</v>
+      </c>
+      <c r="AC17" s="3">
         <v>281000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>136000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>219000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>234000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>196000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>187000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>880000</v>
+      </c>
+      <c r="E18" s="3">
         <v>866000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>816000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>840000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>652000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>761000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>689000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>523000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>392000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>394000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>373000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>234000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>541000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>639000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>392000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>334000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>222000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>308000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>321000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>335000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>291000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>242000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>312000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>296000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>283000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>300000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>364000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>237000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>175000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>213000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>28000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1773,8 +1805,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1830,147 +1863,153 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-9000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-54000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-66000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>97000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-12000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>40000</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>31000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>29000</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
       <c r="AG20" s="3">
         <v>0</v>
       </c>
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>897000</v>
+      </c>
+      <c r="E21" s="3">
         <v>883000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>832000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>857000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>668000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>777000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>704000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>537000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>406000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>409000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>386000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>246000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>553000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>652000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>403000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>345000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>232000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>318000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>322000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>288000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>232000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>346000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>317000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>282000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>276000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>347000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>371000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>274000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>210000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>219000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>35000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>189000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2067,106 +2106,112 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>880000</v>
+      </c>
+      <c r="E23" s="3">
         <v>866000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>816000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>840000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>652000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>761000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>689000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>523000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>392000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>394000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>373000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>234000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>541000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>639000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>392000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>334000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>222000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>308000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>312000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>281000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>225000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>339000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>309000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>276000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>271000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>340000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>364000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>268000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>204000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>213000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>28000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2174,97 +2219,100 @@
         <v>71000</v>
       </c>
       <c r="E24" s="3">
+        <v>71000</v>
+      </c>
+      <c r="F24" s="3">
         <v>77000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>68000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>51000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>61000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>56000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>40000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>32000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>28000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>35000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>28000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>35000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>53000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>12000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>32000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>15000</v>
-      </c>
-      <c r="T24" s="3">
-        <v>18000</v>
       </c>
       <c r="U24" s="3">
         <v>18000</v>
       </c>
       <c r="V24" s="3">
+        <v>18000</v>
+      </c>
+      <c r="W24" s="3">
         <v>20000</v>
-      </c>
-      <c r="W24" s="3">
-        <v>15000</v>
       </c>
       <c r="X24" s="3">
         <v>15000</v>
       </c>
       <c r="Y24" s="3">
+        <v>15000</v>
+      </c>
+      <c r="Z24" s="3">
         <v>19000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>18000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>13000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>21000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>23000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>21000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>17000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>18000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>7000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2361,204 +2409,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>809000</v>
+      </c>
+      <c r="E26" s="3">
         <v>795000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>739000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>772000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>601000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>700000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>633000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>483000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>360000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>366000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>338000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>206000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>506000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>586000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>380000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>302000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>207000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>290000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>294000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>261000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>210000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>324000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>290000</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>258000</v>
       </c>
       <c r="AA26" s="3">
         <v>258000</v>
       </c>
       <c r="AB26" s="3">
+        <v>258000</v>
+      </c>
+      <c r="AC26" s="3">
         <v>319000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>341000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>247000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>187000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>195000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>21000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>168000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>179000</v>
+      </c>
+      <c r="E27" s="3">
         <v>175000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>160000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>167000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>125000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>148000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>136000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>99000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>72000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>73000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>67000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>42000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>92000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>107000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>71000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>46000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>32000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>46000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>44000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>36000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>32000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>49000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>43000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>39000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>41000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>46000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>175000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>31000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>23000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>24000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>4000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2655,8 +2712,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2717,17 +2777,17 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3" t="s">
+      <c r="Y29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2735,11 +2795,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-177000</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2753,8 +2813,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2851,8 +2914,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2949,8 +3015,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3006,147 +3075,153 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>9000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>54000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>66000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-97000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>20000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>12000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-40000</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-31000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-29000</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
       <c r="AG32" s="3">
         <v>0</v>
       </c>
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>179000</v>
+      </c>
+      <c r="E33" s="3">
         <v>175000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>160000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>167000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>125000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>148000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>136000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>99000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>72000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>73000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>67000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>42000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>92000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>107000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>71000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>46000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>32000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>46000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>44000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>36000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>32000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>49000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>43000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>39000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>41000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>46000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>31000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>23000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>24000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>4000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3243,209 +3318,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>179000</v>
+      </c>
+      <c r="E35" s="3">
         <v>175000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>160000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>167000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>125000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>148000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>136000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>99000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>72000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>73000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>67000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>42000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>92000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>107000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>71000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>46000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>32000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>46000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>44000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>36000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>32000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>49000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>43000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>39000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>41000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>46000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>31000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>23000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>24000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>4000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3480,8 +3564,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3516,106 +3601,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3918000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4063000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3753000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3824000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3681000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3214000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3436000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3184000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2881000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2667000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2395000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2838000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3218000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2627000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4292000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3292000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3115000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3101000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2882000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3035000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3162000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2546000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2597000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3062000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2500000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1901000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1732000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2056000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2115000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1656000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1925000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1550000</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3712,106 +3801,112 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>57565000</v>
+      </c>
+      <c r="E43" s="3">
         <v>53516000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>46490000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>45768000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>43757000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>41541000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>42570000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>43969000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>44641000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>50612000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>58833000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>54654000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>54045000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>46129000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>40691000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>32987000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>27154000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>21740000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>32147000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>26969000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>26770000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>26746000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>27864000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>31876000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>30221000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>30565000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>30760000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>26444000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>24056000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>22387000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>20506000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>19053000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3908,74 +4003,77 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>59688000</v>
+      </c>
+      <c r="E45" s="3">
         <v>59253000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>64226000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>57720000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>59227000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>61341000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>56948000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>56733000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>54245000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>48931000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>38009000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>37525000</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3">
         <v>21204000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>15903000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>12789000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>12684000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>14272000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>9400000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>8794000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>8819000</v>
       </c>
-      <c r="X45" s="3">
-        <v>0</v>
-      </c>
       <c r="Y45" s="3">
         <v>0</v>
       </c>
@@ -4006,8 +4104,11 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4104,174 +4205,180 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>14195000</v>
+      </c>
+      <c r="E47" s="3">
         <v>14148000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>12827000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>12282000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>12925000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>12388000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>11263000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9861000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>10694000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>11290000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8965000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>10578000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>30621000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8040000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>6378000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>5848000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7092000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>6082000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8943000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7284000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>6522000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>7103000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>6692000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>6470000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>6209000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>6060000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>8146000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>7364000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>6834000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>7058000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>7777000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>8756000</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E48" s="3">
         <v>111000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>120000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>117000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>119000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>120000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>119000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>109000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>105000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>109000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>101000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>100000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>96000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>98000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>101000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>107000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>110000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>114000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>118000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>122000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>127000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>131000</v>
-      </c>
-      <c r="Y48" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z48" s="3" t="s">
         <v>8</v>
@@ -4282,8 +4389,8 @@
       <c r="AB48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC48" s="3">
-        <v>0</v>
+      <c r="AC48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD48" s="3">
         <v>0</v>
@@ -4300,8 +4407,11 @@
       <c r="AH48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4398,8 +4508,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4496,8 +4609,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4594,8 +4710,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4633,67 +4752,70 @@
         <v>0</v>
       </c>
       <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
         <v>15635000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>25069000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>27821000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>29316000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>33450000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>30187000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>17824000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>21246000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>20273000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>26575000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>23098000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>20355000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>21054000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>20268000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>20232000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>23566000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>24187000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>24710000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>24017000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>25250000</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4790,106 +4912,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>136648000</v>
+      </c>
+      <c r="E54" s="3">
         <v>132238000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>128423000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>120636000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>120593000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>119469000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>115143000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>114683000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>113386000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>114423000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>109113000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>106282000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>104331000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>103764000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>95679000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>84698000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>83965000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>75849000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>71676000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>67804000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>66034000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>63526000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>60547000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>62062000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>60303000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>59093000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>61162000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>59843000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>57597000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>56257000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>54673000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>55064000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4924,8 +5052,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4960,302 +5089,312 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>104851000</v>
+      </c>
+      <c r="E57" s="3">
         <v>102663000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>102345000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>96255000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>97090000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>95939000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>94091000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>93618000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>91691000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>91923000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>86782000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>85345000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>82082000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>81928000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>76441000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>69480000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>69360000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>63348000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>56791000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>55041000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>53763000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>51403000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>48615000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>50347000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>48660000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>47928000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>48165000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>48167000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>46777000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>44865000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>42335000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>43090000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>15693000</v>
+      </c>
+      <c r="E58" s="3">
         <v>14230000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11364000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10493000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10278000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10729000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>8958000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>9525000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10713000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11690000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11796000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>10563000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>12005000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>12079000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>9956000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>6366000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5995000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4058000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>6335000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3970000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4116000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4265000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4054000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>28000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>193000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>19000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1331000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>38000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>9000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>38000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>74000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>447000</v>
+      </c>
+      <c r="E59" s="3">
         <v>450000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>454000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>426000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>411000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>378000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>333000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>229000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>162000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>138000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>131000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>130000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>125000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>129000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>126000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>119000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>122000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>135000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>153000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>163000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>178000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>177000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>41000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>35000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>29000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>27000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>22000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>17000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>14000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>11000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>6000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5352,8 +5491,11 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5450,8 +5592,11 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5548,8 +5693,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5646,8 +5794,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5744,8 +5895,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5842,106 +5996,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>132721000</v>
+      </c>
+      <c r="E66" s="3">
         <v>128506000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>124839000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>117246000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>117435000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>116468000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>112295000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>112006000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>110862000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>111967000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>106718000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>103951000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>102181000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>101728000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>93728000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>83089000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>82427000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>74363000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>70224000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>66399000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>64654000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>62201000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>59265000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>60819000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>59120000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>57961000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>60072000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>58747000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>56548000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>55260000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>53699000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>54083000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5976,8 +6136,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6074,8 +6235,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6172,8 +6336,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6270,8 +6437,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6368,106 +6538,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2168000</v>
+      </c>
+      <c r="E72" s="3">
         <v>2016000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1852000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1703000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1546000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1432000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1294000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1168000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1079000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1017000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>953000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>896000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>864000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>781000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>683000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>621000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>583000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>558000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>520000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>484000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>456000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>431000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>390000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>354000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>323000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>290000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>251000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>260000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>236000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>220000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>203000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6564,8 +6740,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6662,8 +6841,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6760,106 +6942,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3927000</v>
+      </c>
+      <c r="E76" s="3">
         <v>3732000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3584000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3390000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3158000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3001000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2848000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2677000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2524000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2456000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2395000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2331000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2150000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2036000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1951000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1609000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1538000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1486000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1452000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1405000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1380000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1325000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1282000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1243000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1183000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1132000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1090000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1096000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1049000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>997000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>974000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>981000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6956,209 +7144,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>179000</v>
+      </c>
+      <c r="E81" s="3">
         <v>175000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>160000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>167000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>125000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>148000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>136000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>99000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>72000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>73000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>67000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>42000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>92000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>107000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>71000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>46000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>32000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>46000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>44000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>36000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>32000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>49000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>43000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>39000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>41000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>46000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>31000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>23000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>24000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>4000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7193,8 +7390,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7202,49 +7400,49 @@
         <v>17000</v>
       </c>
       <c r="E83" s="3">
+        <v>17000</v>
+      </c>
+      <c r="F83" s="3">
         <v>16000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>17000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>16000</v>
       </c>
       <c r="H83" s="3">
         <v>16000</v>
       </c>
       <c r="I83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="J83" s="3">
         <v>15000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>14000</v>
       </c>
       <c r="K83" s="3">
         <v>14000</v>
       </c>
       <c r="L83" s="3">
+        <v>14000</v>
+      </c>
+      <c r="M83" s="3">
         <v>15000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>13000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>12000</v>
       </c>
       <c r="O83" s="3">
         <v>12000</v>
       </c>
       <c r="P83" s="3">
+        <v>12000</v>
+      </c>
+      <c r="Q83" s="3">
         <v>13000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>11000</v>
       </c>
       <c r="R83" s="3">
         <v>11000</v>
       </c>
       <c r="S83" s="3">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="T83" s="3">
         <v>10000</v>
@@ -7253,7 +7451,7 @@
         <v>10000</v>
       </c>
       <c r="V83" s="3">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="W83" s="3">
         <v>7000</v>
@@ -7262,22 +7460,22 @@
         <v>7000</v>
       </c>
       <c r="Y83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="Z83" s="3">
         <v>8000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>6000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>5000</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>7000</v>
       </c>
       <c r="AC83" s="3">
         <v>7000</v>
       </c>
       <c r="AD83" s="3">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="AE83" s="3">
         <v>6000</v>
@@ -7286,13 +7484,16 @@
         <v>6000</v>
       </c>
       <c r="AG83" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AH83" s="3">
         <v>7000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7389,8 +7590,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7487,8 +7691,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7585,8 +7792,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7683,8 +7893,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7781,106 +7994,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1621000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1683000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2369000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>979000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2119000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-923000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-30000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2414000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-541000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2125000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-375000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1213000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1324000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3734000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4596000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-174000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1557000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>5203000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>488000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>133000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1442000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>603000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-408000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>632000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>931000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1201000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-2153000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>709000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>807000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>779000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>430000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>102000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7915,106 +8134,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-12000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-17000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-19000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-18000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-19000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-26000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-17000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-19000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-9000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-10000</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-12000</v>
       </c>
       <c r="U91" s="3">
         <v>-12000</v>
       </c>
       <c r="V91" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="W91" s="3">
         <v>-17000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-19000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-26000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-13000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-7000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8111,8 +8334,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8209,106 +8435,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-25000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-18000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-15000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>6000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-19000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-22000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-12000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-14000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-129000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-21000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-17000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-22000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-12000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-11000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-12000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-15000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-20000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-42000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-28000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-12000</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>-4000</v>
       </c>
       <c r="AE94" s="3">
         <v>-4000</v>
       </c>
       <c r="AF94" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-17000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8343,25 +8575,26 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-11000</v>
+        <v>-27000</v>
       </c>
       <c r="E96" s="3">
         <v>-11000</v>
       </c>
       <c r="F96" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="G96" s="3">
         <v>-10000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-11000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-10000</v>
       </c>
       <c r="I96" s="3">
         <v>-10000</v>
@@ -8370,19 +8603,19 @@
         <v>-10000</v>
       </c>
       <c r="K96" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="L96" s="3">
         <v>-11000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-9000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-10000</v>
       </c>
       <c r="N96" s="3">
         <v>-10000</v>
       </c>
       <c r="O96" s="3">
-        <v>-9000</v>
+        <v>-10000</v>
       </c>
       <c r="P96" s="3">
         <v>-9000</v>
@@ -8391,13 +8624,13 @@
         <v>-9000</v>
       </c>
       <c r="R96" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="S96" s="3">
         <v>-8000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-7000</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-8000</v>
       </c>
       <c r="U96" s="3">
         <v>-8000</v>
@@ -8406,19 +8639,19 @@
         <v>-8000</v>
       </c>
       <c r="W96" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="X96" s="3">
         <v>-7000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-8000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-7000</v>
       </c>
       <c r="AB96" s="3">
         <v>-7000</v>
@@ -8436,13 +8669,16 @@
         <v>-7000</v>
       </c>
       <c r="AG96" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8539,8 +8775,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8637,8 +8876,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8735,298 +8977,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-333000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-137000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-108000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-127000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-252000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-137000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-122000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-70000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-173000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-105000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-174000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-506000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>158000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-555000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>416000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-27000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-63000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-61000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-242000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-46000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-70000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-58000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-222000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-55000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-64000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-80000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-133000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-84000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-77000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>9000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-102000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>148000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-76000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>31000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>19000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>158000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-123000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-105000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-41000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-40000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>21000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-76000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>95000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>45000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>22000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-38000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>38000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-28000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>16000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-78000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>8000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>5000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>38000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>23000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-47000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1264000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1431000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2384000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>758000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1883000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1035000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-13000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2199000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-831000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1965000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-680000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>646000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1486000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3636000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4114000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>282000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1574000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>5091000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>453000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-152000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1392000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>489000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-485000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>399000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>770000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1137000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2246000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>577000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>757000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>719000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>375000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>107000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IBKR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IBKR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
   <si>
     <t>IBKR</t>
   </si>
@@ -656,444 +656,456 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2266000</v>
+        <v>1340000</v>
       </c>
       <c r="E8" s="3">
-        <v>2216000</v>
+        <v>1250000</v>
       </c>
       <c r="F8" s="3">
-        <v>2104000</v>
+        <v>1205000</v>
       </c>
       <c r="G8" s="3">
-        <v>2055000</v>
+        <v>1148000</v>
       </c>
       <c r="H8" s="3">
-        <v>1851000</v>
+        <v>1162000</v>
       </c>
       <c r="I8" s="3">
-        <v>1766000</v>
+        <v>1055000</v>
       </c>
       <c r="J8" s="3">
+        <v>1055000</v>
+      </c>
+      <c r="K8" s="3">
         <v>1522000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1100000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>768000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>695000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>658000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>515000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>787000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>978000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>654000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>593000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>587000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>645000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>640000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>697000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>652000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>623000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>637000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>578000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>565000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>581000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>500000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>456000</v>
-      </c>
-      <c r="AF8" s="3">
-        <v>409000</v>
       </c>
       <c r="AG8" s="3">
         <v>409000</v>
       </c>
       <c r="AH8" s="3">
+        <v>409000</v>
+      </c>
+      <c r="AI8" s="3">
         <v>215000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>366000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1151000</v>
+        <v>125000</v>
       </c>
       <c r="E9" s="3">
-        <v>1114000</v>
+        <v>125000</v>
       </c>
       <c r="F9" s="3">
-        <v>1065000</v>
+        <v>111000</v>
       </c>
       <c r="G9" s="3">
-        <v>1008000</v>
+        <v>112000</v>
       </c>
       <c r="H9" s="3">
-        <v>944000</v>
+        <v>108000</v>
       </c>
       <c r="I9" s="3">
-        <v>805000</v>
+        <v>103000</v>
       </c>
       <c r="J9" s="3">
+        <v>104000</v>
+      </c>
+      <c r="K9" s="3">
         <v>636000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>396000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>189000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>121000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>108000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>112000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>87000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>153000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>121000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>119000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>124000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>113000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>131000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>177000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>173000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>162000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>142000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>119000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>108000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>94000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>78000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>61000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>51000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>35000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>22000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1115000</v>
+        <v>1215000</v>
       </c>
       <c r="E10" s="3">
-        <v>1102000</v>
+        <v>1125000</v>
       </c>
       <c r="F10" s="3">
-        <v>1039000</v>
+        <v>1094000</v>
       </c>
       <c r="G10" s="3">
-        <v>1047000</v>
+        <v>1036000</v>
       </c>
       <c r="H10" s="3">
-        <v>907000</v>
+        <v>1054000</v>
       </c>
       <c r="I10" s="3">
-        <v>961000</v>
+        <v>952000</v>
       </c>
       <c r="J10" s="3">
+        <v>951000</v>
+      </c>
+      <c r="K10" s="3">
         <v>886000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>704000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>579000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>574000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>550000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>403000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>700000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>825000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>533000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>474000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>463000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>532000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>509000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>520000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>479000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>461000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>495000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>459000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>457000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>487000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>422000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>395000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>358000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>374000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>193000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>345000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1129,8 +1141,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1230,8 +1243,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1331,31 +1347,34 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1396,17 +1415,17 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
+      <c r="Z14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
@@ -1414,11 +1433,11 @@
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3">
         <v>-93000</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
@@ -1432,31 +1451,34 @@
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1533,8 +1555,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1567,210 +1592,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1386000</v>
+        <v>456000</v>
       </c>
       <c r="E17" s="3">
-        <v>1350000</v>
+        <v>350000</v>
       </c>
       <c r="F17" s="3">
-        <v>1288000</v>
+        <v>337000</v>
       </c>
       <c r="G17" s="3">
-        <v>1215000</v>
+        <v>323000</v>
       </c>
       <c r="H17" s="3">
-        <v>1199000</v>
+        <v>305000</v>
       </c>
       <c r="I17" s="3">
-        <v>1005000</v>
+        <v>348000</v>
       </c>
       <c r="J17" s="3">
+        <v>295000</v>
+      </c>
+      <c r="K17" s="3">
         <v>833000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>577000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>376000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>301000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>285000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>281000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>246000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>339000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>262000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>259000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>365000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>337000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>319000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>362000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>361000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>381000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>325000</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>282000</v>
       </c>
       <c r="AB17" s="3">
         <v>282000</v>
       </c>
       <c r="AC17" s="3">
+        <v>282000</v>
+      </c>
+      <c r="AD17" s="3">
         <v>281000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>136000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>219000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>234000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>196000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>187000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>880000</v>
+        <v>884000</v>
       </c>
       <c r="E18" s="3">
-        <v>866000</v>
+        <v>900000</v>
       </c>
       <c r="F18" s="3">
-        <v>816000</v>
+        <v>868000</v>
       </c>
       <c r="G18" s="3">
-        <v>840000</v>
+        <v>825000</v>
       </c>
       <c r="H18" s="3">
-        <v>652000</v>
+        <v>857000</v>
       </c>
       <c r="I18" s="3">
-        <v>761000</v>
+        <v>707000</v>
       </c>
       <c r="J18" s="3">
+        <v>760000</v>
+      </c>
+      <c r="K18" s="3">
         <v>689000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>523000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>392000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>394000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>373000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>234000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>541000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>639000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>392000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>334000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>222000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>308000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>321000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>335000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>291000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>242000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>312000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>296000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>283000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>300000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>364000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>237000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>175000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>213000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>28000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1806,31 +1838,32 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>55000</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1866,173 +1899,179 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-9000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-54000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-66000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>97000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-12000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>40000</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>31000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>29000</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
       <c r="AH20" s="3">
         <v>0</v>
       </c>
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>926000</v>
+      </c>
+      <c r="E21" s="3">
         <v>897000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>883000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>832000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>857000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>668000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>777000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>704000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>537000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>406000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>409000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>386000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>246000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>553000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>652000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>403000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>345000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>232000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>318000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>322000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>288000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>232000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>346000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>317000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>282000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>276000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>347000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>371000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>274000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>210000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>219000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>35000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>189000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2109,210 +2148,219 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>909000</v>
+      </c>
+      <c r="E23" s="3">
         <v>880000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>866000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>816000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>840000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>652000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>761000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>689000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>523000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>392000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>394000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>373000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>234000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>541000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>639000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>392000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>334000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>222000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>308000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>312000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>281000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>225000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>339000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>309000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>276000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>271000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>340000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>364000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>268000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>204000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>213000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>28000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>71000</v>
+        <v>75000</v>
       </c>
       <c r="E24" s="3">
         <v>71000</v>
       </c>
       <c r="F24" s="3">
+        <v>71000</v>
+      </c>
+      <c r="G24" s="3">
         <v>77000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>68000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>51000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>61000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>56000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>40000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>32000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>28000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>35000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>28000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>35000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>53000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>12000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>32000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>15000</v>
-      </c>
-      <c r="U24" s="3">
-        <v>18000</v>
       </c>
       <c r="V24" s="3">
         <v>18000</v>
       </c>
       <c r="W24" s="3">
+        <v>18000</v>
+      </c>
+      <c r="X24" s="3">
         <v>20000</v>
-      </c>
-      <c r="X24" s="3">
-        <v>15000</v>
       </c>
       <c r="Y24" s="3">
         <v>15000</v>
       </c>
       <c r="Z24" s="3">
+        <v>15000</v>
+      </c>
+      <c r="AA24" s="3">
         <v>19000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>18000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>13000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>21000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>23000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>21000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>17000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>18000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>7000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2412,210 +2460,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>834000</v>
+      </c>
+      <c r="E26" s="3">
         <v>809000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>795000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>739000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>772000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>601000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>700000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>633000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>483000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>360000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>366000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>338000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>206000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>506000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>586000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>380000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>302000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>207000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>290000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>294000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>261000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>210000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>324000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>290000</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>258000</v>
       </c>
       <c r="AB26" s="3">
         <v>258000</v>
       </c>
       <c r="AC26" s="3">
+        <v>258000</v>
+      </c>
+      <c r="AD26" s="3">
         <v>319000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>341000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>247000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>187000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>195000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>21000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>168000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>184000</v>
+      </c>
+      <c r="E27" s="3">
         <v>179000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>175000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>160000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>167000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>125000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>148000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>136000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>99000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>72000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>73000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>67000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>42000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>92000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>107000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>71000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>46000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>32000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>46000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>44000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>36000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>32000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>49000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>43000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>39000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>41000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>46000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>175000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>31000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>23000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>24000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>4000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2715,8 +2772,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2780,17 +2840,17 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3" t="s">
+      <c r="Z29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2798,11 +2858,11 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-177000</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -2816,8 +2876,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2917,8 +2980,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3018,31 +3084,34 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-20000</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-17000</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-55000</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -3078,150 +3147,156 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>9000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>54000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>66000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-97000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>20000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>12000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-40000</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-31000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-29000</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
       <c r="AH32" s="3">
         <v>0</v>
       </c>
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>184000</v>
+      </c>
+      <c r="E33" s="3">
         <v>179000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>175000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>160000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>167000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>125000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>148000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>136000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>99000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>72000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>73000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>67000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>42000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>92000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>107000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>71000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>46000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>32000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>46000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>44000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>36000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>32000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>49000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>43000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>39000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>41000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>46000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>31000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>23000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>24000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>4000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3321,215 +3396,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>184000</v>
+      </c>
+      <c r="E35" s="3">
         <v>179000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>175000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>160000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>167000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>125000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>148000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>136000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>99000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>72000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>73000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>67000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>42000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>92000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>107000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>71000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>46000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>32000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>46000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>44000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>36000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>32000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>49000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>43000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>39000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>41000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>46000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>31000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>23000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>24000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>4000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3565,8 +3649,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3602,132 +3687,136 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3595000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3918000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4063000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3753000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3824000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3681000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3214000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3436000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3184000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2881000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2667000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2395000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2838000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3218000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2627000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4292000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3292000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3115000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3101000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2882000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3035000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3162000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2546000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2597000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3062000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2500000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1901000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1732000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2056000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2115000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1656000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1925000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1550000</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>84957000</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>73883000</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>73401000</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>77053000</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>70002000</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>72152000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>73729000</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3804,132 +3893,138 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>57565000</v>
+        <v>58668000</v>
       </c>
       <c r="E43" s="3">
-        <v>53516000</v>
+        <v>57592000</v>
       </c>
       <c r="F43" s="3">
-        <v>46490000</v>
+        <v>53550000</v>
       </c>
       <c r="G43" s="3">
-        <v>45768000</v>
+        <v>46516000</v>
       </c>
       <c r="H43" s="3">
-        <v>43757000</v>
+        <v>45788000</v>
       </c>
       <c r="I43" s="3">
-        <v>41541000</v>
+        <v>43771000</v>
       </c>
       <c r="J43" s="3">
+        <v>41558000</v>
+      </c>
+      <c r="K43" s="3">
         <v>42570000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>43969000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>44641000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>50612000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>58833000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>54654000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>54045000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>46129000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>40691000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>32987000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>27154000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>21740000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>32147000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>26969000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>26770000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>26746000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>27864000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>31876000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>30221000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>30565000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>30760000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>26444000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>24056000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>22387000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>20506000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>19053000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4006,77 +4101,80 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>59688000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>59253000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>64226000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>57720000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>59227000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>61341000</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>56948000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>56733000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>54245000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>48931000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>38009000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>37525000</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3">
         <v>21204000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>15903000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>12789000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>12684000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>14272000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>9400000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>8794000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8819000</v>
       </c>
-      <c r="Y45" s="3">
-        <v>0</v>
-      </c>
       <c r="Z45" s="3">
         <v>0</v>
       </c>
@@ -4107,31 +4205,34 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>147220000</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>135393000</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>131014000</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>127322000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>119614000</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>119604000</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>118501000</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4208,180 +4309,186 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>14195000</v>
+        <v>241000</v>
       </c>
       <c r="E47" s="3">
-        <v>14148000</v>
+        <v>204000</v>
       </c>
       <c r="F47" s="3">
-        <v>12827000</v>
+        <v>191000</v>
       </c>
       <c r="G47" s="3">
-        <v>12282000</v>
+        <v>210000</v>
       </c>
       <c r="H47" s="3">
-        <v>12925000</v>
+        <v>201000</v>
       </c>
       <c r="I47" s="3">
-        <v>12388000</v>
+        <v>165000</v>
       </c>
       <c r="J47" s="3">
+        <v>173000</v>
+      </c>
+      <c r="K47" s="3">
         <v>11263000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9861000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>10694000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>11290000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8965000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>10578000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>30621000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>8040000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>6378000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>5848000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7092000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>6082000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>8943000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7284000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>6522000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>7103000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>6692000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>6470000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>6209000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>6060000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>8146000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>7364000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>6834000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>7058000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>7777000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>8756000</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>110000</v>
+      </c>
+      <c r="E48" s="3">
         <v>107000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>111000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
+        <v>201000</v>
+      </c>
+      <c r="H48" s="3">
+        <v>117000</v>
+      </c>
+      <c r="I48" s="3">
+        <v>119000</v>
+      </c>
+      <c r="J48" s="3">
         <v>120000</v>
       </c>
-      <c r="G48" s="3">
-        <v>117000</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="K48" s="3">
         <v>119000</v>
       </c>
-      <c r="I48" s="3">
-        <v>120000</v>
-      </c>
-      <c r="J48" s="3">
-        <v>119000</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>109000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>105000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>109000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>101000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>100000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>96000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>98000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>101000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>107000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>110000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>114000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>118000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>122000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>127000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>131000</v>
-      </c>
-      <c r="Z48" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA48" s="3" t="s">
         <v>8</v>
@@ -4392,8 +4499,8 @@
       <c r="AC48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD48" s="3">
-        <v>0</v>
+      <c r="AD48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE48" s="3">
         <v>0</v>
@@ -4410,8 +4517,11 @@
       <c r="AI48" s="3">
         <v>0</v>
       </c>
+      <c r="AJ48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4425,7 +4535,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>43000</v>
       </c>
       <c r="H49" s="3">
         <v>0</v>
@@ -4511,8 +4621,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4612,8 +4725,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4713,31 +4829,34 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>765000</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>755000</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>729000</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>402000</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>497000</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>521000</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>486000</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -4755,67 +4874,70 @@
         <v>0</v>
       </c>
       <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
         <v>15635000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>25069000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>27821000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>29316000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>33450000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>30187000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>17824000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>21246000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>20273000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>26575000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>23098000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>20355000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>21054000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>20268000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>20232000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>23566000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>24187000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>24710000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>24017000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>25250000</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4915,109 +5037,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>148526000</v>
+      </c>
+      <c r="E54" s="3">
         <v>136648000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>132238000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>128423000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>120636000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>120593000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>119469000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>115143000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>114683000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>113386000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>114423000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>109113000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>106282000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>104331000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>103764000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>95679000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>84698000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>83965000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>75849000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>71676000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>67804000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>66034000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>63526000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>60547000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>62062000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>60303000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>59093000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>61162000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>59843000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>57597000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>56257000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>54673000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>55064000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5053,8 +5181,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5090,334 +5219,344 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>104851000</v>
+        <v>114180000</v>
       </c>
       <c r="E57" s="3">
-        <v>102663000</v>
+        <v>104211000</v>
       </c>
       <c r="F57" s="3">
-        <v>102345000</v>
+        <v>101987000</v>
       </c>
       <c r="G57" s="3">
-        <v>96255000</v>
+        <v>101805000</v>
       </c>
       <c r="H57" s="3">
-        <v>97090000</v>
+        <v>96043000</v>
       </c>
       <c r="I57" s="3">
-        <v>95939000</v>
+        <v>96901000</v>
       </c>
       <c r="J57" s="3">
+        <v>95725000</v>
+      </c>
+      <c r="K57" s="3">
         <v>94091000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>93618000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>91691000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>91923000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>86782000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>85345000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>82082000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>81928000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>76441000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>69480000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>69360000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>63348000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>56791000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>55041000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>53763000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>51403000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>48615000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>50347000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>48660000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>47928000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>48165000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>48167000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>46777000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>44865000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>42335000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>43090000</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>15693000</v>
+        <v>17032000</v>
       </c>
       <c r="E58" s="3">
-        <v>14230000</v>
+        <v>16009000</v>
       </c>
       <c r="F58" s="3">
-        <v>11364000</v>
+        <v>14330000</v>
       </c>
       <c r="G58" s="3">
-        <v>10493000</v>
+        <v>11507000</v>
       </c>
       <c r="H58" s="3">
-        <v>10278000</v>
+        <v>10670000</v>
       </c>
       <c r="I58" s="3">
-        <v>10729000</v>
+        <v>10323000</v>
       </c>
       <c r="J58" s="3">
+        <v>10775000</v>
+      </c>
+      <c r="K58" s="3">
         <v>8958000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9525000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>10713000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11690000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11796000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>10563000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>12005000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>12079000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>9956000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>6366000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5995000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4058000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>6335000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3970000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4116000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4265000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4054000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>28000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>193000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>19000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1331000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>38000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>9000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>38000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>74000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>447000</v>
+        <v>675000</v>
       </c>
       <c r="E59" s="3">
-        <v>450000</v>
+        <v>621000</v>
       </c>
       <c r="F59" s="3">
-        <v>454000</v>
+        <v>628000</v>
       </c>
       <c r="G59" s="3">
-        <v>426000</v>
+        <v>400000</v>
       </c>
       <c r="H59" s="3">
-        <v>411000</v>
+        <v>152000</v>
       </c>
       <c r="I59" s="3">
-        <v>378000</v>
+        <v>126000</v>
       </c>
       <c r="J59" s="3">
+        <v>164000</v>
+      </c>
+      <c r="K59" s="3">
         <v>333000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>229000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>162000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>138000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>131000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>130000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>125000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>129000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>126000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>119000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>122000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>135000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>153000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>163000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>178000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>177000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>41000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>35000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>29000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>27000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>22000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>17000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>14000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>11000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>6000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>132214000</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>121161000</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>117264000</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>114023000</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>107153000</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>107620000</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>106901000</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5494,31 +5633,34 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>122000</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>111000</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>109000</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>109000</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>127000</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>121000</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -5595,31 +5737,34 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>185000</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>192000</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>206000</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>212000</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>189000</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>214000</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -5696,8 +5841,11 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5797,8 +5945,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5898,8 +6049,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5999,109 +6153,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>132721000</v>
+        <v>132521000</v>
       </c>
       <c r="E66" s="3">
-        <v>128506000</v>
+        <v>121464000</v>
       </c>
       <c r="F66" s="3">
-        <v>124839000</v>
+        <v>117579000</v>
       </c>
       <c r="G66" s="3">
-        <v>117246000</v>
+        <v>114356000</v>
       </c>
       <c r="H66" s="3">
-        <v>117435000</v>
+        <v>107372000</v>
       </c>
       <c r="I66" s="3">
-        <v>116468000</v>
+        <v>107936000</v>
       </c>
       <c r="J66" s="3">
+        <v>107236000</v>
+      </c>
+      <c r="K66" s="3">
         <v>112295000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>112006000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>110862000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>111967000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>106718000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>103951000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>102181000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>101728000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>93728000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>83089000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>82427000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>74363000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>70224000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>66399000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>64654000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>62201000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>59265000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>60819000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>59120000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>57961000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>60072000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>58747000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>56548000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>55260000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>53699000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>54083000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6137,8 +6297,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6238,8 +6399,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6339,8 +6503,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6440,8 +6607,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6541,109 +6711,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2325000</v>
+      </c>
+      <c r="E72" s="3">
         <v>2168000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2016000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1852000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1703000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1546000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1432000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1294000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1168000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1079000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1017000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>953000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>896000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>864000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>781000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>683000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>621000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>583000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>558000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>520000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>484000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>456000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>431000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>390000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>354000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>323000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>290000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>251000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>260000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>236000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>220000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>203000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6743,8 +6919,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6844,8 +7023,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6945,109 +7127,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4145000</v>
+      </c>
+      <c r="E76" s="3">
         <v>3927000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3732000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3584000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3390000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3158000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3001000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2848000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2677000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2524000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2456000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2395000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2331000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2150000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2036000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1951000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1609000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1538000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1486000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1452000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1405000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1380000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1325000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1282000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1243000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1183000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1132000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1090000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1096000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1049000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>997000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>974000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>981000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7147,215 +7335,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>184000</v>
+      </c>
+      <c r="E81" s="3">
         <v>179000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>175000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>160000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>167000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>125000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>148000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>136000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>99000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>72000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>73000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>67000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>42000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>92000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>107000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>71000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>46000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>32000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>46000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>44000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>36000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>32000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>49000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>43000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>39000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>41000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>46000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>31000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>23000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>24000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>4000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7391,61 +7588,62 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>17000</v>
+        <v>23000</v>
       </c>
       <c r="E83" s="3">
-        <v>17000</v>
+        <v>23000</v>
       </c>
       <c r="F83" s="3">
-        <v>16000</v>
+        <v>23000</v>
       </c>
       <c r="G83" s="3">
-        <v>17000</v>
+        <v>22000</v>
       </c>
       <c r="H83" s="3">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="I83" s="3">
-        <v>16000</v>
+        <v>21000</v>
       </c>
       <c r="J83" s="3">
+        <v>21000</v>
+      </c>
+      <c r="K83" s="3">
         <v>15000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>14000</v>
       </c>
       <c r="L83" s="3">
         <v>14000</v>
       </c>
       <c r="M83" s="3">
+        <v>14000</v>
+      </c>
+      <c r="N83" s="3">
         <v>15000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>13000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>12000</v>
       </c>
       <c r="P83" s="3">
         <v>12000</v>
       </c>
       <c r="Q83" s="3">
+        <v>12000</v>
+      </c>
+      <c r="R83" s="3">
         <v>13000</v>
-      </c>
-      <c r="R83" s="3">
-        <v>11000</v>
       </c>
       <c r="S83" s="3">
         <v>11000</v>
       </c>
       <c r="T83" s="3">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="U83" s="3">
         <v>10000</v>
@@ -7454,7 +7652,7 @@
         <v>10000</v>
       </c>
       <c r="W83" s="3">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="X83" s="3">
         <v>7000</v>
@@ -7463,22 +7661,22 @@
         <v>7000</v>
       </c>
       <c r="Z83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AA83" s="3">
         <v>8000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>6000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>5000</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>7000</v>
       </c>
       <c r="AD83" s="3">
         <v>7000</v>
       </c>
       <c r="AE83" s="3">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="AF83" s="3">
         <v>6000</v>
@@ -7487,13 +7685,16 @@
         <v>6000</v>
       </c>
       <c r="AH83" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AI83" s="3">
         <v>7000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7593,8 +7794,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7694,8 +7898,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7795,8 +8002,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7896,8 +8106,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7997,109 +8210,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3582000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1621000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1683000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2369000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>979000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2119000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-923000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-30000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2414000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-541000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2125000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-375000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1213000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1324000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3734000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4596000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-174000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1557000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>5203000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>488000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>133000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1442000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>603000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-408000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>632000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>931000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1201000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-2153000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>709000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>807000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>779000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>430000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>102000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8135,8 +8354,9 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8144,100 +8364,103 @@
         <v>-11000</v>
       </c>
       <c r="E91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-12000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-15000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-17000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-19000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-18000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-19000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-26000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-17000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-21000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-19000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-9000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-10000</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-12000</v>
       </c>
       <c r="V91" s="3">
         <v>-12000</v>
       </c>
       <c r="W91" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="X91" s="3">
         <v>-17000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-26000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-7000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8337,8 +8560,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8438,109 +8664,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-14000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-25000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-18000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-15000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>6000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-19000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-22000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-14000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-129000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-21000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-17000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-21000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-22000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-12000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-11000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-12000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-15000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-20000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-42000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-7000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-28000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-12000</v>
-      </c>
-      <c r="AE94" s="3">
-        <v>-4000</v>
       </c>
       <c r="AF94" s="3">
         <v>-4000</v>
       </c>
       <c r="AG94" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-17000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8576,49 +8808,50 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-27000</v>
+        <v>27000</v>
       </c>
       <c r="E96" s="3">
-        <v>-11000</v>
+        <v>27000</v>
       </c>
       <c r="F96" s="3">
-        <v>-11000</v>
+        <v>11000</v>
       </c>
       <c r="G96" s="3">
-        <v>-10000</v>
+        <v>11000</v>
       </c>
       <c r="H96" s="3">
-        <v>-11000</v>
+        <v>10000</v>
       </c>
       <c r="I96" s="3">
-        <v>-10000</v>
+        <v>11000</v>
       </c>
       <c r="J96" s="3">
-        <v>-10000</v>
+        <v>10000</v>
       </c>
       <c r="K96" s="3">
         <v>-10000</v>
       </c>
       <c r="L96" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="M96" s="3">
         <v>-11000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-9000</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-10000</v>
       </c>
       <c r="O96" s="3">
         <v>-10000</v>
       </c>
       <c r="P96" s="3">
-        <v>-9000</v>
+        <v>-10000</v>
       </c>
       <c r="Q96" s="3">
         <v>-9000</v>
@@ -8627,13 +8860,13 @@
         <v>-9000</v>
       </c>
       <c r="S96" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="T96" s="3">
         <v>-8000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-7000</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-8000</v>
       </c>
       <c r="V96" s="3">
         <v>-8000</v>
@@ -8642,19 +8875,19 @@
         <v>-8000</v>
       </c>
       <c r="X96" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-8000</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-7000</v>
       </c>
       <c r="AC96" s="3">
         <v>-7000</v>
@@ -8672,13 +8905,16 @@
         <v>-7000</v>
       </c>
       <c r="AH96" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8778,8 +9014,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8879,8 +9118,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8980,307 +9222,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-177000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-333000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-137000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-108000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-127000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-252000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-137000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-122000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-70000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-173000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-105000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-174000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-506000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>158000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-555000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>416000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-27000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-63000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-61000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-242000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-46000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-70000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-58000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-222000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-55000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-64000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-80000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-133000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-84000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-77000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>9000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-10000</v>
+        <v>-76000</v>
       </c>
       <c r="E101" s="3">
-        <v>-102000</v>
+        <v>31000</v>
       </c>
       <c r="F101" s="3">
-        <v>148000</v>
+        <v>19000</v>
       </c>
       <c r="G101" s="3">
+        <v>158000</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-123000</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-105000</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="K101" s="3">
+        <v>158000</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-123000</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-105000</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="O101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="P101" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>21000</v>
+      </c>
+      <c r="R101" s="3">
         <v>-76000</v>
       </c>
-      <c r="H101" s="3">
-        <v>31000</v>
-      </c>
-      <c r="I101" s="3">
-        <v>19000</v>
-      </c>
-      <c r="J101" s="3">
-        <v>158000</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-123000</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-105000</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-41000</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="S101" s="3">
+        <v>95000</v>
+      </c>
+      <c r="T101" s="3">
+        <v>45000</v>
+      </c>
+      <c r="U101" s="3">
+        <v>22000</v>
+      </c>
+      <c r="V101" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="W101" s="3">
+        <v>38000</v>
+      </c>
+      <c r="X101" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>16000</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-2000</v>
       </c>
-      <c r="O101" s="3">
-        <v>-40000</v>
-      </c>
-      <c r="P101" s="3">
-        <v>21000</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-76000</v>
-      </c>
-      <c r="R101" s="3">
-        <v>95000</v>
-      </c>
-      <c r="S101" s="3">
-        <v>45000</v>
-      </c>
-      <c r="T101" s="3">
-        <v>22000</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-38000</v>
-      </c>
-      <c r="V101" s="3">
+      <c r="AA101" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>-78000</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>8000</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AG101" s="3">
         <v>38000</v>
       </c>
-      <c r="W101" s="3">
-        <v>-28000</v>
-      </c>
-      <c r="X101" s="3">
-        <v>16000</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>-78000</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>8000</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>5000</v>
-      </c>
-      <c r="AF101" s="3">
-        <v>38000</v>
-      </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>23000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-47000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3523000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1264000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1431000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2384000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>758000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1883000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1035000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-13000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2199000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-831000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1965000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-680000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>646000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1486000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3636000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4114000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>282000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1574000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>5091000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>453000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-152000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1392000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>489000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-485000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>399000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>770000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1137000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-2246000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>577000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>757000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>719000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>375000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>107000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IBKR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IBKR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="92">
   <si>
     <t>IBKR</t>
   </si>
@@ -656,248 +656,254 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="19" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1405000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1340000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1250000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1205000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1148000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1162000</v>
-      </c>
-      <c r="I8" s="3">
-        <v>1055000</v>
       </c>
       <c r="J8" s="3">
         <v>1055000</v>
       </c>
       <c r="K8" s="3">
+        <v>1055000</v>
+      </c>
+      <c r="L8" s="3">
         <v>1522000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1100000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>768000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>695000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>658000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>515000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>787000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>978000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>654000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>593000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>587000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>645000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>640000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>697000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>652000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>623000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>637000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>578000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>565000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>581000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>500000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>456000</v>
-      </c>
-      <c r="AG8" s="3">
-        <v>409000</v>
       </c>
       <c r="AH8" s="3">
         <v>409000</v>
       </c>
       <c r="AI8" s="3">
+        <v>409000</v>
+      </c>
+      <c r="AJ8" s="3">
         <v>215000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>366000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -908,204 +914,210 @@
         <v>125000</v>
       </c>
       <c r="F9" s="3">
+        <v>125000</v>
+      </c>
+      <c r="G9" s="3">
         <v>111000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>112000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>108000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>103000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>104000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>636000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>396000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>189000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>121000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>108000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>112000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>87000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>153000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>121000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>119000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>124000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>113000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>131000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>177000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>173000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>162000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>142000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>119000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>108000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>94000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>78000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>61000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>51000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>35000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>22000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1280000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1215000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1125000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1094000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1036000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1054000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>952000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>951000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>886000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>704000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>579000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>574000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>550000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>403000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>700000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>825000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>533000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>474000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>463000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>532000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>509000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>520000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>479000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>461000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>495000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>459000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>457000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>487000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>422000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>395000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>358000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>374000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>193000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>345000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1142,8 +1154,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1246,8 +1259,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1350,8 +1366,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1376,8 +1395,8 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1418,17 +1437,17 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3" t="s">
+      <c r="AA14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
@@ -1436,11 +1455,11 @@
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF14" s="3">
         <v>-93000</v>
-      </c>
-      <c r="AF14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>8</v>
@@ -1454,13 +1473,16 @@
       <c r="AJ14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>17000</v>
+        <v>16000</v>
       </c>
       <c r="E15" s="3">
         <v>17000</v>
@@ -1469,19 +1491,19 @@
         <v>17000</v>
       </c>
       <c r="G15" s="3">
+        <v>17000</v>
+      </c>
+      <c r="H15" s="3">
         <v>16000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>17000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>16000</v>
       </c>
       <c r="J15" s="3">
         <v>16000</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1558,8 +1580,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1593,216 +1618,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>347000</v>
+      </c>
+      <c r="E17" s="3">
         <v>456000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>350000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>337000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>323000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>305000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>348000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>295000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>833000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>577000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>376000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>301000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>285000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>281000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>246000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>339000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>262000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>259000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>365000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>337000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>319000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>362000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>361000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>381000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>325000</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>282000</v>
       </c>
       <c r="AC17" s="3">
         <v>282000</v>
       </c>
       <c r="AD17" s="3">
+        <v>282000</v>
+      </c>
+      <c r="AE17" s="3">
         <v>281000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>136000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>219000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>234000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>196000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>187000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1058000</v>
+      </c>
+      <c r="E18" s="3">
         <v>884000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>900000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>868000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>825000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>857000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>707000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>760000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>689000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>523000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>392000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>394000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>373000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>234000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>541000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>639000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>392000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>334000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>222000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>308000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>321000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>335000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>291000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>242000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>312000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>296000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>283000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>300000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>364000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>237000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>175000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>213000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>28000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1839,35 +1871,36 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-25000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>20000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>9000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>17000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>55000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1000</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1902,153 +1935,159 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-9000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-54000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-66000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>97000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-12000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>40000</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>31000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>29000</v>
       </c>
-      <c r="AH20" s="3">
-        <v>0</v>
-      </c>
       <c r="AI20" s="3">
         <v>0</v>
       </c>
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1056000</v>
+      </c>
+      <c r="E21" s="3">
         <v>926000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>897000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>883000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>832000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>857000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>668000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>777000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>704000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>537000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>406000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>409000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>386000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>246000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>553000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>652000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>403000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>345000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>232000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>318000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>322000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>288000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>232000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>346000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>317000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>282000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>276000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>347000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>371000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>274000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>210000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>219000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>35000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>189000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2073,8 +2112,8 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2151,216 +2190,225 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1040000</v>
+      </c>
+      <c r="E23" s="3">
         <v>909000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>880000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>866000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>816000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>840000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>652000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>761000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>689000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>523000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>392000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>394000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>373000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>234000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>541000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>639000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>392000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>334000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>222000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>308000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>312000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>281000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>225000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>339000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>309000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>276000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>271000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>340000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>364000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>268000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>204000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>213000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>28000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E24" s="3">
         <v>75000</v>
-      </c>
-      <c r="E24" s="3">
-        <v>71000</v>
       </c>
       <c r="F24" s="3">
         <v>71000</v>
       </c>
       <c r="G24" s="3">
+        <v>71000</v>
+      </c>
+      <c r="H24" s="3">
         <v>77000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>68000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>51000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>61000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>56000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>40000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>32000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>28000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>35000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>28000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>35000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>53000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>12000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>32000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>15000</v>
-      </c>
-      <c r="V24" s="3">
-        <v>18000</v>
       </c>
       <c r="W24" s="3">
         <v>18000</v>
       </c>
       <c r="X24" s="3">
+        <v>18000</v>
+      </c>
+      <c r="Y24" s="3">
         <v>20000</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>15000</v>
       </c>
       <c r="Z24" s="3">
         <v>15000</v>
       </c>
       <c r="AA24" s="3">
+        <v>15000</v>
+      </c>
+      <c r="AB24" s="3">
         <v>19000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>18000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>13000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>21000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>23000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>21000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>17000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>18000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2463,216 +2511,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>969000</v>
+      </c>
+      <c r="E26" s="3">
         <v>834000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>809000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>795000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>739000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>772000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>601000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>700000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>633000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>483000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>360000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>366000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>338000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>206000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>506000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>586000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>380000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>302000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>207000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>290000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>294000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>261000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>210000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>324000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>290000</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>258000</v>
       </c>
       <c r="AC26" s="3">
         <v>258000</v>
       </c>
       <c r="AD26" s="3">
+        <v>258000</v>
+      </c>
+      <c r="AE26" s="3">
         <v>319000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>341000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>247000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>187000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>195000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>21000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>168000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>217000</v>
+      </c>
+      <c r="E27" s="3">
         <v>184000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>179000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>175000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>160000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>167000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>125000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>148000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>136000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>99000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>72000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>73000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>67000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>42000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>92000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>107000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>71000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>46000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>32000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>46000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>44000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>36000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>32000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>49000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>43000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>39000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>41000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>46000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>175000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>31000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>23000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>24000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2775,8 +2832,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2843,17 +2903,17 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3" t="s">
+      <c r="AA29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2861,11 +2921,11 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-177000</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -2879,8 +2939,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2983,8 +3046,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3087,35 +3153,38 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E32" s="3">
         <v>25000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-20000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-9000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-17000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-55000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1000</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -3150,153 +3219,159 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>9000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>54000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>66000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-97000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>20000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>12000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-40000</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-31000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-29000</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
       <c r="AI32" s="3">
         <v>0</v>
       </c>
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>217000</v>
+      </c>
+      <c r="E33" s="3">
         <v>184000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>179000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>175000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>160000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>167000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>125000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>148000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>136000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>99000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>72000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>73000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>67000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>42000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>92000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>107000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>71000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>46000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>32000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>46000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>44000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>36000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>32000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>49000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>43000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>39000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>41000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>46000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>31000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>23000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>24000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3399,221 +3474,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>217000</v>
+      </c>
+      <c r="E35" s="3">
         <v>184000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>179000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>175000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>160000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>167000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>125000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>148000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>136000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>99000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>72000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>73000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>67000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>42000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>92000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>107000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>71000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>46000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>32000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>46000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>44000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>36000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>32000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>49000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>43000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>39000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>41000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>46000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>31000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>23000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>24000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3650,8 +3734,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3688,139 +3773,143 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3633000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3595000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3918000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4063000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3753000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3824000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3681000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3214000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3436000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3184000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2881000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2667000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2395000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2838000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3218000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2627000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4292000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3292000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3115000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3101000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2882000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3035000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3162000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2546000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2597000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3062000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2500000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1901000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1732000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2056000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2115000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1656000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1925000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1550000</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>78314000</v>
+      </c>
+      <c r="E42" s="3">
         <v>84957000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>73883000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>73401000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>77053000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>70002000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>72152000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>73729000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3896,112 +3985,118 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>67105000</v>
+      </c>
+      <c r="E43" s="3">
         <v>58668000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>57592000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>53550000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>46516000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>45788000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>43771000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>41558000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>42570000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>43969000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>44641000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>50612000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>58833000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>54654000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>54045000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>46129000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>40691000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>32987000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>27154000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>21740000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>32147000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>26969000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>26770000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>26746000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>27864000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>31876000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>30221000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>30565000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>30760000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>26444000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>24056000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>22387000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>20506000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>19053000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4026,8 +4121,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4104,8 +4199,11 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4130,54 +4228,54 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>56948000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>56733000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>54245000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>48931000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>38009000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>37525000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3">
         <v>21204000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>15903000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>12789000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>12684000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>14272000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>9400000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8794000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>8819000</v>
       </c>
-      <c r="Z45" s="3">
-        <v>0</v>
-      </c>
       <c r="AA45" s="3">
         <v>0</v>
       </c>
@@ -4208,35 +4306,38 @@
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>149052000</v>
+      </c>
+      <c r="E46" s="3">
         <v>147220000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>135393000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>131014000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>127322000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>119614000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>119604000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>118501000</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -4312,186 +4413,192 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>235000</v>
+      </c>
+      <c r="E47" s="3">
         <v>241000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>204000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>191000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>210000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>201000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>165000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>173000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>11263000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>9861000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>10694000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>11290000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8965000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>10578000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>30621000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>8040000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>6378000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>5848000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7092000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>6082000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>8943000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>7284000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>6522000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>7103000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>6692000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>6470000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>6209000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>6060000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>8146000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>7364000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>6834000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>7058000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>7777000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>8756000</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>161000</v>
+      </c>
+      <c r="E48" s="3">
         <v>110000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>107000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>111000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>201000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>117000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>119000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>120000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>119000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>109000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>105000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>109000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>101000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>100000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>96000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>98000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>101000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>107000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>110000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>114000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>118000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>122000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>127000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>131000</v>
-      </c>
-      <c r="AA48" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB48" s="3" t="s">
         <v>8</v>
@@ -4502,8 +4609,8 @@
       <c r="AD48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE48" s="3">
-        <v>0</v>
+      <c r="AE48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF48" s="3">
         <v>0</v>
@@ -4520,13 +4627,16 @@
       <c r="AJ48" s="3">
         <v>0</v>
       </c>
+      <c r="AK48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>48000</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
@@ -4535,11 +4645,11 @@
         <v>0</v>
       </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>43000</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
@@ -4624,8 +4734,11 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4728,8 +4841,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4832,35 +4948,38 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>396000</v>
+      </c>
+      <c r="E52" s="3">
         <v>765000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>755000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>729000</v>
       </c>
-      <c r="G52" s="3">
-        <v>402000</v>
-      </c>
       <c r="H52" s="3">
+        <v>230000</v>
+      </c>
+      <c r="I52" s="3">
         <v>497000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>521000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>486000</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
@@ -4877,67 +4996,70 @@
         <v>0</v>
       </c>
       <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
         <v>15635000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>25069000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>27821000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>29316000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>33450000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>30187000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>17824000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>21246000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>20273000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>26575000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>23098000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>20355000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>21054000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>20268000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>20232000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>23566000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>24187000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>24710000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>24017000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>25250000</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5040,112 +5162,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>150142000</v>
+      </c>
+      <c r="E54" s="3">
         <v>148526000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>136648000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>132238000</v>
       </c>
-      <c r="G54" s="3">
-        <v>128423000</v>
-      </c>
       <c r="H54" s="3">
+        <v>128251000</v>
+      </c>
+      <c r="I54" s="3">
         <v>120636000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>120593000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>119469000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>115143000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>114683000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>113386000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>114423000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>109113000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>106282000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>104331000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>103764000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>95679000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>84698000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>83965000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>75849000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>71676000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>67804000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>66034000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>63526000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>60547000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>62062000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>60303000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>59093000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>61162000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>59843000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>57597000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>56257000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>54673000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>55064000</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5182,8 +5310,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5220,347 +5349,357 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>116090000</v>
+      </c>
+      <c r="E57" s="3">
         <v>114180000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>104211000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>101987000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>101805000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>96043000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>96901000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>95725000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>94091000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>93618000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>91691000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>91923000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>86782000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>85345000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>82082000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>81928000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>76441000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>69480000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>69360000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>63348000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>56791000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>55041000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>53763000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>51403000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>48615000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>50347000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>48660000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>47928000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>48165000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>48167000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>46777000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>44865000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>42335000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>43090000</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>16451000</v>
+      </c>
+      <c r="E58" s="3">
         <v>17032000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>16009000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>14330000</v>
       </c>
-      <c r="G58" s="3">
-        <v>11507000</v>
-      </c>
       <c r="H58" s="3">
+        <v>11473000</v>
+      </c>
+      <c r="I58" s="3">
         <v>10670000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10323000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10775000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>8958000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>9525000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>10713000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11690000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>11796000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>10563000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>12005000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>12079000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>9956000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>6366000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5995000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4058000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>6335000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3970000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4116000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4265000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4054000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>28000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>193000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>19000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1331000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>38000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>9000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>38000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>74000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>394000</v>
+      </c>
+      <c r="E59" s="3">
         <v>675000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>621000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>628000</v>
       </c>
-      <c r="G59" s="3">
-        <v>400000</v>
-      </c>
       <c r="H59" s="3">
+        <v>228000</v>
+      </c>
+      <c r="I59" s="3">
         <v>152000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>126000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>164000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>333000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>229000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>162000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>138000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>131000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>130000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>125000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>129000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>126000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>119000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>122000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>135000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>153000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>163000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>178000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>177000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>41000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>35000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>29000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>27000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>22000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>17000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>14000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>11000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>6000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>133246000</v>
+      </c>
+      <c r="E60" s="3">
         <v>132214000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>121161000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>117264000</v>
       </c>
-      <c r="G60" s="3">
-        <v>114023000</v>
-      </c>
       <c r="H60" s="3">
+        <v>113817000</v>
+      </c>
+      <c r="I60" s="3">
         <v>107153000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>107620000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>106901000</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -5636,35 +5775,38 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E61" s="3">
         <v>122000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>111000</v>
-      </c>
-      <c r="F61" s="3">
-        <v>109000</v>
       </c>
       <c r="G61" s="3">
         <v>109000</v>
       </c>
       <c r="H61" s="3">
+        <v>143000</v>
+      </c>
+      <c r="I61" s="3">
         <v>7000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>127000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>121000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -5740,35 +5882,38 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>195000</v>
+      </c>
+      <c r="E62" s="3">
         <v>185000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>192000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>206000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>210000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>212000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>189000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>214000</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -5844,8 +5989,11 @@
       <c r="AJ62" s="3">
         <v>0</v>
       </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5948,8 +6096,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6052,8 +6203,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6156,112 +6310,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>133545000</v>
+      </c>
+      <c r="E66" s="3">
         <v>132521000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>121464000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>117579000</v>
       </c>
-      <c r="G66" s="3">
-        <v>114356000</v>
-      </c>
       <c r="H66" s="3">
+        <v>114184000</v>
+      </c>
+      <c r="I66" s="3">
         <v>107372000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>107936000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>107236000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>112295000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>112006000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>110862000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>111967000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>106718000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>103951000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>102181000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>101728000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>93728000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>83089000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>82427000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>74363000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>70224000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>66399000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>64654000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>62201000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>59265000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>60819000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>59120000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>57961000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>60072000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>58747000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>56548000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>55260000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>53699000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>54083000</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6298,8 +6458,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6402,8 +6563,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6506,8 +6670,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6610,8 +6777,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6714,112 +6884,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2515000</v>
+      </c>
+      <c r="E72" s="3">
         <v>2325000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2168000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2016000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1852000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1703000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1546000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1432000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1294000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1168000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1079000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1017000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>953000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>896000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>864000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>781000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>683000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>621000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>583000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>558000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>520000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>484000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>456000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>431000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>390000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>354000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>323000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>290000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>251000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>260000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>236000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>220000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>203000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6922,8 +7098,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7026,8 +7205,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7130,112 +7312,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4280000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4145000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3927000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3732000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3584000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3390000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3158000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3001000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2848000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2677000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2524000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2456000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2395000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2331000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2150000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2036000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1951000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1609000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1538000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1486000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1452000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1405000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1380000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1325000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1282000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1243000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1183000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1132000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1090000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1096000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1049000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>997000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>974000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>981000</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7338,221 +7526,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>217000</v>
+      </c>
+      <c r="E81" s="3">
         <v>184000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>179000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>175000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>160000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>167000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>125000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>148000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>136000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>99000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>72000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>73000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>67000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>42000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>92000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>107000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>71000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>46000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>32000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>46000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>44000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>36000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>32000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>49000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>43000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>39000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>41000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>46000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>31000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>23000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>24000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7589,13 +7786,14 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>23000</v>
+        <v>25000</v>
       </c>
       <c r="E83" s="3">
         <v>23000</v>
@@ -7604,49 +7802,49 @@
         <v>23000</v>
       </c>
       <c r="G83" s="3">
+        <v>23000</v>
+      </c>
+      <c r="H83" s="3">
         <v>22000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>20000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>21000</v>
       </c>
       <c r="J83" s="3">
         <v>21000</v>
       </c>
       <c r="K83" s="3">
+        <v>21000</v>
+      </c>
+      <c r="L83" s="3">
         <v>15000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>14000</v>
       </c>
       <c r="M83" s="3">
         <v>14000</v>
       </c>
       <c r="N83" s="3">
+        <v>14000</v>
+      </c>
+      <c r="O83" s="3">
         <v>15000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>13000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>12000</v>
       </c>
       <c r="Q83" s="3">
         <v>12000</v>
       </c>
       <c r="R83" s="3">
+        <v>12000</v>
+      </c>
+      <c r="S83" s="3">
         <v>13000</v>
-      </c>
-      <c r="S83" s="3">
-        <v>11000</v>
       </c>
       <c r="T83" s="3">
         <v>11000</v>
       </c>
       <c r="U83" s="3">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="V83" s="3">
         <v>10000</v>
@@ -7655,7 +7853,7 @@
         <v>10000</v>
       </c>
       <c r="X83" s="3">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="Y83" s="3">
         <v>7000</v>
@@ -7664,22 +7862,22 @@
         <v>7000</v>
       </c>
       <c r="AA83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AB83" s="3">
         <v>8000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>6000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>5000</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>7000</v>
       </c>
       <c r="AE83" s="3">
         <v>7000</v>
       </c>
       <c r="AF83" s="3">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="AG83" s="3">
         <v>6000</v>
@@ -7688,13 +7886,16 @@
         <v>6000</v>
       </c>
       <c r="AI83" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7797,8 +7998,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7901,8 +8105,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8005,8 +8212,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8109,8 +8319,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8213,112 +8426,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1838000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3582000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1621000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1683000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2369000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>979000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2119000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-923000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-30000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2414000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-541000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2125000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-375000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1213000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1324000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3734000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4596000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-174000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1557000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>5203000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>488000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>133000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1442000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>603000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-408000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>632000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>931000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1201000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-2153000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>709000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>807000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>779000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>430000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>102000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8355,112 +8574,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-11000</v>
+        <v>-15000</v>
       </c>
       <c r="E91" s="3">
         <v>-11000</v>
       </c>
       <c r="F91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="G91" s="3">
         <v>-12000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-15000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-17000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-19000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-18000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-19000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-26000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-17000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-21000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-19000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-9000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-10000</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-12000</v>
       </c>
       <c r="W91" s="3">
         <v>-12000</v>
       </c>
       <c r="X91" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-17000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-19000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-7000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8563,8 +8786,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8667,112 +8893,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-35000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-14000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-25000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-18000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-15000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>6000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-19000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-22000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-129000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-17000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-21000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-22000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-12000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-11000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-12000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-15000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-20000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-42000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-7000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-28000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-12000</v>
-      </c>
-      <c r="AF94" s="3">
-        <v>-4000</v>
       </c>
       <c r="AG94" s="3">
         <v>-4000</v>
       </c>
       <c r="AH94" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-17000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8809,8 +9041,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8821,40 +9054,40 @@
         <v>27000</v>
       </c>
       <c r="F96" s="3">
-        <v>11000</v>
+        <v>27000</v>
       </c>
       <c r="G96" s="3">
         <v>11000</v>
       </c>
       <c r="H96" s="3">
+        <v>11000</v>
+      </c>
+      <c r="I96" s="3">
         <v>10000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>11000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>10000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-10000</v>
       </c>
       <c r="L96" s="3">
         <v>-10000</v>
       </c>
       <c r="M96" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="N96" s="3">
         <v>-11000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-9000</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-10000</v>
       </c>
       <c r="P96" s="3">
         <v>-10000</v>
       </c>
       <c r="Q96" s="3">
-        <v>-9000</v>
+        <v>-10000</v>
       </c>
       <c r="R96" s="3">
         <v>-9000</v>
@@ -8863,13 +9096,13 @@
         <v>-9000</v>
       </c>
       <c r="T96" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="U96" s="3">
         <v>-8000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-7000</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-8000</v>
       </c>
       <c r="W96" s="3">
         <v>-8000</v>
@@ -8878,19 +9111,19 @@
         <v>-8000</v>
       </c>
       <c r="Y96" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-7000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-8000</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-7000</v>
       </c>
       <c r="AD96" s="3">
         <v>-7000</v>
@@ -8908,13 +9141,16 @@
         <v>-7000</v>
       </c>
       <c r="AI96" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-6000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9017,8 +9253,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9121,8 +9360,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9225,316 +9467,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-186000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-177000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-333000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-137000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-108000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-127000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-252000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-137000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-122000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-70000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-173000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-105000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-174000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-506000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>158000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-555000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>416000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-27000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-63000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-61000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-242000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-46000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-70000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-58000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-222000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-55000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-64000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-80000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-133000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-84000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-77000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>9000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>148000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-76000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>31000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>19000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>158000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-123000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-105000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-41000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>158000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-123000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-105000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-41000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-40000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>21000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-76000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>95000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>45000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>22000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-38000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>38000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-28000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>16000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-78000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>8000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>5000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>38000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>23000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-47000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1422000</v>
+      </c>
+      <c r="E102" s="3">
         <v>3523000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1264000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1431000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2384000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>758000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1883000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1035000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-13000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2199000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-831000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1965000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-680000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>646000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1486000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3636000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>4114000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>282000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1574000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>5091000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>453000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-152000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1392000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>489000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-485000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>399000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>770000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1137000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2246000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>577000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>757000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>719000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>375000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>107000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IBKR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IBKR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="92">
   <si>
     <t>IBKR</t>
   </si>
@@ -656,259 +656,265 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="19" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="20" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1407000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1405000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1340000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1250000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1205000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1148000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1162000</v>
-      </c>
-      <c r="J8" s="3">
-        <v>1055000</v>
       </c>
       <c r="K8" s="3">
         <v>1055000</v>
       </c>
       <c r="L8" s="3">
+        <v>1055000</v>
+      </c>
+      <c r="M8" s="3">
         <v>1522000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1100000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>768000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>695000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>658000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>515000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>787000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>978000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>654000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>593000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>587000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>645000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>640000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>697000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>652000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>623000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>637000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>578000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>565000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>581000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>500000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>456000</v>
-      </c>
-      <c r="AH8" s="3">
-        <v>409000</v>
       </c>
       <c r="AI8" s="3">
         <v>409000</v>
       </c>
       <c r="AJ8" s="3">
+        <v>409000</v>
+      </c>
+      <c r="AK8" s="3">
         <v>215000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>366000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>125000</v>
+        <v>131000</v>
       </c>
       <c r="E9" s="3">
         <v>125000</v>
@@ -917,207 +923,213 @@
         <v>125000</v>
       </c>
       <c r="G9" s="3">
+        <v>125000</v>
+      </c>
+      <c r="H9" s="3">
         <v>111000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>112000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>108000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>103000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>104000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>636000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>396000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>189000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>121000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>108000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>112000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>87000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>153000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>121000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>119000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>124000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>113000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>131000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>177000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>173000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>162000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>142000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>119000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>108000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>94000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>78000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>61000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>51000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>35000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>22000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1276000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1280000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1215000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1125000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1094000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1036000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1054000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>952000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>951000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>886000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>704000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>579000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>574000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>550000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>403000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>700000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>825000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>533000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>474000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>463000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>532000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>509000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>520000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>479000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>461000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>495000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>459000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>457000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>487000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>422000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>395000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>358000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>374000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>193000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>345000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1155,8 +1167,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1262,8 +1275,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1369,8 +1385,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1398,8 +1417,8 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1440,17 +1459,17 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3" t="s">
+      <c r="AB14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
@@ -1458,11 +1477,11 @@
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG14" s="3">
         <v>-93000</v>
-      </c>
-      <c r="AG14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>8</v>
@@ -1476,16 +1495,19 @@
       <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E15" s="3">
         <v>16000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>17000</v>
       </c>
       <c r="F15" s="3">
         <v>17000</v>
@@ -1494,19 +1516,19 @@
         <v>17000</v>
       </c>
       <c r="H15" s="3">
+        <v>17000</v>
+      </c>
+      <c r="I15" s="3">
         <v>16000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>17000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>16000</v>
       </c>
       <c r="K15" s="3">
         <v>16000</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1583,8 +1605,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1619,222 +1644,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>372000</v>
+      </c>
+      <c r="E17" s="3">
         <v>347000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>456000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>350000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>337000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>323000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>305000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>348000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>295000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>833000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>577000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>376000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>301000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>285000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>281000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>246000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>339000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>262000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>259000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>365000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>337000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>319000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>362000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>361000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>381000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>325000</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>282000</v>
       </c>
       <c r="AD17" s="3">
         <v>282000</v>
       </c>
       <c r="AE17" s="3">
+        <v>282000</v>
+      </c>
+      <c r="AF17" s="3">
         <v>281000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>136000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>219000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>234000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>196000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>187000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1035000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1058000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>884000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>900000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>868000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>825000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>857000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>707000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>760000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>689000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>523000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>392000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>394000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>373000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>234000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>541000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>639000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>392000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>334000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>222000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>308000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>321000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>335000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>291000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>242000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>312000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>296000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>283000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>300000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>364000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>237000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>175000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>213000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>28000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1872,38 +1904,39 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E20" s="3">
         <v>18000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-25000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>20000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>9000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>17000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>55000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1000</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1938,156 +1971,162 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-54000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-66000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>97000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-12000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>40000</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
         <v>31000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>29000</v>
       </c>
-      <c r="AI20" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
       <c r="AK20" s="3">
         <v>0</v>
       </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1070000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1056000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>926000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>897000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>883000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>832000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>857000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>668000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>777000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>704000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>537000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>406000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>409000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>386000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>246000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>553000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>652000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>403000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>345000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>232000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>318000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>322000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>288000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>232000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>346000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>317000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>282000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>276000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>347000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>371000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>274000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>210000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>219000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>35000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>189000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2115,8 +2154,8 @@
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2193,222 +2232,231 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1055000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1040000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>909000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>880000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>866000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>816000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>840000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>652000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>761000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>689000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>523000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>392000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>394000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>373000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>234000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>541000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>639000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>392000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>334000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>222000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>308000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>312000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>281000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>225000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>339000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>309000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>276000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>271000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>340000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>364000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>268000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>204000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>213000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>28000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E24" s="3">
         <v>71000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>75000</v>
-      </c>
-      <c r="F24" s="3">
-        <v>71000</v>
       </c>
       <c r="G24" s="3">
         <v>71000</v>
       </c>
       <c r="H24" s="3">
+        <v>71000</v>
+      </c>
+      <c r="I24" s="3">
         <v>77000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>68000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>51000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>61000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>56000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>40000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>32000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>28000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>35000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>28000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>35000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>53000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>12000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>32000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>15000</v>
-      </c>
-      <c r="W24" s="3">
-        <v>18000</v>
       </c>
       <c r="X24" s="3">
         <v>18000</v>
       </c>
       <c r="Y24" s="3">
+        <v>18000</v>
+      </c>
+      <c r="Z24" s="3">
         <v>20000</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>15000</v>
       </c>
       <c r="AA24" s="3">
         <v>15000</v>
       </c>
       <c r="AB24" s="3">
+        <v>15000</v>
+      </c>
+      <c r="AC24" s="3">
         <v>19000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>18000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>13000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>21000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>23000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>21000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>17000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>18000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>7000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2514,222 +2562,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>964000</v>
+      </c>
+      <c r="E26" s="3">
         <v>969000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>834000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>809000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>795000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>739000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>772000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>601000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>700000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>633000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>483000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>360000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>366000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>338000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>206000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>506000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>586000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>380000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>302000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>207000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>290000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>294000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>261000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>210000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>324000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>290000</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>258000</v>
       </c>
       <c r="AD26" s="3">
         <v>258000</v>
       </c>
       <c r="AE26" s="3">
+        <v>258000</v>
+      </c>
+      <c r="AF26" s="3">
         <v>319000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>341000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>247000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>187000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>195000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>21000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>168000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>213000</v>
+      </c>
+      <c r="E27" s="3">
         <v>217000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>184000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>179000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>175000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>160000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>167000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>125000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>148000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>136000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>99000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>72000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>73000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>67000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>42000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>92000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>107000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>71000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>46000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>32000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>46000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>44000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>36000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>32000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>49000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>43000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>39000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>41000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>46000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>175000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>31000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>23000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>24000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>4000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2835,8 +2892,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2906,17 +2966,17 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3" t="s">
+      <c r="AB29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2924,11 +2984,11 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-177000</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -2942,8 +3002,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3049,8 +3112,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3156,38 +3222,41 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-18000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>25000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-20000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-9000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-17000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-55000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1000</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -3222,156 +3291,162 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>9000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>54000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>66000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-97000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>3000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>20000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>12000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-40000</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-31000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-29000</v>
       </c>
-      <c r="AI32" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
       <c r="AK32" s="3">
         <v>0</v>
       </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>213000</v>
+      </c>
+      <c r="E33" s="3">
         <v>217000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>184000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>179000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>175000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>160000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>167000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>125000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>148000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>136000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>99000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>72000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>73000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>67000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>42000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>92000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>107000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>71000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>46000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>32000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>46000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>44000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>36000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>32000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>49000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>43000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>39000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>41000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>46000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>31000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>23000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>24000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>4000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3477,227 +3552,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>213000</v>
+      </c>
+      <c r="E35" s="3">
         <v>217000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>184000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>179000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>175000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>160000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>167000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>125000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>148000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>136000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>99000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>72000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>73000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>67000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>42000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>92000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>107000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>71000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>46000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>32000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>46000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>44000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>36000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>32000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>49000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>43000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>39000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>41000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>46000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>31000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>23000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>24000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>4000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3735,8 +3819,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3774,145 +3859,149 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3500000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3633000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3595000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3918000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4063000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3753000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3824000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3681000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3214000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3436000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3184000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2881000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2667000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2395000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2838000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3218000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2627000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4292000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3292000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3115000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3101000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2882000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3035000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3162000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2546000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2597000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3062000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2500000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1901000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1732000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2056000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2115000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1656000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1925000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1550000</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>86194000</v>
+      </c>
+      <c r="E42" s="3">
         <v>78314000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>84957000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>73883000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>73401000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>77053000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>70002000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>72152000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>73729000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3988,115 +4077,121 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>66830000</v>
+      </c>
+      <c r="E43" s="3">
         <v>67105000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>58668000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>57592000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>53550000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>46516000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>45788000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>43771000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>41558000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>42570000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>43969000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>44641000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>50612000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>58833000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>54654000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>54045000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>46129000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>40691000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>32987000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>27154000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>21740000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>32147000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>26969000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>26770000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>26746000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>27864000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>31876000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>30221000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>30565000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>30760000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>26444000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>24056000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>22387000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>20506000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>19053000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4124,8 +4219,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4202,8 +4297,11 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4231,54 +4329,54 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>56948000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>56733000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>54245000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>48931000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>38009000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>37525000</v>
       </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
       <c r="S45" s="3">
+        <v>0</v>
+      </c>
+      <c r="T45" s="3">
         <v>21204000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>15903000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>12789000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>12684000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>14272000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>9400000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>8794000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>8819000</v>
       </c>
-      <c r="AA45" s="3">
-        <v>0</v>
-      </c>
       <c r="AB45" s="3">
         <v>0</v>
       </c>
@@ -4309,38 +4407,41 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>156524000</v>
+      </c>
+      <c r="E46" s="3">
         <v>149052000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>147220000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>135393000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>131014000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>127322000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>119614000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>119604000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>118501000</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -4416,192 +4517,198 @@
       <c r="AK46" s="3">
         <v>0</v>
       </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>243000</v>
+      </c>
+      <c r="E47" s="3">
         <v>235000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>241000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>204000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>191000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>210000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>201000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>165000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>173000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>11263000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>9861000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>10694000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>11290000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8965000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>10578000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>30621000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>8040000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>6378000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>5848000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7092000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>6082000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>8943000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>7284000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>6522000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>7103000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>6692000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>6470000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>6209000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>6060000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>8146000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>7364000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>6834000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>7058000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>7777000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>8756000</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E48" s="3">
         <v>161000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>110000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>107000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>111000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>201000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>117000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>119000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>120000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>119000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>109000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>105000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>109000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>101000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>100000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>96000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>98000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>101000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>107000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>110000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>114000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>118000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>122000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>127000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>131000</v>
-      </c>
-      <c r="AB48" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC48" s="3" t="s">
         <v>8</v>
@@ -4612,8 +4719,8 @@
       <c r="AE48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF48" s="3">
-        <v>0</v>
+      <c r="AF48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG48" s="3">
         <v>0</v>
@@ -4630,17 +4737,20 @@
       <c r="AK48" s="3">
         <v>0</v>
       </c>
+      <c r="AL48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
         <v>48000</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
       <c r="F49" s="3">
         <v>0</v>
       </c>
@@ -4648,11 +4758,11 @@
         <v>0</v>
       </c>
       <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
         <v>43000</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
@@ -4737,8 +4847,11 @@
       <c r="AK49" s="3">
         <v>0</v>
       </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4844,8 +4957,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4951,38 +5067,41 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>604000</v>
+      </c>
+      <c r="E52" s="3">
         <v>396000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>765000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>755000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>729000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>230000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>497000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>521000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>486000</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
@@ -4999,67 +5118,70 @@
         <v>0</v>
       </c>
       <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
         <v>15635000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>25069000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>27821000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>29316000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>33450000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>30187000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>17824000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>21246000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>20273000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>26575000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>23098000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>20355000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>21054000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>20268000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>20232000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>23566000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>24187000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>24710000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>24017000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>25250000</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5165,115 +5287,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>157670000</v>
+      </c>
+      <c r="E54" s="3">
         <v>150142000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>148526000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>136648000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>132238000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>128251000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>120636000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>120593000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>119469000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>115143000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>114683000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>113386000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>114423000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>109113000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>106282000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>104331000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>103764000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>95679000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>84698000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>83965000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>75849000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>71676000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>67804000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>66034000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>63526000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>60547000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>62062000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>60303000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>59093000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>61162000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>59843000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>57597000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>56257000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>54673000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>55064000</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5311,8 +5439,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5350,359 +5479,369 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>122134000</v>
+      </c>
+      <c r="E57" s="3">
         <v>116090000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>114180000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>104211000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>101987000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>101805000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>96043000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>96901000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>95725000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>94091000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>93618000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>91691000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>91923000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>86782000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>85345000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>82082000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>81928000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>76441000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>69480000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>69360000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>63348000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>56791000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>55041000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>53763000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>51403000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>48615000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>50347000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>48660000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>47928000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>48165000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>48167000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>46777000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>44865000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>42335000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>43090000</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>17047000</v>
+      </c>
+      <c r="E58" s="3">
         <v>16451000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>17032000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>16009000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>14330000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11473000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10670000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10323000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10775000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>8958000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>9525000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>10713000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>11690000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>11796000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>10563000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>12005000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>12079000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>9956000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>6366000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5995000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4058000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>6335000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3970000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4116000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4265000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>4054000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>28000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>193000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>19000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1331000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>38000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>9000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>38000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>74000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>414000</v>
+      </c>
+      <c r="E59" s="3">
         <v>394000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>675000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>621000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>628000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>228000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>152000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>126000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>164000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>333000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>229000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>162000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>138000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>131000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>130000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>125000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>129000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>126000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>119000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>122000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>135000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>153000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>163000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>178000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>177000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>41000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>35000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>29000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>27000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>22000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>17000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>14000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>11000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>6000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>139892000</v>
+      </c>
+      <c r="E60" s="3">
         <v>133246000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>132214000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>121161000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>117264000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>113817000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>107153000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>107620000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>106901000</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5778,38 +5917,41 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E61" s="3">
         <v>91000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>122000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>111000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>109000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>143000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>127000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>121000</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5885,8 +6027,11 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5894,29 +6039,29 @@
         <v>195000</v>
       </c>
       <c r="E62" s="3">
+        <v>195000</v>
+      </c>
+      <c r="F62" s="3">
         <v>185000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>192000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>206000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>210000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>212000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>189000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>214000</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -5992,8 +6137,11 @@
       <c r="AK62" s="3">
         <v>0</v>
       </c>
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6099,8 +6247,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6206,8 +6357,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6313,115 +6467,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>140187000</v>
+      </c>
+      <c r="E66" s="3">
         <v>133545000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>132521000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>121464000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>117579000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>114184000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>107372000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>107936000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>107236000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>112295000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>112006000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>110862000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>111967000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>106718000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>103951000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>102181000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>101728000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>93728000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>83089000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>82427000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>74363000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>70224000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>66399000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>64654000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>62201000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>59265000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>60819000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>59120000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>57961000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>60072000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>58747000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>56548000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>55260000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>53699000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>54083000</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6459,8 +6619,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6566,8 +6727,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6673,8 +6837,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6780,8 +6947,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6887,115 +7057,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2701000</v>
+      </c>
+      <c r="E72" s="3">
         <v>2515000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2325000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2168000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2016000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1852000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1703000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1546000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1432000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1294000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1168000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1079000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1017000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>953000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>896000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>864000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>781000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>683000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>621000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>583000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>558000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>520000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>484000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>456000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>431000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>390000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>354000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>323000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>290000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>251000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>260000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>236000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>220000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>203000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7101,8 +7277,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7208,8 +7387,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7315,115 +7497,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4502000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4280000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4145000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3927000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3732000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3584000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3390000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3158000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3001000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2848000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2677000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2524000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2456000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2395000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2331000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2150000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2036000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1951000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1609000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1538000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1486000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1452000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1405000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1380000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1325000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1282000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1243000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1183000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1132000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1090000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1096000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1049000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>997000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>974000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>981000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7529,227 +7717,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>213000</v>
+      </c>
+      <c r="E81" s="3">
         <v>217000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>184000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>179000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>175000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>160000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>167000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>125000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>148000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>136000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>99000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>72000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>73000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>67000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>42000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>92000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>107000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>71000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>46000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>32000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>46000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>44000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>36000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>32000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>49000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>43000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>39000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>41000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>46000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>31000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>23000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>24000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>4000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7787,16 +7984,17 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E83" s="3">
         <v>25000</v>
-      </c>
-      <c r="E83" s="3">
-        <v>23000</v>
       </c>
       <c r="F83" s="3">
         <v>23000</v>
@@ -7805,49 +8003,49 @@
         <v>23000</v>
       </c>
       <c r="H83" s="3">
+        <v>23000</v>
+      </c>
+      <c r="I83" s="3">
         <v>22000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>20000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>21000</v>
       </c>
       <c r="K83" s="3">
         <v>21000</v>
       </c>
       <c r="L83" s="3">
+        <v>21000</v>
+      </c>
+      <c r="M83" s="3">
         <v>15000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>14000</v>
       </c>
       <c r="N83" s="3">
         <v>14000</v>
       </c>
       <c r="O83" s="3">
+        <v>14000</v>
+      </c>
+      <c r="P83" s="3">
         <v>15000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>13000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>12000</v>
       </c>
       <c r="R83" s="3">
         <v>12000</v>
       </c>
       <c r="S83" s="3">
+        <v>12000</v>
+      </c>
+      <c r="T83" s="3">
         <v>13000</v>
-      </c>
-      <c r="T83" s="3">
-        <v>11000</v>
       </c>
       <c r="U83" s="3">
         <v>11000</v>
       </c>
       <c r="V83" s="3">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="W83" s="3">
         <v>10000</v>
@@ -7856,7 +8054,7 @@
         <v>10000</v>
       </c>
       <c r="Y83" s="3">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="Z83" s="3">
         <v>7000</v>
@@ -7865,22 +8063,22 @@
         <v>7000</v>
       </c>
       <c r="AB83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AC83" s="3">
         <v>8000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>6000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>5000</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>7000</v>
       </c>
       <c r="AF83" s="3">
         <v>7000</v>
       </c>
       <c r="AG83" s="3">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="AH83" s="3">
         <v>6000</v>
@@ -7889,13 +8087,16 @@
         <v>6000</v>
       </c>
       <c r="AJ83" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AK83" s="3">
         <v>7000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8001,8 +8202,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8108,8 +8312,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8215,8 +8422,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8322,8 +8532,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8429,115 +8642,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2584000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1838000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3582000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1621000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1683000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2369000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>979000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2119000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-923000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-30000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2414000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-541000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2125000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-375000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1213000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1324000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3734000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4596000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-174000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1557000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>5203000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>488000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>133000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1442000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>603000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-408000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>632000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>931000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1201000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-2153000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>709000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>807000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>779000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>430000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>102000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8575,115 +8794,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-15000</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-11000</v>
       </c>
       <c r="F91" s="3">
         <v>-11000</v>
       </c>
       <c r="G91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="H91" s="3">
         <v>-12000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-15000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-17000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-19000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-18000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-19000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-17000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-21000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-19000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-9000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-10000</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-12000</v>
       </c>
       <c r="X91" s="3">
         <v>-12000</v>
       </c>
       <c r="Y91" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-17000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-7000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8789,8 +9012,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8896,115 +9122,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E94" s="3">
         <v>18000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-35000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-14000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-25000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-18000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-15000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>6000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-19000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-22000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-12000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-14000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-129000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-21000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-17000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-21000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-22000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-12000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-11000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-15000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-20000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-42000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-7000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-28000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-12000</v>
-      </c>
-      <c r="AG94" s="3">
-        <v>-4000</v>
       </c>
       <c r="AH94" s="3">
         <v>-4000</v>
       </c>
       <c r="AI94" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-6000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-17000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9042,8 +9274,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9057,40 +9290,40 @@
         <v>27000</v>
       </c>
       <c r="G96" s="3">
-        <v>11000</v>
+        <v>27000</v>
       </c>
       <c r="H96" s="3">
         <v>11000</v>
       </c>
       <c r="I96" s="3">
+        <v>11000</v>
+      </c>
+      <c r="J96" s="3">
         <v>10000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>11000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>10000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-10000</v>
       </c>
       <c r="M96" s="3">
         <v>-10000</v>
       </c>
       <c r="N96" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="O96" s="3">
         <v>-11000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-9000</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-10000</v>
       </c>
       <c r="Q96" s="3">
         <v>-10000</v>
       </c>
       <c r="R96" s="3">
-        <v>-9000</v>
+        <v>-10000</v>
       </c>
       <c r="S96" s="3">
         <v>-9000</v>
@@ -9099,13 +9332,13 @@
         <v>-9000</v>
       </c>
       <c r="U96" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="V96" s="3">
         <v>-8000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-7000</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-8000</v>
       </c>
       <c r="X96" s="3">
         <v>-8000</v>
@@ -9114,19 +9347,19 @@
         <v>-8000</v>
       </c>
       <c r="Z96" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-7000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-8000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-7000</v>
       </c>
       <c r="AE96" s="3">
         <v>-7000</v>
@@ -9144,13 +9377,16 @@
         <v>-7000</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-6000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9256,8 +9492,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9363,8 +9602,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9470,325 +9712,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-225000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-186000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-177000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-333000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-137000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-108000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-127000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-252000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-137000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-122000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-70000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-173000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-105000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-174000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-506000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>158000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-555000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>416000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-27000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-63000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-61000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-242000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-46000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-70000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-58000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-222000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-55000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-64000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-80000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-133000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-84000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-77000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>9000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-102000</v>
+      </c>
+      <c r="E101" s="3">
         <v>148000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-76000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>31000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>19000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>158000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-123000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-105000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-41000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>158000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-123000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-105000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-41000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-40000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>21000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-76000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>95000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>45000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>22000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-38000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>38000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-28000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>16000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-78000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>8000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>5000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>38000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>23000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-47000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2440000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1422000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3523000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1264000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1431000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2384000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>758000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1883000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1035000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2199000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-831000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1965000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-680000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>646000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1486000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3636000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4114000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>282000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1574000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>5091000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>453000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-152000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1392000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>489000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-485000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>399000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>770000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1137000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2246000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>577000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>757000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>719000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>375000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>107000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IBKR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IBKR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
   <si>
     <t>IBKR</t>
   </si>
@@ -656,268 +656,274 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="20" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="21" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1485000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1407000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1405000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1340000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1250000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1205000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1148000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1162000</v>
-      </c>
-      <c r="K8" s="3">
-        <v>1055000</v>
       </c>
       <c r="L8" s="3">
         <v>1055000</v>
       </c>
       <c r="M8" s="3">
+        <v>1055000</v>
+      </c>
+      <c r="N8" s="3">
         <v>1522000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1100000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>768000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>695000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>658000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>515000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>787000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>978000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>654000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>593000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>587000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>645000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>640000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>697000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>652000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>623000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>637000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>578000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>565000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>581000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>500000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>456000</v>
-      </c>
-      <c r="AI8" s="3">
-        <v>409000</v>
       </c>
       <c r="AJ8" s="3">
         <v>409000</v>
       </c>
       <c r="AK8" s="3">
+        <v>409000</v>
+      </c>
+      <c r="AL8" s="3">
         <v>215000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>366000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>127000</v>
+      </c>
+      <c r="E9" s="3">
         <v>131000</v>
-      </c>
-      <c r="E9" s="3">
-        <v>125000</v>
       </c>
       <c r="F9" s="3">
         <v>125000</v>
@@ -926,210 +932,216 @@
         <v>125000</v>
       </c>
       <c r="H9" s="3">
+        <v>125000</v>
+      </c>
+      <c r="I9" s="3">
         <v>111000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>112000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>108000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>103000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>104000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>636000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>396000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>189000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>121000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>108000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>112000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>87000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>153000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>121000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>119000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>124000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>113000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>131000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>177000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>173000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>162000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>142000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>119000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>108000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>94000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>78000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>61000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>51000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>35000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>22000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1358000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1276000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1280000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1215000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1125000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1094000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1036000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1054000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>952000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>951000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>886000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>704000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>579000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>574000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>550000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>403000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>700000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>825000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>533000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>474000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>463000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>532000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>509000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>520000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>479000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>461000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>495000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>459000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>457000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>487000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>422000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>395000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>358000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>374000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>193000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>345000</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1168,8 +1180,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1278,8 +1291,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1388,8 +1404,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1420,8 +1439,8 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1462,17 +1481,17 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3" t="s">
+      <c r="AC14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
@@ -1480,11 +1499,11 @@
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3">
         <v>-93000</v>
-      </c>
-      <c r="AH14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI14" s="3" t="s">
         <v>8</v>
@@ -1498,8 +1517,11 @@
       <c r="AL14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1507,10 +1529,10 @@
         <v>15000</v>
       </c>
       <c r="E15" s="3">
+        <v>15000</v>
+      </c>
+      <c r="F15" s="3">
         <v>16000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>17000</v>
       </c>
       <c r="G15" s="3">
         <v>17000</v>
@@ -1519,19 +1541,19 @@
         <v>17000</v>
       </c>
       <c r="I15" s="3">
+        <v>17000</v>
+      </c>
+      <c r="J15" s="3">
         <v>16000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>17000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>16000</v>
       </c>
       <c r="L15" s="3">
         <v>16000</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1608,8 +1630,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1645,228 +1670,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>376000</v>
+      </c>
+      <c r="E17" s="3">
         <v>372000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>347000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>456000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>350000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>337000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>323000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>305000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>348000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>295000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>833000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>577000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>376000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>301000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>285000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>281000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>246000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>339000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>262000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>259000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>365000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>337000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>319000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>362000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>361000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>381000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>325000</v>
-      </c>
-      <c r="AD17" s="3">
-        <v>282000</v>
       </c>
       <c r="AE17" s="3">
         <v>282000</v>
       </c>
       <c r="AF17" s="3">
+        <v>282000</v>
+      </c>
+      <c r="AG17" s="3">
         <v>281000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>136000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>219000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>234000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>196000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>187000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1109000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1035000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1058000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>884000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>900000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>868000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>825000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>857000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>707000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>760000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>689000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>523000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>392000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>394000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>373000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>234000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>541000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>639000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>392000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>334000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>222000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>308000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>321000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>335000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>291000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>242000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>312000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>296000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>283000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>300000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>364000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>237000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>175000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>213000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>28000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1905,41 +1937,42 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-20000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>18000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-25000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>20000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>9000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>17000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>55000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1000</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1974,159 +2007,165 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-54000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-66000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>97000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-12000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>40000</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
       <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
         <v>31000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>29000</v>
       </c>
-      <c r="AJ20" s="3">
-        <v>0</v>
-      </c>
       <c r="AK20" s="3">
         <v>0</v>
       </c>
       <c r="AL20" s="3">
         <v>0</v>
       </c>
+      <c r="AM20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1119000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1070000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1056000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>926000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>897000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>883000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>832000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>857000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>668000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>777000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>704000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>537000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>406000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>409000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>386000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>246000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>553000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>652000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>403000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>345000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>232000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>318000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>322000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>288000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>232000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>346000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>317000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>282000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>276000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>347000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>371000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>274000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>210000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>219000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>35000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>189000</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2157,8 +2196,8 @@
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2235,228 +2274,237 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1104000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1055000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1040000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>909000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>880000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>866000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>816000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>840000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>652000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>761000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>689000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>523000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>392000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>394000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>373000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>234000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>541000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>639000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>392000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>334000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>222000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>308000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>312000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>281000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>225000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>339000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>309000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>276000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>271000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>340000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>364000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>268000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>204000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>213000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>28000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E24" s="3">
         <v>91000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>71000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>75000</v>
-      </c>
-      <c r="G24" s="3">
-        <v>71000</v>
       </c>
       <c r="H24" s="3">
         <v>71000</v>
       </c>
       <c r="I24" s="3">
+        <v>71000</v>
+      </c>
+      <c r="J24" s="3">
         <v>77000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>68000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>51000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>61000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>56000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>40000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>32000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>28000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>35000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>28000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>35000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>53000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>12000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>32000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>15000</v>
-      </c>
-      <c r="X24" s="3">
-        <v>18000</v>
       </c>
       <c r="Y24" s="3">
         <v>18000</v>
       </c>
       <c r="Z24" s="3">
+        <v>18000</v>
+      </c>
+      <c r="AA24" s="3">
         <v>20000</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>15000</v>
       </c>
       <c r="AB24" s="3">
         <v>15000</v>
       </c>
       <c r="AC24" s="3">
+        <v>15000</v>
+      </c>
+      <c r="AD24" s="3">
         <v>19000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>18000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>13000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>21000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>23000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>21000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>17000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>18000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>7000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2565,228 +2613,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1006000</v>
+      </c>
+      <c r="E26" s="3">
         <v>964000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>969000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>834000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>809000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>795000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>739000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>772000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>601000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>700000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>633000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>483000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>360000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>366000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>338000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>206000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>506000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>586000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>380000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>302000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>207000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>290000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>294000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>261000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>210000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>324000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>290000</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>258000</v>
       </c>
       <c r="AE26" s="3">
         <v>258000</v>
       </c>
       <c r="AF26" s="3">
+        <v>258000</v>
+      </c>
+      <c r="AG26" s="3">
         <v>319000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>341000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>247000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>187000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>195000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>21000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>168000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>224000</v>
+      </c>
+      <c r="E27" s="3">
         <v>213000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>217000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>184000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>179000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>175000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>160000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>167000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>125000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>148000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>136000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>99000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>72000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>73000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>67000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>42000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>92000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>107000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>71000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>46000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>32000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>46000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>44000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>36000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>32000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>49000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>43000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>39000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>41000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>46000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>175000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>31000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>23000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>24000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>4000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2895,8 +2952,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2969,17 +3029,17 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3" t="s">
+      <c r="AC29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2987,11 +3047,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-177000</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3005,8 +3065,11 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3115,8 +3178,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3225,41 +3291,44 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E32" s="3">
         <v>20000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-18000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>25000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-20000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-9000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-17000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-55000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1000</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -3294,159 +3363,165 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>9000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>54000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>66000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-97000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>3000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>20000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>12000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-40000</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
       <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-31000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-29000</v>
       </c>
-      <c r="AJ32" s="3">
-        <v>0</v>
-      </c>
       <c r="AK32" s="3">
         <v>0</v>
       </c>
       <c r="AL32" s="3">
         <v>0</v>
       </c>
+      <c r="AM32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>224000</v>
+      </c>
+      <c r="E33" s="3">
         <v>213000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>217000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>184000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>179000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>175000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>160000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>167000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>125000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>148000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>136000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>99000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>72000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>73000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>67000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>42000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>92000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>107000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>71000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>46000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>32000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>46000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>44000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>36000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>32000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>49000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>43000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>39000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>41000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>46000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>31000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>23000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>24000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>4000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3555,233 +3630,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>224000</v>
+      </c>
+      <c r="E35" s="3">
         <v>213000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>217000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>184000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>179000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>175000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>160000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>167000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>125000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>148000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>136000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>99000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>72000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>73000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>67000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>42000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>92000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>107000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>71000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>46000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>32000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>46000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>44000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>36000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>32000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>49000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>43000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>39000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>41000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>46000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>31000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>23000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>24000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>4000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3820,8 +3904,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3860,151 +3945,155 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4688000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3500000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3633000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3595000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3918000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4063000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3753000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3824000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3681000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3214000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3436000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3184000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2881000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2667000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2395000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2838000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3218000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2627000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4292000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3292000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3115000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3101000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2882000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3035000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3162000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2546000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2597000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3062000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2500000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1901000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1732000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2056000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2115000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1656000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1925000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1550000</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>105559000</v>
+      </c>
+      <c r="E42" s="3">
         <v>86194000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>78314000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>84957000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>73883000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>73401000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>77053000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>70002000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>72152000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>73729000</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -4080,118 +4169,124 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>69904000</v>
+      </c>
+      <c r="E43" s="3">
         <v>66830000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>67105000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>58668000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>57592000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>53550000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>46516000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>45788000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>43771000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>41558000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>42570000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>43969000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>44641000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>50612000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>58833000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>54654000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>54045000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>46129000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>40691000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>32987000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>27154000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>21740000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>32147000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>26969000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>26770000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>26746000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>27864000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>31876000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>30221000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>30565000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>30760000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>26444000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>24056000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>22387000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>20506000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>19053000</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4222,8 +4317,8 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4300,8 +4395,11 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4332,54 +4430,54 @@
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>56948000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>56733000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>54245000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>48931000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>38009000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>37525000</v>
       </c>
-      <c r="S45" s="3">
-        <v>0</v>
-      </c>
       <c r="T45" s="3">
+        <v>0</v>
+      </c>
+      <c r="U45" s="3">
         <v>21204000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>15903000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>12789000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>12684000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>14272000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>9400000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>8794000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>8819000</v>
       </c>
-      <c r="AB45" s="3">
-        <v>0</v>
-      </c>
       <c r="AC45" s="3">
         <v>0</v>
       </c>
@@ -4410,41 +4508,44 @@
       <c r="AL45" s="3">
         <v>0</v>
       </c>
+      <c r="AM45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>180151000</v>
+      </c>
+      <c r="E46" s="3">
         <v>156524000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>149052000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>147220000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>135393000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>131014000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>127322000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>119614000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>119604000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>118501000</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -4520,118 +4621,124 @@
       <c r="AL46" s="3">
         <v>0</v>
       </c>
+      <c r="AM46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>283000</v>
+      </c>
+      <c r="E47" s="3">
         <v>243000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>235000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>241000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>204000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>191000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>210000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>201000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>165000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>173000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>11263000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>9861000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>10694000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>11290000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>8965000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>10578000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>30621000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8040000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>6378000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>5848000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7092000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>6082000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>8943000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>7284000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>6522000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>7103000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>6692000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>6470000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>6209000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>6060000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>8146000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>7364000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>6834000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>7058000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>7777000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>8756000</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4639,79 +4746,79 @@
         <v>107000</v>
       </c>
       <c r="E48" s="3">
+        <v>107000</v>
+      </c>
+      <c r="F48" s="3">
         <v>161000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>110000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>107000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>111000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>201000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>117000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>119000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>120000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>119000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>109000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>105000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>109000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>101000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>100000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>96000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>98000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>101000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>107000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>110000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>114000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>118000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>122000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>127000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>131000</v>
-      </c>
-      <c r="AC48" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD48" s="3" t="s">
         <v>8</v>
@@ -4722,8 +4829,8 @@
       <c r="AF48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG48" s="3">
-        <v>0</v>
+      <c r="AG48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH48" s="3">
         <v>0</v>
@@ -4740,8 +4847,11 @@
       <c r="AL48" s="3">
         <v>0</v>
       </c>
+      <c r="AM48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4749,11 +4859,11 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>48000</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
         <v>0</v>
       </c>
@@ -4761,11 +4871,11 @@
         <v>0</v>
       </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>43000</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
@@ -4850,8 +4960,11 @@
       <c r="AL49" s="3">
         <v>0</v>
       </c>
+      <c r="AM49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4960,8 +5073,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5070,41 +5186,44 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>746000</v>
+      </c>
+      <c r="E52" s="3">
         <v>604000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>396000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>765000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>755000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>729000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>230000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>497000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>521000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>486000</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
@@ -5121,67 +5240,70 @@
         <v>0</v>
       </c>
       <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
         <v>15635000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>25069000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>27821000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>29316000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>33450000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>30187000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>17824000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>21246000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>20273000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>26575000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>23098000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>20355000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>21054000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>20268000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>20232000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>23566000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>24187000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>24710000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>24017000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>25250000</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5290,118 +5412,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>181475000</v>
+      </c>
+      <c r="E54" s="3">
         <v>157670000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>150142000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>148526000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>136648000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>132238000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>128251000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>120636000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>120593000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>119469000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>115143000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>114683000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>113386000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>114423000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>109113000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>106282000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>104331000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>103764000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>95679000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>84698000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>83965000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>75849000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>71676000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>67804000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>66034000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>63526000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>60547000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>62062000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>60303000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>59093000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>61162000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>59843000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>57597000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>56257000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>54673000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>55064000</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5440,8 +5568,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5480,371 +5609,381 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>140306000</v>
+      </c>
+      <c r="E57" s="3">
         <v>122134000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>116090000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>114180000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>104211000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>101987000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>101805000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>96043000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>96901000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>95725000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>94091000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>93618000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>91691000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>91923000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>86782000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>85345000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>82082000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>81928000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>76441000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>69480000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>69360000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>63348000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>56791000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>55041000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>53763000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>51403000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>48615000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>50347000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>48660000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>47928000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>48165000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>48167000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>46777000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>44865000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>42335000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>43090000</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>21587000</v>
+      </c>
+      <c r="E58" s="3">
         <v>17047000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>16451000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>17032000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>16009000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>14330000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>11473000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10670000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10323000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>10775000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>8958000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>9525000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>10713000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>11690000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>11796000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>10563000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>12005000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>12079000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>9956000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>6366000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5995000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4058000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>6335000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3970000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4116000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>4265000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>4054000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>28000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>193000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>19000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1331000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>38000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>9000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>38000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>74000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>495000</v>
+      </c>
+      <c r="E59" s="3">
         <v>414000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>394000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>675000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>621000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>628000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>228000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>152000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>126000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>164000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>333000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>229000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>162000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>138000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>131000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>130000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>125000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>129000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>126000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>119000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>122000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>135000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>153000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>163000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>178000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>177000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>41000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>35000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>29000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>27000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>22000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>17000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>14000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>11000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>6000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>162671000</v>
+      </c>
+      <c r="E60" s="3">
         <v>139892000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>133246000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>132214000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>121161000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>117264000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>113817000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>107153000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>107620000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>106901000</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -5920,41 +6059,44 @@
       <c r="AL60" s="3">
         <v>0</v>
       </c>
+      <c r="AM60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>106000</v>
+      </c>
+      <c r="E61" s="3">
         <v>100000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>91000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>122000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>111000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>109000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>143000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>127000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>121000</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -6030,41 +6172,44 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>195000</v>
+        <v>180000</v>
       </c>
       <c r="E62" s="3">
         <v>195000</v>
       </c>
       <c r="F62" s="3">
+        <v>195000</v>
+      </c>
+      <c r="G62" s="3">
         <v>185000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>192000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>206000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>210000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>212000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>189000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>214000</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
@@ -6140,8 +6285,11 @@
       <c r="AL62" s="3">
         <v>0</v>
       </c>
+      <c r="AM62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6250,8 +6398,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6360,8 +6511,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6470,118 +6624,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>162957000</v>
+      </c>
+      <c r="E66" s="3">
         <v>140187000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>133545000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>132521000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>121464000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>117579000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>114184000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>107372000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>107936000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>107236000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>112295000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>112006000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>110862000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>111967000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>106718000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>103951000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>102181000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>101728000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>93728000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>83089000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>82427000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>74363000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>70224000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>66399000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>64654000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>62201000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>59265000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>60819000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>59120000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>57961000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>60072000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>58747000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>56548000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>55260000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>53699000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>54083000</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6620,8 +6780,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6730,8 +6891,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6840,8 +7004,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6950,8 +7117,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7060,118 +7230,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2890000</v>
+      </c>
+      <c r="E72" s="3">
         <v>2701000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2515000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2325000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2168000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2016000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1852000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1703000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1546000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1432000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1294000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1168000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1079000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1017000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>953000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>896000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>864000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>781000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>683000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>621000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>583000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>558000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>520000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>484000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>456000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>431000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>390000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>354000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>323000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>290000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>251000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>260000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>236000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>220000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>203000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7280,8 +7456,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7390,8 +7569,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7500,118 +7682,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4825000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4502000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4280000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4145000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3927000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3732000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3584000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3390000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3158000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3001000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2848000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2677000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2524000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2456000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2395000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2331000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2150000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2036000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1951000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1609000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1538000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1486000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1452000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1405000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1380000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1325000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1282000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1243000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1183000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1132000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1090000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1096000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1049000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>997000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>974000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>981000</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7720,233 +7908,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>224000</v>
+      </c>
+      <c r="E81" s="3">
         <v>213000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>217000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>184000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>179000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>175000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>160000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>167000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>125000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>148000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>136000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>99000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>72000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>73000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>67000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>42000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>92000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>107000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>71000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>46000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>32000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>46000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>44000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>36000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>32000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>49000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>43000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>39000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>41000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>46000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>31000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>23000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>24000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>4000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7985,8 +8182,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7994,10 +8192,10 @@
         <v>24000</v>
       </c>
       <c r="E83" s="3">
+        <v>24000</v>
+      </c>
+      <c r="F83" s="3">
         <v>25000</v>
-      </c>
-      <c r="F83" s="3">
-        <v>23000</v>
       </c>
       <c r="G83" s="3">
         <v>23000</v>
@@ -8006,49 +8204,49 @@
         <v>23000</v>
       </c>
       <c r="I83" s="3">
+        <v>23000</v>
+      </c>
+      <c r="J83" s="3">
         <v>22000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>20000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>21000</v>
       </c>
       <c r="L83" s="3">
         <v>21000</v>
       </c>
       <c r="M83" s="3">
+        <v>21000</v>
+      </c>
+      <c r="N83" s="3">
         <v>15000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>14000</v>
       </c>
       <c r="O83" s="3">
         <v>14000</v>
       </c>
       <c r="P83" s="3">
+        <v>14000</v>
+      </c>
+      <c r="Q83" s="3">
         <v>15000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>13000</v>
-      </c>
-      <c r="R83" s="3">
-        <v>12000</v>
       </c>
       <c r="S83" s="3">
         <v>12000</v>
       </c>
       <c r="T83" s="3">
+        <v>12000</v>
+      </c>
+      <c r="U83" s="3">
         <v>13000</v>
-      </c>
-      <c r="U83" s="3">
-        <v>11000</v>
       </c>
       <c r="V83" s="3">
         <v>11000</v>
       </c>
       <c r="W83" s="3">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="X83" s="3">
         <v>10000</v>
@@ -8057,7 +8255,7 @@
         <v>10000</v>
       </c>
       <c r="Z83" s="3">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="AA83" s="3">
         <v>7000</v>
@@ -8066,22 +8264,22 @@
         <v>7000</v>
       </c>
       <c r="AC83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AD83" s="3">
         <v>8000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>6000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>5000</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>7000</v>
       </c>
       <c r="AG83" s="3">
         <v>7000</v>
       </c>
       <c r="AH83" s="3">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="AI83" s="3">
         <v>6000</v>
@@ -8090,13 +8288,16 @@
         <v>6000</v>
       </c>
       <c r="AK83" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AL83" s="3">
         <v>7000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8205,8 +8406,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8315,8 +8519,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8425,8 +8632,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8535,8 +8745,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8645,118 +8858,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7139000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2584000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1838000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3582000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1621000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1683000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2369000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>979000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2119000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-923000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-30000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2414000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-541000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2125000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-375000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1213000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1324000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3734000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4596000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-174000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1557000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>5203000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>488000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>133000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1442000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>603000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-408000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>632000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>931000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1201000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-2153000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>709000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>807000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>779000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>430000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>102000</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8795,118 +9014,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-16000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-15000</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-11000</v>
       </c>
       <c r="G91" s="3">
         <v>-11000</v>
       </c>
       <c r="H91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="I91" s="3">
         <v>-12000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-15000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-17000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-19000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-18000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-19000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-26000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-17000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-21000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-19000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-9000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-10000</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-12000</v>
       </c>
       <c r="Y91" s="3">
         <v>-12000</v>
       </c>
       <c r="Z91" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-17000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-19000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-7000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9015,8 +9238,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9125,118 +9351,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-42000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-26000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>18000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-35000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-14000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-25000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-18000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-15000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>6000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-19000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-22000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-12000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-129000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-21000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-17000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-21000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-22000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-12000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-15000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-20000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-42000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-7000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-28000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-12000</v>
-      </c>
-      <c r="AH94" s="3">
-        <v>-4000</v>
       </c>
       <c r="AI94" s="3">
         <v>-4000</v>
       </c>
       <c r="AJ94" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AK94" s="3">
         <v>-6000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-17000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9275,13 +9507,14 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="E96" s="3">
         <v>27000</v>
@@ -9293,40 +9526,40 @@
         <v>27000</v>
       </c>
       <c r="H96" s="3">
-        <v>11000</v>
+        <v>27000</v>
       </c>
       <c r="I96" s="3">
         <v>11000</v>
       </c>
       <c r="J96" s="3">
+        <v>11000</v>
+      </c>
+      <c r="K96" s="3">
         <v>10000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>11000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>10000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-10000</v>
       </c>
       <c r="N96" s="3">
         <v>-10000</v>
       </c>
       <c r="O96" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="P96" s="3">
         <v>-11000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-9000</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-10000</v>
       </c>
       <c r="R96" s="3">
         <v>-10000</v>
       </c>
       <c r="S96" s="3">
-        <v>-9000</v>
+        <v>-10000</v>
       </c>
       <c r="T96" s="3">
         <v>-9000</v>
@@ -9335,13 +9568,13 @@
         <v>-9000</v>
       </c>
       <c r="V96" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-8000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-7000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-8000</v>
       </c>
       <c r="Y96" s="3">
         <v>-8000</v>
@@ -9350,19 +9583,19 @@
         <v>-8000</v>
       </c>
       <c r="AA96" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-7000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-7000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-8000</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-7000</v>
       </c>
       <c r="AF96" s="3">
         <v>-7000</v>
@@ -9380,13 +9613,16 @@
         <v>-7000</v>
       </c>
       <c r="AK96" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-6000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9495,8 +9731,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9605,8 +9844,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9715,334 +9957,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-331000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-225000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-186000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-177000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-333000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-137000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-108000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-127000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-252000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-137000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-122000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-70000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-173000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-105000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-174000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-506000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>158000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-555000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>416000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-27000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-63000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-61000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-242000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-46000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-70000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-58000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-222000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-55000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-64000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-80000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-133000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-84000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-77000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>9000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-102000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>148000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-76000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>31000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>19000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>158000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-123000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-105000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-41000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>158000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-123000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-105000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-41000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-40000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>21000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-76000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>95000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>45000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>22000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-38000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>38000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-28000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>16000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-78000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>8000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>5000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>38000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>23000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-47000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7072000</v>
+      </c>
+      <c r="E102" s="3">
         <v>2440000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1422000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3523000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1264000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1431000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2384000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>758000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1883000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1035000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2199000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-831000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1965000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-680000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>646000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1486000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3636000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4114000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>282000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1574000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>5091000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>453000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-152000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1392000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>489000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-485000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>399000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>770000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1137000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2246000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>577000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>757000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>719000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>375000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>107000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IBKR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IBKR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
   <si>
     <t>IBKR</t>
   </si>
@@ -656,286 +656,292 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1618000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1651000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1533000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1407000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1405000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1340000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1250000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1205000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1148000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1162000</v>
-      </c>
-      <c r="M8" s="3">
-        <v>1055000</v>
       </c>
       <c r="N8" s="3">
         <v>1055000</v>
       </c>
       <c r="O8" s="3">
+        <v>1055000</v>
+      </c>
+      <c r="P8" s="3">
         <v>1522000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1100000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>768000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>695000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>658000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>515000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>787000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>978000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>654000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>593000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>587000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>645000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>640000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>697000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>652000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>623000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>637000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>578000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>565000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>581000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>500000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>456000</v>
-      </c>
-      <c r="AK8" s="3">
-        <v>409000</v>
       </c>
       <c r="AL8" s="3">
         <v>409000</v>
       </c>
       <c r="AM8" s="3">
+        <v>409000</v>
+      </c>
+      <c r="AN8" s="3">
         <v>215000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>366000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>102000</v>
+      </c>
+      <c r="E9" s="3">
         <v>103000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>127000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>131000</v>
-      </c>
-      <c r="G9" s="3">
-        <v>125000</v>
       </c>
       <c r="H9" s="3">
         <v>125000</v>
@@ -944,216 +950,222 @@
         <v>125000</v>
       </c>
       <c r="J9" s="3">
+        <v>125000</v>
+      </c>
+      <c r="K9" s="3">
         <v>111000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>112000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>108000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>103000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>104000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>636000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>396000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>189000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>121000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>108000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>112000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>87000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>153000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>121000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>119000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>124000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>113000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>131000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>177000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>173000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>162000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>142000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>119000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>108000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>94000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>78000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>61000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>51000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>35000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>22000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1516000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1548000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1406000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1276000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1280000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1215000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1125000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1094000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1036000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1054000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>952000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>951000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>886000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>704000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>579000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>574000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>550000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>403000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>700000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>825000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>533000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>474000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>463000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>532000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>509000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>520000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>479000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>461000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>495000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>459000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>457000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>487000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>422000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>395000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>358000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>374000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>193000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>345000</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1194,8 +1206,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1310,8 +1323,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1426,28 +1442,31 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>48000</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H14" s="3">
+        <v>-100000</v>
+      </c>
+      <c r="I14" s="3">
         <v>100000</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
@@ -1464,8 +1483,8 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1506,17 +1525,17 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AE14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>8</v>
@@ -1524,11 +1543,11 @@
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>-93000</v>
-      </c>
-      <c r="AJ14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK14" s="3" t="s">
         <v>8</v>
@@ -1542,13 +1561,16 @@
       <c r="AN14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="E15" s="3">
         <v>15000</v>
@@ -1557,10 +1579,10 @@
         <v>15000</v>
       </c>
       <c r="G15" s="3">
+        <v>15000</v>
+      </c>
+      <c r="H15" s="3">
         <v>16000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>17000</v>
       </c>
       <c r="I15" s="3">
         <v>17000</v>
@@ -1569,19 +1591,19 @@
         <v>17000</v>
       </c>
       <c r="K15" s="3">
+        <v>17000</v>
+      </c>
+      <c r="L15" s="3">
         <v>16000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>17000</v>
-      </c>
-      <c r="M15" s="3">
-        <v>16000</v>
       </c>
       <c r="N15" s="3">
         <v>16000</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1658,8 +1680,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1697,8 +1722,9 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1706,231 +1732,237 @@
         <v>343000</v>
       </c>
       <c r="E17" s="3">
+        <v>343000</v>
+      </c>
+      <c r="F17" s="3">
         <v>376000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>372000</v>
       </c>
-      <c r="G17" s="3">
-        <v>347000</v>
-      </c>
       <c r="H17" s="3">
+        <v>447000</v>
+      </c>
+      <c r="I17" s="3">
         <v>356000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>350000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>337000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>323000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>305000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>348000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>295000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>833000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>577000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>376000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>301000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>285000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>281000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>246000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>339000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>262000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>259000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>365000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>337000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>319000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>362000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>361000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>381000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>325000</v>
-      </c>
-      <c r="AF17" s="3">
-        <v>282000</v>
       </c>
       <c r="AG17" s="3">
         <v>282000</v>
       </c>
       <c r="AH17" s="3">
+        <v>282000</v>
+      </c>
+      <c r="AI17" s="3">
         <v>281000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>136000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>219000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>234000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>196000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>187000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1275000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1308000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1157000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1035000</v>
       </c>
-      <c r="G18" s="3">
-        <v>1058000</v>
-      </c>
       <c r="H18" s="3">
+        <v>958000</v>
+      </c>
+      <c r="I18" s="3">
         <v>984000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>900000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>868000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>825000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>857000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>707000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>760000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>689000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>523000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>392000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>394000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>373000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>234000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>541000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>639000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>392000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>334000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>222000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>308000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>321000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>335000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>291000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>242000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>312000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>296000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>283000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>300000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>364000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>237000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>175000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>213000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>28000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1971,47 +2003,48 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-20000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>18000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-25000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>20000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>9000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>17000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>55000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1000</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -2046,165 +2079,171 @@
         <v>0</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-54000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-66000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>97000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-12000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>40000</v>
       </c>
-      <c r="AI20" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3">
         <v>31000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>29000</v>
       </c>
-      <c r="AL20" s="3">
-        <v>0</v>
-      </c>
       <c r="AM20" s="3">
         <v>0</v>
       </c>
       <c r="AN20" s="3">
         <v>0</v>
       </c>
+      <c r="AO20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1268000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1327000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1167000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1070000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1056000</v>
-      </c>
       <c r="H21" s="3">
+        <v>956000</v>
+      </c>
+      <c r="I21" s="3">
         <v>1026000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>897000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>883000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>832000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>857000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>668000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>777000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>704000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>537000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>406000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>409000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>386000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>246000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>553000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>652000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>403000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>345000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>232000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>318000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>322000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>288000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>232000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>346000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>317000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>282000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>276000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>347000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>371000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>274000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>210000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>219000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>35000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>189000</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2241,8 +2280,8 @@
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2319,240 +2358,249 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1300000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1312000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1104000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1055000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1040000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>909000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>880000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>866000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>816000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>840000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>652000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>761000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>689000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>523000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>392000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>394000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>373000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>234000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>541000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>639000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>392000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>334000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>222000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>308000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>312000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>281000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>225000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>339000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>309000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>276000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>271000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>340000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>364000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>268000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>204000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>213000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>28000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E24" s="3">
         <v>126000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>98000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>91000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>71000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>75000</v>
-      </c>
-      <c r="I24" s="3">
-        <v>71000</v>
       </c>
       <c r="J24" s="3">
         <v>71000</v>
       </c>
       <c r="K24" s="3">
+        <v>71000</v>
+      </c>
+      <c r="L24" s="3">
         <v>77000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>68000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>51000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>61000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>56000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>40000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>32000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>28000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>35000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>28000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>35000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>53000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>12000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>32000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>15000</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>18000</v>
       </c>
       <c r="AA24" s="3">
         <v>18000</v>
       </c>
       <c r="AB24" s="3">
+        <v>18000</v>
+      </c>
+      <c r="AC24" s="3">
         <v>20000</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>15000</v>
       </c>
       <c r="AD24" s="3">
         <v>15000</v>
       </c>
       <c r="AE24" s="3">
+        <v>15000</v>
+      </c>
+      <c r="AF24" s="3">
         <v>19000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>18000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>13000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>21000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>23000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>21000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>17000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>18000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>7000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2667,240 +2715,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1201000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1186000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1006000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>964000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>969000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>834000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>809000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>795000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>739000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>772000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>601000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>700000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>633000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>483000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>360000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>366000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>338000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>206000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>506000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>586000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>380000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>302000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>207000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>290000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>294000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>261000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>210000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>324000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>290000</v>
-      </c>
-      <c r="AF26" s="3">
-        <v>258000</v>
       </c>
       <c r="AG26" s="3">
         <v>258000</v>
       </c>
       <c r="AH26" s="3">
+        <v>258000</v>
+      </c>
+      <c r="AI26" s="3">
         <v>319000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>341000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>247000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>187000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>195000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>21000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>168000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>284000</v>
+      </c>
+      <c r="E27" s="3">
         <v>263000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>224000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>213000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>217000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>184000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>179000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>175000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>160000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>167000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>125000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>148000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>136000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>99000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>72000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>73000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>67000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>42000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>92000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>107000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>71000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>46000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>32000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>46000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>44000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>36000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>32000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>49000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>43000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>39000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>41000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>46000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>175000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>31000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>23000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>24000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>4000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3015,8 +3072,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3095,17 +3155,17 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="3" t="s">
+      <c r="AE29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -3113,11 +3173,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-177000</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
@@ -3131,8 +3191,11 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3247,8 +3310,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3363,47 +3429,50 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="E32" s="3">
         <v>4000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>20000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-18000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>25000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-20000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-9000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-17000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-55000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1000</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -3438,165 +3507,171 @@
         <v>0</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>9000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>54000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>66000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-97000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>3000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>20000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>12000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-40000</v>
       </c>
-      <c r="AI32" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3">
         <v>-31000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-29000</v>
       </c>
-      <c r="AL32" s="3">
-        <v>0</v>
-      </c>
       <c r="AM32" s="3">
         <v>0</v>
       </c>
       <c r="AN32" s="3">
         <v>0</v>
       </c>
+      <c r="AO32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>284000</v>
+      </c>
+      <c r="E33" s="3">
         <v>263000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>224000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>213000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>217000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>184000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>179000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>175000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>160000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>167000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>125000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>148000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>136000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>99000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>72000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>73000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>67000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>42000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>92000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>107000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>71000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>46000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>32000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>46000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>44000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>36000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>32000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>49000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>43000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>39000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>41000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>46000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>31000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>23000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>24000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>4000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3711,245 +3786,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>284000</v>
+      </c>
+      <c r="E35" s="3">
         <v>263000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>224000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>213000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>217000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>184000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>179000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>175000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>160000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>167000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>125000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>148000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>136000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>99000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>72000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>73000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>67000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>42000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>92000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>107000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>71000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>46000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>32000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>46000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>44000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>36000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>32000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>49000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>43000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>39000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>41000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>46000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>31000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>23000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>24000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>4000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3990,8 +4074,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4032,163 +4117,167 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4963000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5128000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4688000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3500000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3633000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3595000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3918000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4063000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3753000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3824000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3681000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3214000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3436000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3184000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2881000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2667000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2395000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2838000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3218000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2627000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4292000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3292000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3115000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3101000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2882000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3035000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3162000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2546000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2597000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3062000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2500000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1901000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1732000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2056000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2115000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1656000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1925000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1550000</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>100541000</v>
+      </c>
+      <c r="E42" s="3">
         <v>110694000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>105559000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>86194000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>78314000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>84957000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>73883000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>73401000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>77053000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>70002000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>72152000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>73729000</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -4264,124 +4353,130 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>96200000</v>
+      </c>
+      <c r="E43" s="3">
         <v>82889000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>69904000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>66830000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>67105000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>58668000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>57592000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>53550000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>46516000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>45788000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>43771000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>41558000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>42570000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>43969000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>44641000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>50612000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>58833000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>54654000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>54045000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>46129000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>40691000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>32987000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>27154000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>21740000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>32147000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>26969000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>26770000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>26746000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>27864000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>31876000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>30221000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>30565000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>30760000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>26444000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>24056000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>22387000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>20506000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>19053000</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4418,8 +4513,8 @@
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4496,8 +4591,11 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4534,54 +4632,54 @@
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3">
         <v>56948000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>56733000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>54245000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>48931000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>38009000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>37525000</v>
       </c>
-      <c r="U45" s="3">
-        <v>0</v>
-      </c>
       <c r="V45" s="3">
+        <v>0</v>
+      </c>
+      <c r="W45" s="3">
         <v>21204000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>15903000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>12789000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>12684000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>14272000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>9400000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>8794000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>8819000</v>
       </c>
-      <c r="AD45" s="3">
-        <v>0</v>
-      </c>
       <c r="AE45" s="3">
         <v>0</v>
       </c>
@@ -4612,47 +4710,50 @@
       <c r="AN45" s="3">
         <v>0</v>
       </c>
+      <c r="AO45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>201704000</v>
+      </c>
+      <c r="E46" s="3">
         <v>198711000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>180151000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>156524000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>149052000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>147220000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>135393000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>131014000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>127322000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>119614000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>119604000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>118501000</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -4728,210 +4829,216 @@
       <c r="AN46" s="3">
         <v>0</v>
       </c>
+      <c r="AO46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>288000</v>
+      </c>
+      <c r="E47" s="3">
         <v>344000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>283000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>243000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>235000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>241000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>204000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>191000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>210000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>201000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>165000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>173000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>11263000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>9861000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>10694000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>11290000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>8965000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>10578000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>30621000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>8040000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>6378000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>5848000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>7092000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>6082000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>8943000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>7284000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>6522000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>7103000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>6692000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>6470000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>6209000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>6060000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>8146000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>7364000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>6834000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>7058000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>7777000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>8756000</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>197000</v>
+      </c>
+      <c r="E48" s="3">
         <v>101000</v>
-      </c>
-      <c r="E48" s="3">
-        <v>107000</v>
       </c>
       <c r="F48" s="3">
         <v>107000</v>
       </c>
       <c r="G48" s="3">
+        <v>107000</v>
+      </c>
+      <c r="H48" s="3">
         <v>161000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>110000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>107000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>111000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>201000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>117000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>119000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>120000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>119000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>109000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>105000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>109000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>101000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>100000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>96000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>98000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>101000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>107000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>110000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>114000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>118000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>122000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>127000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>131000</v>
-      </c>
-      <c r="AE48" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF48" s="3" t="s">
         <v>8</v>
@@ -4942,8 +5049,8 @@
       <c r="AH48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI48" s="3">
-        <v>0</v>
+      <c r="AI48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ48" s="3">
         <v>0</v>
@@ -4960,13 +5067,16 @@
       <c r="AN48" s="3">
         <v>0</v>
       </c>
+      <c r="AO48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>52000</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
@@ -4975,11 +5085,11 @@
         <v>0</v>
       </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>48000</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
@@ -4987,11 +5097,11 @@
         <v>0</v>
       </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>43000</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
         <v>0</v>
       </c>
@@ -5076,8 +5186,11 @@
       <c r="AN49" s="3">
         <v>0</v>
       </c>
+      <c r="AO49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5192,8 +5305,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5308,47 +5424,50 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>727000</v>
+      </c>
+      <c r="E52" s="3">
         <v>843000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>746000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>604000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>396000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>765000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>755000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>729000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>230000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>497000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>521000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>486000</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
       <c r="P52" s="3">
         <v>0</v>
       </c>
@@ -5365,67 +5484,70 @@
         <v>0</v>
       </c>
       <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
         <v>15635000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>25069000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>27821000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>29316000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>33450000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>30187000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>17824000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>21246000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>20273000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>26575000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>23098000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>20355000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>21054000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>20268000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>20232000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>23566000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>24187000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>24710000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>24017000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>25250000</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5540,124 +5662,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>203240000</v>
+      </c>
+      <c r="E54" s="3">
         <v>200222000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>181475000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>157670000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>150142000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>148526000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>136648000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>132238000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>128251000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>120636000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>120593000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>119469000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>115143000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>114683000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>113386000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>114423000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>109113000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>106282000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>104331000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>103764000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>95679000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>84698000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>83965000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>75849000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>71676000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>67804000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>66034000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>63526000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>60547000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>62062000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>60303000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>59093000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>61162000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>59843000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>57597000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>56257000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>54673000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>55064000</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5698,8 +5826,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5740,395 +5869,405 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>156085000</v>
+      </c>
+      <c r="E57" s="3">
         <v>151266000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>140306000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>122134000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>116090000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>114180000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>104211000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>101987000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>101805000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>96043000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>96901000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>95725000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>94091000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>93618000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>91691000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>91923000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>86782000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>85345000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>82082000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>81928000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>76441000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>69480000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>69360000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>63348000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>56791000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>55041000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>53763000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>51403000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>48615000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>50347000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>48660000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>47928000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>48165000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>48167000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>46777000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>44865000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>42335000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>43090000</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>25301000</v>
+      </c>
+      <c r="E58" s="3">
         <v>28212000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>21587000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>17047000</v>
       </c>
-      <c r="G58" s="3">
-        <v>16451000</v>
-      </c>
       <c r="H58" s="3">
+        <v>16421000</v>
+      </c>
+      <c r="I58" s="3">
         <v>17032000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>16009000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>14330000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11473000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>10670000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>10323000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>10775000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>8958000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>9525000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>10713000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>11690000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>11796000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>10563000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>12005000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>12079000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>9956000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>6366000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>5995000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4058000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>6335000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3970000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>4116000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>4265000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>4054000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>28000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>193000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>19000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1331000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>38000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>9000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>38000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>74000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>669000</v>
+      </c>
+      <c r="E59" s="3">
         <v>624000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>495000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>414000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>394000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>675000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>621000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>628000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>228000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>152000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>126000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>164000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>333000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>229000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>162000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>138000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>131000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>130000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>125000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>129000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>126000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>119000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>122000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>135000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>153000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>163000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>178000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>177000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>41000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>35000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>29000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>27000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>22000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>17000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>14000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>11000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>6000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>182376000</v>
+      </c>
+      <c r="E60" s="3">
         <v>180419000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>162671000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>139892000</v>
       </c>
-      <c r="G60" s="3">
-        <v>133246000</v>
-      </c>
       <c r="H60" s="3">
+        <v>133216000</v>
+      </c>
+      <c r="I60" s="3">
         <v>132214000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>121161000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>117264000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>113817000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>107153000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>107620000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>106901000</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -6204,47 +6343,50 @@
       <c r="AN60" s="3">
         <v>0</v>
       </c>
+      <c r="AO60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>152000</v>
+      </c>
+      <c r="E61" s="3">
         <v>108000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>106000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>100000</v>
       </c>
-      <c r="G61" s="3">
-        <v>91000</v>
-      </c>
       <c r="H61" s="3">
+        <v>121000</v>
+      </c>
+      <c r="I61" s="3">
         <v>122000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>111000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>109000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>143000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>127000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>121000</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -6320,47 +6462,50 @@
       <c r="AN61" s="3">
         <v>0</v>
       </c>
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>217000</v>
+      </c>
+      <c r="E62" s="3">
         <v>215000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>180000</v>
-      </c>
-      <c r="F62" s="3">
-        <v>195000</v>
       </c>
       <c r="G62" s="3">
         <v>195000</v>
       </c>
       <c r="H62" s="3">
+        <v>195000</v>
+      </c>
+      <c r="I62" s="3">
         <v>185000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>192000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>206000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>210000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>212000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>189000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>214000</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
@@ -6436,8 +6581,11 @@
       <c r="AN62" s="3">
         <v>0</v>
       </c>
+      <c r="AO62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6552,8 +6700,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6668,8 +6819,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6784,124 +6938,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>182768000</v>
+      </c>
+      <c r="E66" s="3">
         <v>180742000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>162957000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>140187000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>133545000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>132521000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>121464000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>117579000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>114184000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>107372000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>107936000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>107236000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>112295000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>112006000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>110862000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>111967000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>106718000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>103951000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>102181000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>101728000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>93728000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>83089000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>82427000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>74363000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>70224000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>66399000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>64654000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>62201000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>59265000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>60819000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>59120000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>57961000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>60072000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>58747000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>56548000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>55260000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>53699000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>54083000</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6942,8 +7102,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7058,8 +7219,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7174,8 +7338,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7290,8 +7457,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7406,124 +7576,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3365000</v>
+      </c>
+      <c r="E72" s="3">
         <v>3117000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2890000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2701000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2515000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2325000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2168000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2016000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1852000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1703000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1546000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1432000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1294000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1168000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1079000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1017000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>953000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>896000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>864000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>781000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>683000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>621000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>583000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>558000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>520000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>484000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>456000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>431000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>390000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>354000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>323000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>290000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>251000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>260000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>236000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>220000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>203000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7638,8 +7814,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7754,8 +7933,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7870,124 +8052,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5363000</v>
+      </c>
+      <c r="E76" s="3">
         <v>5106000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4825000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4502000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4280000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4145000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3927000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3732000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3584000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3390000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3158000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3001000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2848000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2677000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2524000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2456000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2395000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2331000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2150000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2036000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1951000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1609000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1538000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1486000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1452000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1405000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1380000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1325000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1282000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1243000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1183000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1132000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1090000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1096000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1049000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>997000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>974000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>981000</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8102,245 +8290,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>284000</v>
+      </c>
+      <c r="E81" s="3">
         <v>263000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>224000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>213000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>217000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>184000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>179000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>175000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>160000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>167000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>125000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>148000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>136000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>99000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>72000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>73000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>67000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>42000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>92000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>107000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>71000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>46000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>32000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>46000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>44000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>36000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>32000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>49000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>43000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>39000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>41000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>46000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>31000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>23000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>24000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>4000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8381,25 +8578,26 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E83" s="3">
         <v>25000</v>
-      </c>
-      <c r="E83" s="3">
-        <v>24000</v>
       </c>
       <c r="F83" s="3">
         <v>24000</v>
       </c>
       <c r="G83" s="3">
+        <v>24000</v>
+      </c>
+      <c r="H83" s="3">
         <v>25000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>23000</v>
       </c>
       <c r="I83" s="3">
         <v>23000</v>
@@ -8408,49 +8606,49 @@
         <v>23000</v>
       </c>
       <c r="K83" s="3">
+        <v>23000</v>
+      </c>
+      <c r="L83" s="3">
         <v>22000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>20000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>21000</v>
       </c>
       <c r="N83" s="3">
         <v>21000</v>
       </c>
       <c r="O83" s="3">
+        <v>21000</v>
+      </c>
+      <c r="P83" s="3">
         <v>15000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>14000</v>
       </c>
       <c r="Q83" s="3">
         <v>14000</v>
       </c>
       <c r="R83" s="3">
+        <v>14000</v>
+      </c>
+      <c r="S83" s="3">
         <v>15000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>13000</v>
-      </c>
-      <c r="T83" s="3">
-        <v>12000</v>
       </c>
       <c r="U83" s="3">
         <v>12000</v>
       </c>
       <c r="V83" s="3">
+        <v>12000</v>
+      </c>
+      <c r="W83" s="3">
         <v>13000</v>
-      </c>
-      <c r="W83" s="3">
-        <v>11000</v>
       </c>
       <c r="X83" s="3">
         <v>11000</v>
       </c>
       <c r="Y83" s="3">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="Z83" s="3">
         <v>10000</v>
@@ -8459,7 +8657,7 @@
         <v>10000</v>
       </c>
       <c r="AB83" s="3">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="AC83" s="3">
         <v>7000</v>
@@ -8468,22 +8666,22 @@
         <v>7000</v>
       </c>
       <c r="AE83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AF83" s="3">
         <v>8000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>6000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>5000</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>7000</v>
       </c>
       <c r="AI83" s="3">
         <v>7000</v>
       </c>
       <c r="AJ83" s="3">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="AK83" s="3">
         <v>6000</v>
@@ -8492,13 +8690,16 @@
         <v>6000</v>
       </c>
       <c r="AM83" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AN83" s="3">
         <v>7000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8613,8 +8814,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8729,8 +8933,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8845,8 +9052,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8961,8 +9171,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9077,124 +9290,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1609000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4479000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7139000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2584000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1838000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3582000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1621000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1683000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2369000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>979000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2119000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-923000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-30000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2414000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-541000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2125000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-375000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1213000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1324000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3734000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4596000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-174000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1557000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>5203000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>488000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>133000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1442000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>603000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-408000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>632000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>931000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1201000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-2153000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>709000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>807000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>779000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>430000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>102000</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9235,124 +9454,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-15000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-14000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-16000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15000</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-11000</v>
       </c>
       <c r="I91" s="3">
         <v>-11000</v>
       </c>
       <c r="J91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-12000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-9000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-15000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-17000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-19000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-19000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-26000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-13000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-17000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-21000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-19000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-10000</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-12000</v>
       </c>
       <c r="AA91" s="3">
         <v>-12000</v>
       </c>
       <c r="AB91" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-17000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-7000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9467,8 +9690,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9583,124 +9809,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-59000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-44000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-42000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-26000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>18000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-35000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-14000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-25000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-18000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-15000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>6000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-19000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-12000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-14000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-129000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-21000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-17000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-21000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-22000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-12000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-15000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-20000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-42000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-7000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-28000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-12000</v>
-      </c>
-      <c r="AJ94" s="3">
-        <v>-4000</v>
       </c>
       <c r="AK94" s="3">
         <v>-4000</v>
       </c>
       <c r="AL94" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AM94" s="3">
         <v>-6000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-17000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9741,8 +9973,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9750,10 +9983,10 @@
         <v>36000</v>
       </c>
       <c r="E96" s="3">
+        <v>36000</v>
+      </c>
+      <c r="F96" s="3">
         <v>35000</v>
-      </c>
-      <c r="F96" s="3">
-        <v>27000</v>
       </c>
       <c r="G96" s="3">
         <v>27000</v>
@@ -9765,40 +9998,40 @@
         <v>27000</v>
       </c>
       <c r="J96" s="3">
-        <v>11000</v>
+        <v>27000</v>
       </c>
       <c r="K96" s="3">
         <v>11000</v>
       </c>
       <c r="L96" s="3">
+        <v>11000</v>
+      </c>
+      <c r="M96" s="3">
         <v>10000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>11000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>10000</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-10000</v>
       </c>
       <c r="P96" s="3">
         <v>-10000</v>
       </c>
       <c r="Q96" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="R96" s="3">
         <v>-11000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-9000</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-10000</v>
       </c>
       <c r="T96" s="3">
         <v>-10000</v>
       </c>
       <c r="U96" s="3">
-        <v>-9000</v>
+        <v>-10000</v>
       </c>
       <c r="V96" s="3">
         <v>-9000</v>
@@ -9807,13 +10040,13 @@
         <v>-9000</v>
       </c>
       <c r="X96" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-7000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-8000</v>
       </c>
       <c r="AA96" s="3">
         <v>-8000</v>
@@ -9822,19 +10055,19 @@
         <v>-8000</v>
       </c>
       <c r="AC96" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-7000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-8000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-7000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-8000</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-7000</v>
       </c>
       <c r="AH96" s="3">
         <v>-7000</v>
@@ -9852,13 +10085,16 @@
         <v>-7000</v>
       </c>
       <c r="AM96" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-6000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9973,8 +10209,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10089,8 +10328,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10205,352 +10447,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-183000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-230000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-331000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-225000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-186000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-177000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-333000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-137000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-108000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-127000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-252000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-137000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-122000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-70000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-173000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-105000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-174000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-506000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>158000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-555000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>416000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-27000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-63000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-61000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-242000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-46000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-70000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-58000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-222000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-55000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-64000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-80000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-133000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-84000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-77000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>9000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-248000</v>
+      </c>
+      <c r="E101" s="3">
         <v>153000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-10000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-102000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>148000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-76000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>31000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>19000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>158000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-123000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-105000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-41000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>158000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-123000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-105000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-41000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-40000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>21000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-76000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>95000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>45000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>22000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-38000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>38000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-28000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>16000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-78000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>8000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>5000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>38000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>23000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-47000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1383000</v>
+      </c>
+      <c r="E102" s="3">
         <v>4167000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7072000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2440000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1422000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3523000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1264000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1431000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2384000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>758000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1883000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1035000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-13000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2199000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-831000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1965000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-680000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>646000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1486000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3636000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>4114000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>282000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1574000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>5091000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>453000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-152000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1392000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>489000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-485000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>399000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>770000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1137000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-2246000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>577000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>757000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>719000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>375000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>107000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IBKR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IBKR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
   <si>
     <t>IBKR</t>
   </si>
@@ -656,295 +656,301 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="24" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1643000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1618000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1651000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1533000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1407000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1405000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1340000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1250000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1205000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1148000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1162000</v>
-      </c>
-      <c r="N8" s="3">
-        <v>1055000</v>
       </c>
       <c r="O8" s="3">
         <v>1055000</v>
       </c>
       <c r="P8" s="3">
+        <v>1055000</v>
+      </c>
+      <c r="Q8" s="3">
         <v>1522000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1100000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>768000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>695000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>658000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>515000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>787000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>978000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>654000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>593000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>587000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>645000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>640000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>697000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>652000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>623000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>637000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>578000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>565000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>581000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>500000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>456000</v>
-      </c>
-      <c r="AL8" s="3">
-        <v>409000</v>
       </c>
       <c r="AM8" s="3">
         <v>409000</v>
       </c>
       <c r="AN8" s="3">
+        <v>409000</v>
+      </c>
+      <c r="AO8" s="3">
         <v>215000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>366000</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E9" s="3">
         <v>102000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>103000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>127000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>131000</v>
-      </c>
-      <c r="H9" s="3">
-        <v>125000</v>
       </c>
       <c r="I9" s="3">
         <v>125000</v>
@@ -953,219 +959,225 @@
         <v>125000</v>
       </c>
       <c r="K9" s="3">
+        <v>125000</v>
+      </c>
+      <c r="L9" s="3">
         <v>111000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>112000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>108000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>103000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>104000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>636000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>396000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>189000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>121000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>108000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>112000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>87000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>153000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>121000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>119000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>124000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>113000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>131000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>177000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>173000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>162000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>142000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>119000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>108000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>94000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>78000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>61000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>51000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>35000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>22000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1525000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1516000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1548000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1406000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1276000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1280000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1215000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1125000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1094000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1036000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1054000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>952000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>951000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>886000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>704000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>579000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>574000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>550000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>403000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>700000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>825000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>533000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>474000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>463000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>532000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>509000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>520000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>479000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>461000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>495000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>459000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>457000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>487000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>422000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>395000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>358000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>374000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>193000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>345000</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1326,8 +1339,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1445,31 +1461,34 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>-48000</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>48000</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-100000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>100000</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1486,8 +1505,8 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1528,17 +1547,17 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3" t="s">
+      <c r="AF14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>8</v>
@@ -1546,11 +1565,11 @@
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK14" s="3">
         <v>-93000</v>
-      </c>
-      <c r="AK14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AL14" s="3" t="s">
         <v>8</v>
@@ -1564,8 +1583,11 @@
       <c r="AO14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1573,7 +1595,7 @@
         <v>16000</v>
       </c>
       <c r="E15" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="F15" s="3">
         <v>15000</v>
@@ -1582,10 +1604,10 @@
         <v>15000</v>
       </c>
       <c r="H15" s="3">
+        <v>15000</v>
+      </c>
+      <c r="I15" s="3">
         <v>16000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>17000</v>
       </c>
       <c r="J15" s="3">
         <v>17000</v>
@@ -1594,19 +1616,19 @@
         <v>17000</v>
       </c>
       <c r="L15" s="3">
+        <v>17000</v>
+      </c>
+      <c r="M15" s="3">
         <v>16000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>17000</v>
-      </c>
-      <c r="N15" s="3">
-        <v>16000</v>
       </c>
       <c r="O15" s="3">
         <v>16000</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1683,8 +1705,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1723,246 +1748,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>343000</v>
+        <v>381000</v>
       </c>
       <c r="E17" s="3">
         <v>343000</v>
       </c>
       <c r="F17" s="3">
+        <v>343000</v>
+      </c>
+      <c r="G17" s="3">
         <v>376000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>372000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>447000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>356000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>350000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>337000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>323000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>305000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>348000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>295000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>833000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>577000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>376000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>301000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>285000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>281000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>246000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>339000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>262000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>259000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>365000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>337000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>319000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>362000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>361000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>381000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>325000</v>
-      </c>
-      <c r="AG17" s="3">
-        <v>282000</v>
       </c>
       <c r="AH17" s="3">
         <v>282000</v>
       </c>
       <c r="AI17" s="3">
+        <v>282000</v>
+      </c>
+      <c r="AJ17" s="3">
         <v>281000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>136000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>219000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>234000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>196000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>187000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1262000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1275000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1308000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1157000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1035000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>958000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>984000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>900000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>868000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>825000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>857000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>707000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>760000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>689000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>523000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>392000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>394000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>373000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>234000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>541000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>639000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>392000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>334000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>222000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>308000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>321000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>335000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>291000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>242000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>312000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>296000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>283000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>300000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>364000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>237000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>175000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>213000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>28000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2004,50 +2036,51 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E20" s="3">
         <v>23000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-20000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>18000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-25000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>20000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>9000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>17000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>55000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1000</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -2082,168 +2115,174 @@
         <v>0</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-54000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-66000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>97000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-12000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>40000</v>
       </c>
-      <c r="AJ20" s="3">
-        <v>0</v>
-      </c>
       <c r="AK20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="3">
         <v>31000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>29000</v>
       </c>
-      <c r="AM20" s="3">
-        <v>0</v>
-      </c>
       <c r="AN20" s="3">
         <v>0</v>
       </c>
       <c r="AO20" s="3">
         <v>0</v>
       </c>
+      <c r="AP20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1304000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1268000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1327000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1167000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1070000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>956000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1026000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>897000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>883000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>832000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>857000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>668000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>777000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>704000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>537000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>406000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>409000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>386000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>246000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>553000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>652000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>403000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>345000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>232000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>318000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>322000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>288000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>232000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>346000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>317000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>282000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>276000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>347000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>371000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>274000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>210000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>219000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>35000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>189000</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2283,8 +2322,8 @@
       <c r="O22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2361,246 +2400,255 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1288000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1300000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1312000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1104000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1055000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1040000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>909000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>880000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>866000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>816000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>840000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>652000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>761000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>689000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>523000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>392000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>394000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>373000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>234000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>541000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>639000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>392000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>334000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>222000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>308000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>312000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>281000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>225000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>339000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>309000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>276000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>271000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>340000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>364000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>268000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>204000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>213000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>28000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>117000</v>
+      </c>
+      <c r="E24" s="3">
         <v>99000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>126000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>98000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>91000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>71000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>75000</v>
-      </c>
-      <c r="J24" s="3">
-        <v>71000</v>
       </c>
       <c r="K24" s="3">
         <v>71000</v>
       </c>
       <c r="L24" s="3">
+        <v>71000</v>
+      </c>
+      <c r="M24" s="3">
         <v>77000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>68000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>51000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>61000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>56000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>40000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>32000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>28000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>35000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>28000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>35000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>53000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>12000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>32000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>15000</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>18000</v>
       </c>
       <c r="AB24" s="3">
         <v>18000</v>
       </c>
       <c r="AC24" s="3">
+        <v>18000</v>
+      </c>
+      <c r="AD24" s="3">
         <v>20000</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>15000</v>
       </c>
       <c r="AE24" s="3">
         <v>15000</v>
       </c>
       <c r="AF24" s="3">
+        <v>15000</v>
+      </c>
+      <c r="AG24" s="3">
         <v>19000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>18000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>13000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>21000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>23000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>21000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>17000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>18000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>7000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2718,246 +2766,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1171000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1201000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1186000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1006000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>964000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>969000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>834000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>809000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>795000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>739000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>772000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>601000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>700000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>633000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>483000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>360000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>366000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>338000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>206000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>506000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>586000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>380000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>302000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>207000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>290000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>294000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>261000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>210000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>324000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>290000</v>
-      </c>
-      <c r="AG26" s="3">
-        <v>258000</v>
       </c>
       <c r="AH26" s="3">
         <v>258000</v>
       </c>
       <c r="AI26" s="3">
+        <v>258000</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>319000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>341000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>247000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>187000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>195000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>21000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>168000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>267000</v>
+      </c>
+      <c r="E27" s="3">
         <v>284000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>263000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>224000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>213000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>217000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>184000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>179000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>175000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>160000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>167000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>125000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>148000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>136000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>99000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>72000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>73000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>67000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>42000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>92000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>107000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>71000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>46000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>32000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>46000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>44000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>36000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>32000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>49000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>43000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>39000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>41000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>46000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>175000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>31000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>23000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>24000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>4000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3075,8 +3132,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3158,17 +3218,17 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG29" s="3" t="s">
+      <c r="AF29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -3176,11 +3236,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-177000</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
@@ -3194,8 +3254,11 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3313,8 +3376,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3432,50 +3498,53 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-23000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>20000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-18000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>25000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-20000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-9000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-17000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-55000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1000</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -3510,168 +3579,174 @@
         <v>0</v>
       </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>9000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>54000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>66000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-97000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>3000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>20000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>12000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-40000</v>
       </c>
-      <c r="AJ32" s="3">
-        <v>0</v>
-      </c>
       <c r="AK32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="3">
         <v>-31000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-29000</v>
       </c>
-      <c r="AM32" s="3">
-        <v>0</v>
-      </c>
       <c r="AN32" s="3">
         <v>0</v>
       </c>
       <c r="AO32" s="3">
         <v>0</v>
       </c>
+      <c r="AP32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>267000</v>
+      </c>
+      <c r="E33" s="3">
         <v>284000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>263000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>224000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>213000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>217000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>184000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>179000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>175000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>160000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>167000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>125000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>148000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>136000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>99000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>72000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>73000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>67000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>42000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>92000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>107000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>71000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>46000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>32000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>46000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>44000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>36000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>32000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>49000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>43000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>39000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>41000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>46000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>31000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>23000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>24000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>4000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3789,251 +3864,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>267000</v>
+      </c>
+      <c r="E35" s="3">
         <v>284000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>263000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>224000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>213000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>217000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>184000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>179000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>175000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>160000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>167000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>125000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>148000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>136000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>99000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>72000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>73000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>67000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>42000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>92000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>107000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>71000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>46000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>32000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>46000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>44000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>36000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>32000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>49000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>43000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>39000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>41000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>46000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>31000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>23000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>24000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>4000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4075,8 +4159,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4118,169 +4203,173 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5085000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4963000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5128000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4688000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3500000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3633000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3595000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3918000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4063000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3753000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3824000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3681000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3214000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3436000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3184000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2881000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2667000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2395000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2838000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3218000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2627000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4292000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3292000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3115000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3101000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2882000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3035000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3162000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2546000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2597000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3062000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2500000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1901000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1732000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2056000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2115000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1656000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1925000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1550000</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>119501000</v>
+      </c>
+      <c r="E42" s="3">
         <v>100541000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>110694000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>105559000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>86194000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>78314000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>84957000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>73883000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>73401000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>77053000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>70002000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>72152000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>73729000</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -4356,127 +4445,133 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>92531000</v>
+      </c>
+      <c r="E43" s="3">
         <v>96200000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>82889000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>69904000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>66830000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>67105000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>58668000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>57592000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>53550000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>46516000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>45788000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>43771000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>41558000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>42570000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>43969000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>44641000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>50612000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>58833000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>54654000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>54045000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>46129000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>40691000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>32987000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>27154000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>21740000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>32147000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>26969000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>26770000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>26746000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>27864000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>31876000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>30221000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>30565000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>30760000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>26444000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>24056000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>22387000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>20506000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>19053000</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4516,8 +4611,8 @@
       <c r="O44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4594,8 +4689,11 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4635,54 +4733,54 @@
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3">
         <v>56948000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>56733000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>54245000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>48931000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>38009000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>37525000</v>
       </c>
-      <c r="V45" s="3">
-        <v>0</v>
-      </c>
       <c r="W45" s="3">
+        <v>0</v>
+      </c>
+      <c r="X45" s="3">
         <v>21204000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>15903000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>12789000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>12684000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>14272000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>9400000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>8794000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>8819000</v>
       </c>
-      <c r="AE45" s="3">
-        <v>0</v>
-      </c>
       <c r="AF45" s="3">
         <v>0</v>
       </c>
@@ -4713,50 +4811,53 @@
       <c r="AO45" s="3">
         <v>0</v>
       </c>
+      <c r="AP45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>217117000</v>
+      </c>
+      <c r="E46" s="3">
         <v>201704000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>198711000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>180151000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>156524000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>149052000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>147220000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>135393000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>131014000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>127322000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>119614000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>119604000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>118501000</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -4832,216 +4933,222 @@
       <c r="AO46" s="3">
         <v>0</v>
       </c>
+      <c r="AP46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>269000</v>
+      </c>
+      <c r="E47" s="3">
         <v>288000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>344000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>283000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>243000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>235000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>241000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>204000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>191000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>210000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>201000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>165000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>173000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>11263000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>9861000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>10694000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>11290000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8965000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>10578000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>30621000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>8040000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>6378000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>5848000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>7092000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>6082000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>8943000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>7284000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>6522000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>7103000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>6692000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>6470000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>6209000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>6060000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>8146000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>7364000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>6834000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>7058000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>7777000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>8756000</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>128000</v>
+      </c>
+      <c r="E48" s="3">
         <v>197000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>101000</v>
-      </c>
-      <c r="F48" s="3">
-        <v>107000</v>
       </c>
       <c r="G48" s="3">
         <v>107000</v>
       </c>
       <c r="H48" s="3">
+        <v>107000</v>
+      </c>
+      <c r="I48" s="3">
         <v>161000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>110000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>107000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>111000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>201000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>117000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>119000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>120000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>119000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>109000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>105000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>109000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>101000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>100000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>96000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>98000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>101000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>107000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>110000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>114000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>118000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>122000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>127000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>131000</v>
-      </c>
-      <c r="AF48" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG48" s="3" t="s">
         <v>8</v>
@@ -5052,8 +5159,8 @@
       <c r="AI48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ48" s="3">
-        <v>0</v>
+      <c r="AJ48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK48" s="3">
         <v>0</v>
@@ -5070,17 +5177,20 @@
       <c r="AO48" s="3">
         <v>0</v>
       </c>
+      <c r="AP48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
         <v>52000</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
       <c r="F49" s="3">
         <v>0</v>
       </c>
@@ -5088,11 +5198,11 @@
         <v>0</v>
       </c>
       <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
         <v>48000</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
@@ -5100,11 +5210,11 @@
         <v>0</v>
       </c>
       <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>43000</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
       <c r="N49" s="3">
         <v>0</v>
       </c>
@@ -5189,8 +5299,11 @@
       <c r="AO49" s="3">
         <v>0</v>
       </c>
+      <c r="AP49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5308,8 +5421,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5427,50 +5543,53 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1018000</v>
+      </c>
+      <c r="E52" s="3">
         <v>727000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>843000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>746000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>604000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>396000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>765000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>755000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>729000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>230000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>497000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>521000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>486000</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
       <c r="Q52" s="3">
         <v>0</v>
       </c>
@@ -5487,67 +5606,70 @@
         <v>0</v>
       </c>
       <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3">
         <v>15635000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>25069000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>27821000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>29316000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>33450000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>30187000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>17824000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>21246000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>20273000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>26575000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>23098000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>20355000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>21054000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>20268000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>20232000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>23566000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>24187000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>24710000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>24017000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>25250000</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5665,127 +5787,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>218749000</v>
+      </c>
+      <c r="E54" s="3">
         <v>203240000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>200222000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>181475000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>157670000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>150142000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>148526000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>136648000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>132238000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>128251000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>120636000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>120593000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>119469000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>115143000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>114683000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>113386000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>114423000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>109113000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>106282000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>104331000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>103764000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>95679000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>84698000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>83965000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>75849000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>71676000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>67804000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>66034000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>63526000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>60547000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>62062000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>60303000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>59093000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>61162000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>59843000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>57597000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>56257000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>54673000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>55064000</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5827,8 +5955,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5870,407 +5999,417 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>163819000</v>
+      </c>
+      <c r="E57" s="3">
         <v>156085000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>151266000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>140306000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>122134000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>116090000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>114180000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>104211000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>101987000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>101805000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>96043000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>96901000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>95725000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>94091000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>93618000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>91691000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>91923000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>86782000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>85345000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>82082000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>81928000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>76441000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>69480000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>69360000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>63348000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>56791000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>55041000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>53763000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>51403000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>48615000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>50347000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>48660000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>47928000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>48165000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>48167000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>46777000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>44865000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>42335000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>43090000</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>32235000</v>
+      </c>
+      <c r="E58" s="3">
         <v>25301000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>28212000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>21587000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>17047000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>16421000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>17032000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>16009000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>14330000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11473000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>10670000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>10323000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>10775000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>8958000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>9525000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>10713000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>11690000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>11796000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>10563000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>12005000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>12079000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>9956000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>6366000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5995000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4058000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>6335000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3970000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>4116000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>4265000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>4054000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>28000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>193000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>19000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1331000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>38000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>9000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>38000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>74000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>781000</v>
+      </c>
+      <c r="E59" s="3">
         <v>669000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>624000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>495000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>414000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>394000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>675000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>621000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>628000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>228000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>152000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>126000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>164000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>333000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>229000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>162000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>138000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>131000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>130000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>125000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>129000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>126000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>119000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>122000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>135000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>153000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>163000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>178000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>177000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>41000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>35000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>29000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>27000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>22000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>17000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>14000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>11000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>6000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>197150000</v>
+      </c>
+      <c r="E60" s="3">
         <v>182376000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>180419000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>162671000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>139892000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>133216000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>132214000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>121161000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>117264000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>113817000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>107153000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>107620000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>106901000</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -6346,50 +6485,53 @@
       <c r="AO60" s="3">
         <v>0</v>
       </c>
+      <c r="AP60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>121000</v>
+      </c>
+      <c r="E61" s="3">
         <v>152000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>108000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>106000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>100000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>121000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>122000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>111000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>109000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>143000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>127000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>121000</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -6465,50 +6607,53 @@
       <c r="AO61" s="3">
         <v>0</v>
       </c>
+      <c r="AP61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>218000</v>
+      </c>
+      <c r="E62" s="3">
         <v>217000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>215000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>180000</v>
-      </c>
-      <c r="G62" s="3">
-        <v>195000</v>
       </c>
       <c r="H62" s="3">
         <v>195000</v>
       </c>
       <c r="I62" s="3">
+        <v>195000</v>
+      </c>
+      <c r="J62" s="3">
         <v>185000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>192000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>206000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>210000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>212000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>189000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>214000</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
@@ -6584,8 +6729,11 @@
       <c r="AO62" s="3">
         <v>0</v>
       </c>
+      <c r="AP62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6703,8 +6851,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6822,8 +6973,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6941,127 +7095,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>197489000</v>
+      </c>
+      <c r="E66" s="3">
         <v>182768000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>180742000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>162957000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>140187000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>133545000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>132521000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>121464000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>117579000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>114184000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>107372000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>107936000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>107236000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>112295000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>112006000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>110862000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>111967000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>106718000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>103951000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>102181000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>101728000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>93728000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>83089000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>82427000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>74363000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>70224000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>66399000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>64654000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>62201000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>59265000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>60819000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>59120000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>57961000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>60072000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>58747000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>56548000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>55260000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>53699000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>54083000</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7103,8 +7263,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7222,8 +7383,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7341,8 +7505,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7460,8 +7627,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7579,127 +7749,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3596000</v>
+      </c>
+      <c r="E72" s="3">
         <v>3365000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3117000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2890000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2701000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2515000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2325000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2168000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2016000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1852000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1703000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1546000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1432000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1294000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1168000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1079000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1017000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>953000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>896000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>864000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>781000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>683000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>621000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>583000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>558000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>520000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>484000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>456000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>431000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>390000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>354000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>323000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>290000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>251000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>260000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>236000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>220000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>203000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7817,8 +7993,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7936,8 +8115,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8055,127 +8237,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5585000</v>
+      </c>
+      <c r="E76" s="3">
         <v>5363000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5106000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4825000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4502000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4280000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4145000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3927000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3732000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3584000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3390000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3158000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3001000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2848000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2677000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2524000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2456000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2395000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2331000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2150000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2036000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1951000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1609000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1538000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1486000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1452000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1405000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1380000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1325000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1282000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1243000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1183000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1132000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1090000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1096000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1049000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>997000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>974000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>981000</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8293,251 +8481,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>267000</v>
+      </c>
+      <c r="E81" s="3">
         <v>284000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>263000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>224000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>213000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>217000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>184000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>179000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>175000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>160000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>167000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>125000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>148000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>136000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>99000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>72000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>73000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>67000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>42000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>92000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>107000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>71000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>46000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>32000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>46000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>44000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>36000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>32000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>49000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>43000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>39000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>41000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>46000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>31000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>23000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>24000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>4000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8579,28 +8776,29 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E83" s="3">
         <v>23000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>25000</v>
-      </c>
-      <c r="F83" s="3">
-        <v>24000</v>
       </c>
       <c r="G83" s="3">
         <v>24000</v>
       </c>
       <c r="H83" s="3">
+        <v>24000</v>
+      </c>
+      <c r="I83" s="3">
         <v>25000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>23000</v>
       </c>
       <c r="J83" s="3">
         <v>23000</v>
@@ -8609,49 +8807,49 @@
         <v>23000</v>
       </c>
       <c r="L83" s="3">
+        <v>23000</v>
+      </c>
+      <c r="M83" s="3">
         <v>22000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>20000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>21000</v>
       </c>
       <c r="O83" s="3">
         <v>21000</v>
       </c>
       <c r="P83" s="3">
+        <v>21000</v>
+      </c>
+      <c r="Q83" s="3">
         <v>15000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>14000</v>
       </c>
       <c r="R83" s="3">
         <v>14000</v>
       </c>
       <c r="S83" s="3">
+        <v>14000</v>
+      </c>
+      <c r="T83" s="3">
         <v>15000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>13000</v>
-      </c>
-      <c r="U83" s="3">
-        <v>12000</v>
       </c>
       <c r="V83" s="3">
         <v>12000</v>
       </c>
       <c r="W83" s="3">
+        <v>12000</v>
+      </c>
+      <c r="X83" s="3">
         <v>13000</v>
-      </c>
-      <c r="X83" s="3">
-        <v>11000</v>
       </c>
       <c r="Y83" s="3">
         <v>11000</v>
       </c>
       <c r="Z83" s="3">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="AA83" s="3">
         <v>10000</v>
@@ -8660,7 +8858,7 @@
         <v>10000</v>
       </c>
       <c r="AC83" s="3">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="AD83" s="3">
         <v>7000</v>
@@ -8669,22 +8867,22 @@
         <v>7000</v>
       </c>
       <c r="AF83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AG83" s="3">
         <v>8000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>6000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>5000</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>7000</v>
       </c>
       <c r="AJ83" s="3">
         <v>7000</v>
       </c>
       <c r="AK83" s="3">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="AL83" s="3">
         <v>6000</v>
@@ -8693,13 +8891,16 @@
         <v>6000</v>
       </c>
       <c r="AN83" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AO83" s="3">
         <v>7000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8817,8 +9018,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8936,8 +9140,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9055,8 +9262,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9174,8 +9384,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9293,127 +9506,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3611000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1609000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4479000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7139000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2584000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1838000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3582000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1621000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1683000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2369000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>979000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2119000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-923000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-30000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2414000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-541000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2125000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-375000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1213000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1324000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3734000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4596000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-174000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1557000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>5203000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>488000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>133000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1442000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>603000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-408000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>632000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>931000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1201000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-2153000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>709000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>807000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>779000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>430000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>102000</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9455,127 +9674,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-22000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-15000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-14000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-16000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-15000</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-11000</v>
       </c>
       <c r="J91" s="3">
         <v>-11000</v>
       </c>
       <c r="K91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="L91" s="3">
         <v>-12000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-9000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-15000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-17000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-19000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-18000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-19000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-26000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-13000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-17000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-21000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-10000</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-12000</v>
       </c>
       <c r="AB91" s="3">
         <v>-12000</v>
       </c>
       <c r="AC91" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-17000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-19000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-7000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9693,8 +9916,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9812,127 +10038,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-59000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-44000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-42000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-26000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>18000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-35000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-13000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-25000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-18000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-15000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>6000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-19000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-22000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-12000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-14000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-129000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-21000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-17000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-21000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-22000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-12000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-12000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-15000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-20000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-42000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-7000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-28000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-12000</v>
-      </c>
-      <c r="AK94" s="3">
-        <v>-4000</v>
       </c>
       <c r="AL94" s="3">
         <v>-4000</v>
       </c>
       <c r="AM94" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AN94" s="3">
         <v>-6000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-17000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9974,8 +10206,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9986,10 +10219,10 @@
         <v>36000</v>
       </c>
       <c r="F96" s="3">
+        <v>36000</v>
+      </c>
+      <c r="G96" s="3">
         <v>35000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>27000</v>
       </c>
       <c r="H96" s="3">
         <v>27000</v>
@@ -10001,40 +10234,40 @@
         <v>27000</v>
       </c>
       <c r="K96" s="3">
-        <v>11000</v>
+        <v>27000</v>
       </c>
       <c r="L96" s="3">
         <v>11000</v>
       </c>
       <c r="M96" s="3">
+        <v>11000</v>
+      </c>
+      <c r="N96" s="3">
         <v>10000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>11000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>10000</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-10000</v>
       </c>
       <c r="Q96" s="3">
         <v>-10000</v>
       </c>
       <c r="R96" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="S96" s="3">
         <v>-11000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-9000</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-10000</v>
       </c>
       <c r="U96" s="3">
         <v>-10000</v>
       </c>
       <c r="V96" s="3">
-        <v>-9000</v>
+        <v>-10000</v>
       </c>
       <c r="W96" s="3">
         <v>-9000</v>
@@ -10043,13 +10276,13 @@
         <v>-9000</v>
       </c>
       <c r="Y96" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-7000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-8000</v>
       </c>
       <c r="AB96" s="3">
         <v>-8000</v>
@@ -10058,19 +10291,19 @@
         <v>-8000</v>
       </c>
       <c r="AD96" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-7000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-8000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-7000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-8000</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-7000</v>
       </c>
       <c r="AI96" s="3">
         <v>-7000</v>
@@ -10088,13 +10321,16 @@
         <v>-7000</v>
       </c>
       <c r="AN96" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-6000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10212,8 +10448,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10331,8 +10570,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10450,361 +10692,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-316000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-183000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-230000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-331000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-225000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-186000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-177000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-333000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-137000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-108000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-127000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-252000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-137000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-122000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-70000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-173000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-105000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-174000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-506000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>158000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-555000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>416000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-27000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-63000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-61000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-242000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-46000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-70000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-58000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-222000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-55000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-64000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-80000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-133000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-84000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-77000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>9000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-248000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>153000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-10000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-102000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>148000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-76000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>31000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>19000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>158000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-123000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-105000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-41000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>158000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-123000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-105000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-41000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-40000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>21000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-76000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>95000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>45000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>22000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-38000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>38000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-28000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>16000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-78000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>8000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>5000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>38000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>23000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-47000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3204000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1383000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4167000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7072000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2440000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1422000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3523000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1264000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1431000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2384000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>758000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1883000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1035000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2199000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-831000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1965000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-680000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>646000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1486000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3636000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>4114000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>282000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1574000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>5091000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>453000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-152000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1392000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>489000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-485000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>399000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>770000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1137000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-2246000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>577000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>757000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>719000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>375000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>107000</v>
       </c>
     </row>
